--- a/artfynd/A 49115-2023 artfynd.xlsx
+++ b/artfynd/A 49115-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 49115-2023 artfynd.xlsx
+++ b/artfynd/A 49115-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1027,6 +1027,1789 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>115143341</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56453</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Solberga, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>512600</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6728226</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ål</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Paula Testad</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Paula Testad, Lars Johan Klockars</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>115142298</v>
+      </c>
+      <c r="B6" t="n">
+        <v>78476</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Solberga, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>512293</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6728324</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ål</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Paula Testad</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Paula Testad, Lars Johan Klockars</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>115142552</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57239</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Solberga, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>512326</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6728301</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ål</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Savande spår (se bilder). Svårt att veta hur färska de är.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Paula Testad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Paula Testad, Lars Johan Klockars</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>115142732</v>
+      </c>
+      <c r="B8" t="n">
+        <v>90263</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Solberga, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>512433</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6728164</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ål</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Paula Testad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Paula Testad, Lars Johan Klockars</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>115142596</v>
+      </c>
+      <c r="B9" t="n">
+        <v>78476</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Solberga, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>512326</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6728301</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ål</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Paula Testad</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Paula Testad, Lars Johan Klockars</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>115142921</v>
+      </c>
+      <c r="B10" t="n">
+        <v>90263</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Solberga, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>512447</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6728139</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ål</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Paula Testad</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Paula Testad, Lars Johan Klockars</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>115142434</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57239</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Solberga, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>512325</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6728311</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ål</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Viss osäkerhet om det är verkligen är ringhack.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Paula Testad</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Paula Testad, Lars Johan Klockars</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>115142265</v>
+      </c>
+      <c r="B12" t="n">
+        <v>78476</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Solberga, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>512296</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6728314</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ål</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Gammal naturskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Paula Testad</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Paula Testad, Lars Johan Klockars</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>115142632</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78476</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Solberga, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>512336</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6728307</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ål</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Paula Testad</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Paula Testad, Lars Johan Klockars</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>115142346</v>
+      </c>
+      <c r="B14" t="n">
+        <v>78476</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Solberga, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>512316</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6728299</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ål</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Paula Testad</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Paula Testad, Lars Johan Klockars</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>115143099</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57239</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Solberga , Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>512415</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6728109</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ål</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Bortsprättade mindre ”barkmynt” på gran typiskt för tretåig. Finns rikligt i omgivande skog. Även ringhack? (Se bild!)</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Paula Testad</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Paula Testad, Lars Johan Klockars</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>115143256</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57255</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Solberga, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>512517</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6728155</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ål</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Paula Testad</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Paula Testad, Lars Johan Klockars</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>115143006</v>
+      </c>
+      <c r="B17" t="n">
+        <v>90263</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Solberga , Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>512415</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6728109</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ål</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Paula Testad</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Paula Testad, Lars Johan Klockars</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>115142861</v>
+      </c>
+      <c r="B18" t="n">
+        <v>90227</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Solberga, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>512447</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6728138</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ål</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Paula Testad</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Paula Testad, Lars Johan Klockars</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>115142956</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57255</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Solberga, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>512404</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6728118</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ål</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Paula Testad</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Paula Testad, Lars Johan Klockars</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>115142688</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57255</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Solberga, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>512393</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6728364</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ål</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Paula Testad</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Paula Testad, Lars Johan Klockars</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49115-2023 artfynd.xlsx
+++ b/artfynd/A 49115-2023 artfynd.xlsx
@@ -10090,10 +10090,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>117694724</v>
+        <v>117693944</v>
       </c>
       <c r="B82" t="n">
-        <v>57287</v>
+        <v>96791</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10102,35 +10102,31 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -10138,10 +10134,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>512478</v>
+        <v>512332</v>
       </c>
       <c r="R82" t="n">
-        <v>6728307</v>
+        <v>6728295</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10168,12 +10164,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10182,6 +10178,7 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -10192,7 +10189,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>Äldre barrnaturskog</t>
+          <t>Gammal barrnaturskog</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -10203,7 +10200,7 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Paula Testad, Lars Johan Klockars</t>
+          <t>Paula Testad</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -10326,10 +10323,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>117693944</v>
+        <v>117694724</v>
       </c>
       <c r="B84" t="n">
-        <v>96791</v>
+        <v>57287</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10338,31 +10335,35 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -10370,10 +10371,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>512332</v>
+        <v>512478</v>
       </c>
       <c r="R84" t="n">
-        <v>6728295</v>
+        <v>6728307</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10400,12 +10401,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10414,7 +10415,6 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -10425,7 +10425,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>Gammal barrnaturskog</t>
+          <t>Äldre barrnaturskog</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -10436,7 +10436,7 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Paula Testad</t>
+          <t>Paula Testad, Lars Johan Klockars</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -11151,10 +11151,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>117694161</v>
+        <v>117694385</v>
       </c>
       <c r="B91" t="n">
-        <v>57287</v>
+        <v>78480</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11167,31 +11167,26 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
@@ -11199,10 +11194,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>512387</v>
+        <v>512408</v>
       </c>
       <c r="R91" t="n">
-        <v>6728162</v>
+        <v>6728236</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11243,6 +11238,7 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -11271,10 +11267,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>117694331</v>
+        <v>117694404</v>
       </c>
       <c r="B92" t="n">
-        <v>57287</v>
+        <v>57303</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11287,16 +11283,16 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -11319,10 +11315,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>512401</v>
+        <v>512423</v>
       </c>
       <c r="R92" t="n">
-        <v>6728197</v>
+        <v>6728253</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11391,10 +11387,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>117694385</v>
+        <v>117694161</v>
       </c>
       <c r="B93" t="n">
-        <v>78480</v>
+        <v>57287</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11407,26 +11403,31 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
@@ -11434,10 +11435,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>512408</v>
+        <v>512387</v>
       </c>
       <c r="R93" t="n">
-        <v>6728236</v>
+        <v>6728162</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11478,7 +11479,6 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -11507,10 +11507,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>117694404</v>
+        <v>117694331</v>
       </c>
       <c r="B94" t="n">
-        <v>57303</v>
+        <v>57287</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11523,16 +11523,16 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -11555,10 +11555,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>512423</v>
+        <v>512401</v>
       </c>
       <c r="R94" t="n">
-        <v>6728253</v>
+        <v>6728197</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>

--- a/artfynd/A 49115-2023 artfynd.xlsx
+++ b/artfynd/A 49115-2023 artfynd.xlsx
@@ -10090,10 +10090,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>117693944</v>
+        <v>117694724</v>
       </c>
       <c r="B82" t="n">
-        <v>96791</v>
+        <v>57287</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10102,31 +10102,35 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -10134,10 +10138,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>512332</v>
+        <v>512478</v>
       </c>
       <c r="R82" t="n">
-        <v>6728295</v>
+        <v>6728307</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10164,12 +10168,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10178,7 +10182,6 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -10189,7 +10192,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>Gammal barrnaturskog</t>
+          <t>Äldre barrnaturskog</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -10200,17 +10203,17 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Paula Testad</t>
+          <t>Paula Testad, Lars Johan Klockars</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>117694397</v>
+        <v>117693959</v>
       </c>
       <c r="B83" t="n">
-        <v>78480</v>
+        <v>79597</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10219,25 +10222,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -10250,10 +10253,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>512407</v>
+        <v>512288</v>
       </c>
       <c r="R83" t="n">
-        <v>6728237</v>
+        <v>6728327</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10323,10 +10326,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>117694724</v>
+        <v>117694404</v>
       </c>
       <c r="B84" t="n">
-        <v>57287</v>
+        <v>57303</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10339,16 +10342,16 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -10371,10 +10374,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>512478</v>
+        <v>512423</v>
       </c>
       <c r="R84" t="n">
-        <v>6728307</v>
+        <v>6728253</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10401,12 +10404,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10425,7 +10428,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>Äldre barrnaturskog</t>
+          <t>Gammal barrnaturskog</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -10436,17 +10439,17 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Paula Testad, Lars Johan Klockars</t>
+          <t>Paula Testad</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>117694225</v>
+        <v>117694483</v>
       </c>
       <c r="B85" t="n">
-        <v>90499</v>
+        <v>78480</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10459,21 +10462,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10486,10 +10489,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>512401</v>
+        <v>512384</v>
       </c>
       <c r="R85" t="n">
-        <v>6728182</v>
+        <v>6728360</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10559,10 +10562,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>117694009</v>
+        <v>117694225</v>
       </c>
       <c r="B86" t="n">
-        <v>57303</v>
+        <v>90499</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10575,31 +10578,26 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -10607,10 +10605,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>512372</v>
+        <v>512401</v>
       </c>
       <c r="R86" t="n">
-        <v>6728198</v>
+        <v>6728182</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10651,6 +10649,7 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -10679,10 +10678,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>117694297</v>
+        <v>117694025</v>
       </c>
       <c r="B87" t="n">
-        <v>57287</v>
+        <v>57303</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10695,16 +10694,16 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -10727,10 +10726,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>512398</v>
+        <v>512372</v>
       </c>
       <c r="R87" t="n">
-        <v>6728194</v>
+        <v>6728196</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10799,10 +10798,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>117694051</v>
+        <v>117694751</v>
       </c>
       <c r="B88" t="n">
-        <v>90499</v>
+        <v>78480</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10815,21 +10814,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10842,10 +10841,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>512389</v>
+        <v>512519</v>
       </c>
       <c r="R88" t="n">
-        <v>6728161</v>
+        <v>6728314</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10872,12 +10871,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10897,7 +10896,7 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>Gammal barrnaturskog</t>
+          <t>Äldre barrnaturskog</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -10908,17 +10907,17 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Paula Testad</t>
+          <t>Paula Testad, Lars Johan Klockars</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>117694483</v>
+        <v>117694080</v>
       </c>
       <c r="B89" t="n">
-        <v>78480</v>
+        <v>90499</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10931,21 +10930,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10958,10 +10957,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>512384</v>
+        <v>512390</v>
       </c>
       <c r="R89" t="n">
-        <v>6728360</v>
+        <v>6728159</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11031,10 +11030,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>117694278</v>
+        <v>117694385</v>
       </c>
       <c r="B90" t="n">
-        <v>57287</v>
+        <v>78480</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11047,31 +11046,26 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
@@ -11079,10 +11073,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>512399</v>
+        <v>512408</v>
       </c>
       <c r="R90" t="n">
-        <v>6728189</v>
+        <v>6728236</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11123,6 +11117,7 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -11151,10 +11146,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>117694385</v>
+        <v>117693944</v>
       </c>
       <c r="B91" t="n">
-        <v>78480</v>
+        <v>96791</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11163,30 +11158,31 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
@@ -11194,10 +11190,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>512408</v>
+        <v>512332</v>
       </c>
       <c r="R91" t="n">
-        <v>6728236</v>
+        <v>6728295</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11267,10 +11263,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>117694404</v>
+        <v>117694462</v>
       </c>
       <c r="B92" t="n">
-        <v>57303</v>
+        <v>57287</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11283,16 +11279,16 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -11315,10 +11311,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>512423</v>
+        <v>512404</v>
       </c>
       <c r="R92" t="n">
-        <v>6728253</v>
+        <v>6728323</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11387,7 +11383,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>117694161</v>
+        <v>117694331</v>
       </c>
       <c r="B93" t="n">
         <v>57287</v>
@@ -11435,10 +11431,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>512387</v>
+        <v>512401</v>
       </c>
       <c r="R93" t="n">
-        <v>6728162</v>
+        <v>6728197</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11507,10 +11503,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>117694331</v>
+        <v>117694378</v>
       </c>
       <c r="B94" t="n">
-        <v>57287</v>
+        <v>78480</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11523,31 +11519,26 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
@@ -11555,10 +11546,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>512401</v>
+        <v>512413</v>
       </c>
       <c r="R94" t="n">
-        <v>6728197</v>
+        <v>6728235</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11599,6 +11590,7 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -11627,10 +11619,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>117694025</v>
+        <v>117694195</v>
       </c>
       <c r="B95" t="n">
-        <v>57303</v>
+        <v>57287</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11643,16 +11635,16 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -11675,10 +11667,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>512372</v>
+        <v>512416</v>
       </c>
       <c r="R95" t="n">
-        <v>6728196</v>
+        <v>6728187</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11747,10 +11739,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>117694080</v>
+        <v>117694775</v>
       </c>
       <c r="B96" t="n">
-        <v>90499</v>
+        <v>57287</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11763,26 +11755,31 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
@@ -11790,10 +11787,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>512390</v>
+        <v>512523</v>
       </c>
       <c r="R96" t="n">
-        <v>6728159</v>
+        <v>6728303</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11820,12 +11817,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11834,7 +11831,6 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -11845,7 +11841,7 @@
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>Gammal barrnaturskog</t>
+          <t>Äldre barrnaturskog</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -11856,14 +11852,14 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Paula Testad</t>
+          <t>Paula Testad, Lars Johan Klockars</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>117694462</v>
+        <v>117694278</v>
       </c>
       <c r="B97" t="n">
         <v>57287</v>
@@ -11911,10 +11907,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>512404</v>
+        <v>512399</v>
       </c>
       <c r="R97" t="n">
-        <v>6728323</v>
+        <v>6728189</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11983,10 +11979,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>117694751</v>
+        <v>117694161</v>
       </c>
       <c r="B98" t="n">
-        <v>78480</v>
+        <v>57287</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11999,26 +11995,31 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
@@ -12026,10 +12027,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>512519</v>
+        <v>512387</v>
       </c>
       <c r="R98" t="n">
-        <v>6728314</v>
+        <v>6728162</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -12056,12 +12057,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12070,7 +12071,6 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -12081,7 +12081,7 @@
       </c>
       <c r="AI98" t="inlineStr">
         <is>
-          <t>Äldre barrnaturskog</t>
+          <t>Gammal barrnaturskog</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>
@@ -12092,17 +12092,17 @@
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Paula Testad, Lars Johan Klockars</t>
+          <t>Paula Testad</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>117694378</v>
+        <v>117694297</v>
       </c>
       <c r="B99" t="n">
-        <v>78480</v>
+        <v>57287</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -12115,26 +12115,31 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
@@ -12142,10 +12147,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>512413</v>
+        <v>512398</v>
       </c>
       <c r="R99" t="n">
-        <v>6728235</v>
+        <v>6728194</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12186,7 +12191,6 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -12215,10 +12219,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>117694775</v>
+        <v>117694051</v>
       </c>
       <c r="B100" t="n">
-        <v>57287</v>
+        <v>90499</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -12231,31 +12235,26 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
@@ -12263,10 +12262,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>512523</v>
+        <v>512389</v>
       </c>
       <c r="R100" t="n">
-        <v>6728303</v>
+        <v>6728161</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12293,12 +12292,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12307,6 +12306,7 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -12317,7 +12317,7 @@
       </c>
       <c r="AI100" t="inlineStr">
         <is>
-          <t>Äldre barrnaturskog</t>
+          <t>Gammal barrnaturskog</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr"/>
@@ -12328,7 +12328,7 @@
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Paula Testad, Lars Johan Klockars</t>
+          <t>Paula Testad</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -12455,10 +12455,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>117694195</v>
+        <v>117694009</v>
       </c>
       <c r="B102" t="n">
-        <v>57287</v>
+        <v>57303</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12471,16 +12471,16 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -12493,7 +12493,7 @@
       <c r="L102" t="inlineStr"/>
       <c r="M102" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N102" t="inlineStr"/>
@@ -12503,10 +12503,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>512416</v>
+        <v>512372</v>
       </c>
       <c r="R102" t="n">
-        <v>6728187</v>
+        <v>6728198</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12575,10 +12575,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>117693959</v>
+        <v>117694397</v>
       </c>
       <c r="B103" t="n">
-        <v>79597</v>
+        <v>78480</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12587,25 +12587,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12618,10 +12618,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>512288</v>
+        <v>512407</v>
       </c>
       <c r="R103" t="n">
-        <v>6728327</v>
+        <v>6728237</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>

--- a/artfynd/A 49115-2023 artfynd.xlsx
+++ b/artfynd/A 49115-2023 artfynd.xlsx
@@ -10090,10 +10090,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>117694724</v>
+        <v>117693944</v>
       </c>
       <c r="B82" t="n">
-        <v>57287</v>
+        <v>96793</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10102,35 +10102,31 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -10138,10 +10134,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>512478</v>
+        <v>512332</v>
       </c>
       <c r="R82" t="n">
-        <v>6728307</v>
+        <v>6728295</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10168,12 +10164,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10182,6 +10178,7 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -10192,7 +10189,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>Äldre barrnaturskog</t>
+          <t>Gammal barrnaturskog</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -10203,17 +10200,17 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Paula Testad, Lars Johan Klockars</t>
+          <t>Paula Testad</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>117693959</v>
+        <v>117694009</v>
       </c>
       <c r="B83" t="n">
-        <v>79597</v>
+        <v>57304</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10222,30 +10219,35 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6464</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -10253,10 +10255,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>512288</v>
+        <v>512372</v>
       </c>
       <c r="R83" t="n">
-        <v>6728327</v>
+        <v>6728198</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10297,7 +10299,6 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -10326,10 +10327,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>117694404</v>
+        <v>117694775</v>
       </c>
       <c r="B84" t="n">
-        <v>57303</v>
+        <v>57288</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10342,16 +10343,16 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -10364,7 +10365,7 @@
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N84" t="inlineStr"/>
@@ -10374,10 +10375,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>512423</v>
+        <v>512523</v>
       </c>
       <c r="R84" t="n">
-        <v>6728253</v>
+        <v>6728303</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10404,12 +10405,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10428,7 +10429,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>Gammal barrnaturskog</t>
+          <t>Äldre barrnaturskog</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -10439,17 +10440,17 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Paula Testad</t>
+          <t>Paula Testad, Lars Johan Klockars</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>117694483</v>
+        <v>117694080</v>
       </c>
       <c r="B85" t="n">
-        <v>78480</v>
+        <v>90501</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10462,21 +10463,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10489,10 +10490,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>512384</v>
+        <v>512390</v>
       </c>
       <c r="R85" t="n">
-        <v>6728360</v>
+        <v>6728159</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10562,10 +10563,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>117694225</v>
+        <v>117694751</v>
       </c>
       <c r="B86" t="n">
-        <v>90499</v>
+        <v>78482</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10578,21 +10579,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10605,10 +10606,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>512401</v>
+        <v>512519</v>
       </c>
       <c r="R86" t="n">
-        <v>6728182</v>
+        <v>6728314</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10635,12 +10636,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10660,7 +10661,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>Gammal barrnaturskog</t>
+          <t>Äldre barrnaturskog</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -10671,17 +10672,17 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Paula Testad</t>
+          <t>Paula Testad, Lars Johan Klockars</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>117694025</v>
+        <v>117694131</v>
       </c>
       <c r="B87" t="n">
-        <v>57303</v>
+        <v>57288</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10694,16 +10695,16 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -10726,10 +10727,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>512372</v>
+        <v>512390</v>
       </c>
       <c r="R87" t="n">
-        <v>6728196</v>
+        <v>6728159</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10798,10 +10799,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>117694751</v>
+        <v>117694462</v>
       </c>
       <c r="B88" t="n">
-        <v>78480</v>
+        <v>57288</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10814,26 +10815,31 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
@@ -10841,10 +10847,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>512519</v>
+        <v>512404</v>
       </c>
       <c r="R88" t="n">
-        <v>6728314</v>
+        <v>6728323</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10871,12 +10877,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10885,7 +10891,6 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -10896,7 +10901,7 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>Äldre barrnaturskog</t>
+          <t>Gammal barrnaturskog</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -10907,17 +10912,17 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Paula Testad, Lars Johan Klockars</t>
+          <t>Paula Testad</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>117694080</v>
+        <v>117694025</v>
       </c>
       <c r="B89" t="n">
-        <v>90499</v>
+        <v>57304</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10930,26 +10935,31 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -10957,10 +10967,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>512390</v>
+        <v>512372</v>
       </c>
       <c r="R89" t="n">
-        <v>6728159</v>
+        <v>6728196</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11001,7 +11011,6 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -11030,10 +11039,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>117694385</v>
+        <v>117694331</v>
       </c>
       <c r="B90" t="n">
-        <v>78480</v>
+        <v>57288</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11046,26 +11055,31 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
@@ -11073,10 +11087,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>512408</v>
+        <v>512401</v>
       </c>
       <c r="R90" t="n">
-        <v>6728236</v>
+        <v>6728197</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11117,7 +11131,6 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -11146,10 +11159,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>117693944</v>
+        <v>117693959</v>
       </c>
       <c r="B91" t="n">
-        <v>96791</v>
+        <v>79599</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11162,27 +11175,26 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>221945</v>
+        <v>6464</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
@@ -11190,10 +11202,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>512332</v>
+        <v>512288</v>
       </c>
       <c r="R91" t="n">
-        <v>6728295</v>
+        <v>6728327</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11263,10 +11275,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>117694462</v>
+        <v>117694297</v>
       </c>
       <c r="B92" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11311,10 +11323,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>512404</v>
+        <v>512398</v>
       </c>
       <c r="R92" t="n">
-        <v>6728323</v>
+        <v>6728194</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11383,10 +11395,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>117694331</v>
+        <v>117694051</v>
       </c>
       <c r="B93" t="n">
-        <v>57287</v>
+        <v>90501</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11399,31 +11411,26 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
@@ -11431,10 +11438,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>512401</v>
+        <v>512389</v>
       </c>
       <c r="R93" t="n">
-        <v>6728197</v>
+        <v>6728161</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11475,6 +11482,7 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -11503,10 +11511,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>117694378</v>
+        <v>117694195</v>
       </c>
       <c r="B94" t="n">
-        <v>78480</v>
+        <v>57288</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11519,26 +11527,31 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
@@ -11546,10 +11559,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>512413</v>
+        <v>512416</v>
       </c>
       <c r="R94" t="n">
-        <v>6728235</v>
+        <v>6728187</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11590,7 +11603,6 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -11619,10 +11631,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>117694195</v>
+        <v>117694724</v>
       </c>
       <c r="B95" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11667,10 +11679,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>512416</v>
+        <v>512478</v>
       </c>
       <c r="R95" t="n">
-        <v>6728187</v>
+        <v>6728307</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11697,12 +11709,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11721,7 +11733,7 @@
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>Gammal barrnaturskog</t>
+          <t>Äldre barrnaturskog</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -11732,17 +11744,17 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Paula Testad</t>
+          <t>Paula Testad, Lars Johan Klockars</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>117694775</v>
+        <v>117694397</v>
       </c>
       <c r="B96" t="n">
-        <v>57287</v>
+        <v>78482</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11755,31 +11767,26 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
@@ -11787,10 +11794,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>512523</v>
+        <v>512407</v>
       </c>
       <c r="R96" t="n">
-        <v>6728303</v>
+        <v>6728237</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11817,12 +11824,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11831,6 +11838,7 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -11841,7 +11849,7 @@
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>Äldre barrnaturskog</t>
+          <t>Gammal barrnaturskog</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -11852,17 +11860,17 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Paula Testad, Lars Johan Klockars</t>
+          <t>Paula Testad</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>117694278</v>
+        <v>117694378</v>
       </c>
       <c r="B97" t="n">
-        <v>57287</v>
+        <v>78482</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11875,31 +11883,26 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
@@ -11907,10 +11910,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>512399</v>
+        <v>512413</v>
       </c>
       <c r="R97" t="n">
-        <v>6728189</v>
+        <v>6728235</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11951,6 +11954,7 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -11979,10 +11983,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>117694161</v>
+        <v>117694278</v>
       </c>
       <c r="B98" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -12027,10 +12031,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>512387</v>
+        <v>512399</v>
       </c>
       <c r="R98" t="n">
-        <v>6728162</v>
+        <v>6728189</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -12099,10 +12103,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>117694297</v>
+        <v>117694225</v>
       </c>
       <c r="B99" t="n">
-        <v>57287</v>
+        <v>90501</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -12115,31 +12119,26 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
@@ -12147,10 +12146,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>512398</v>
+        <v>512401</v>
       </c>
       <c r="R99" t="n">
-        <v>6728194</v>
+        <v>6728182</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12191,6 +12190,7 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -12219,10 +12219,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>117694051</v>
+        <v>117694483</v>
       </c>
       <c r="B100" t="n">
-        <v>90499</v>
+        <v>78482</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -12235,21 +12235,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -12262,10 +12262,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>512389</v>
+        <v>512384</v>
       </c>
       <c r="R100" t="n">
-        <v>6728161</v>
+        <v>6728360</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12335,10 +12335,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>117694131</v>
+        <v>117694385</v>
       </c>
       <c r="B101" t="n">
-        <v>57287</v>
+        <v>78482</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12351,31 +12351,26 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
@@ -12383,10 +12378,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>512390</v>
+        <v>512408</v>
       </c>
       <c r="R101" t="n">
-        <v>6728159</v>
+        <v>6728236</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12427,6 +12422,7 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -12455,10 +12451,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>117694009</v>
+        <v>117694161</v>
       </c>
       <c r="B102" t="n">
-        <v>57303</v>
+        <v>57288</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12471,16 +12467,16 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -12493,7 +12489,7 @@
       <c r="L102" t="inlineStr"/>
       <c r="M102" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N102" t="inlineStr"/>
@@ -12503,10 +12499,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>512372</v>
+        <v>512387</v>
       </c>
       <c r="R102" t="n">
-        <v>6728198</v>
+        <v>6728162</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12575,10 +12571,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>117694397</v>
+        <v>117694404</v>
       </c>
       <c r="B103" t="n">
-        <v>78480</v>
+        <v>57304</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12591,26 +12587,31 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
@@ -12618,10 +12619,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>512407</v>
+        <v>512423</v>
       </c>
       <c r="R103" t="n">
-        <v>6728237</v>
+        <v>6728253</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12662,7 +12663,6 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -12694,7 +12694,7 @@
         <v>117694364</v>
       </c>
       <c r="B104" t="n">
-        <v>90464</v>
+        <v>90466</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>

--- a/artfynd/A 49115-2023 artfynd.xlsx
+++ b/artfynd/A 49115-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY104"/>
+  <dimension ref="A1:AY109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12805,6 +12805,626 @@
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>118059220</v>
+      </c>
+      <c r="B105" t="n">
+        <v>57304</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Solberga, Dlr</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>512497</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6728299</v>
+      </c>
+      <c r="S105" t="n">
+        <v>10</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Ål</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Medobservatör Göran Rönning.</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH105" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI105" t="inlineStr">
+        <is>
+          <t>Gammal barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Paula Testad</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Paula Testad</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>118057835</v>
+      </c>
+      <c r="B106" t="n">
+        <v>56500</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Solberga, Dlr</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>512574</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6728230</v>
+      </c>
+      <c r="S106" t="n">
+        <v>10</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Ål</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Sandbad med fjädrar från tupp och även spillning bredvid. Medobservatör tjäderexpert Göran Rönning.</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH106" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI106" t="inlineStr">
+        <is>
+          <t>Gammal barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Paula Testad</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Paula Testad</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>118060142</v>
+      </c>
+      <c r="B107" t="n">
+        <v>57304</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Solberga, Dlr</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>512424</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6728336</v>
+      </c>
+      <c r="S107" t="n">
+        <v>10</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Ål</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Medobservatör Göran Rönning.</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH107" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI107" t="inlineStr">
+        <is>
+          <t>Gammal barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Paula Testad</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Paula Testad</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>118059254</v>
+      </c>
+      <c r="B108" t="n">
+        <v>91774</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Solberga, Dlr</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>512419</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6728317</v>
+      </c>
+      <c r="S108" t="n">
+        <v>10</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Ål</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF108" t="inlineStr"/>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH108" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI108" t="inlineStr">
+        <is>
+          <t>Gammal barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Paula Testad</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Paula Testad</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>118057800</v>
+      </c>
+      <c r="B109" t="n">
+        <v>56500</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Solberga, Dlr</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>512582</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6728217</v>
+      </c>
+      <c r="S109" t="n">
+        <v>10</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Ål</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Äldre fjäder från tupp. Medobservatör tjäderexpert Göran Rönning.</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI109" t="inlineStr">
+        <is>
+          <t>Gammal barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Paula Testad</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Paula Testad</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49115-2023 artfynd.xlsx
+++ b/artfynd/A 49115-2023 artfynd.xlsx
@@ -13427,10 +13427,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>118329502</v>
+        <v>118325960</v>
       </c>
       <c r="B110" t="n">
-        <v>5166</v>
+        <v>97763</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -13443,32 +13443,31 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100526</v>
+        <v>219790</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
@@ -13476,10 +13475,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>512542</v>
+        <v>512362</v>
       </c>
       <c r="R110" t="n">
-        <v>6728174</v>
+        <v>6728316</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13506,12 +13505,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13531,7 +13530,7 @@
       </c>
       <c r="AI110" t="inlineStr">
         <is>
-          <t>Gammal barrnaturskog</t>
+          <t>Blött område i gammal barrnaturskog</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr"/>
@@ -13549,10 +13548,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>118329471</v>
+        <v>118329647</v>
       </c>
       <c r="B111" t="n">
-        <v>5186</v>
+        <v>97846</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -13561,36 +13560,39 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
       <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
@@ -13598,10 +13600,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>512541</v>
+        <v>512463</v>
       </c>
       <c r="R111" t="n">
-        <v>6728175</v>
+        <v>6728208</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13636,6 +13638,11 @@
           <t>2024-07-07</t>
         </is>
       </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Återfunnen. Nu med  några blomstänglar i gruppen plantor.</t>
+        </is>
+      </c>
       <c r="AD111" t="b">
         <v>0</v>
       </c>
@@ -13645,16 +13652,6 @@
       <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
-      </c>
-      <c r="AH111" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI111" t="inlineStr">
-        <is>
-          <t>Gammal barrnaturskog</t>
-        </is>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
@@ -13787,10 +13784,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>118329647</v>
+        <v>118329502</v>
       </c>
       <c r="B113" t="n">
-        <v>97846</v>
+        <v>5166</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13799,39 +13796,36 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+      <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
@@ -13839,10 +13833,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>512463</v>
+        <v>512542</v>
       </c>
       <c r="R113" t="n">
-        <v>6728208</v>
+        <v>6728174</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13877,11 +13871,6 @@
           <t>2024-07-07</t>
         </is>
       </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>Återfunnen. Nu med  några blomstänglar i gruppen plantor.</t>
-        </is>
-      </c>
       <c r="AD113" t="b">
         <v>0</v>
       </c>
@@ -13891,6 +13880,16 @@
       <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
+      </c>
+      <c r="AH113" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI113" t="inlineStr">
+        <is>
+          <t>Gammal barrnaturskog</t>
+        </is>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
@@ -13907,10 +13906,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>118325960</v>
+        <v>118329471</v>
       </c>
       <c r="B114" t="n">
-        <v>97763</v>
+        <v>5186</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -13923,31 +13922,32 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>219790</v>
+        <v>105930</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
@@ -13955,10 +13955,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>512362</v>
+        <v>512541</v>
       </c>
       <c r="R114" t="n">
-        <v>6728316</v>
+        <v>6728175</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13985,12 +13985,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2024-07-07</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2024-07-07</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -14010,7 +14010,7 @@
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>Blött område i gammal barrnaturskog</t>
+          <t>Gammal barrnaturskog</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -14028,10 +14028,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>118436167</v>
+        <v>118436002</v>
       </c>
       <c r="B115" t="n">
-        <v>56502</v>
+        <v>97846</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -14040,35 +14040,39 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
@@ -14076,10 +14080,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>512432</v>
+        <v>512427</v>
       </c>
       <c r="R115" t="n">
-        <v>6728362</v>
+        <v>6728245</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -14114,17 +14118,13 @@
           <t>2024-07-13</t>
         </is>
       </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>Fjäder från tjädertupp</t>
-        </is>
-      </c>
       <c r="AD115" t="b">
         <v>0</v>
       </c>
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -14153,10 +14153,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>118436002</v>
+        <v>118436167</v>
       </c>
       <c r="B116" t="n">
-        <v>97846</v>
+        <v>56502</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -14165,39 +14165,35 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
@@ -14205,10 +14201,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>512427</v>
+        <v>512432</v>
       </c>
       <c r="R116" t="n">
-        <v>6728245</v>
+        <v>6728362</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -14243,13 +14239,17 @@
           <t>2024-07-13</t>
         </is>
       </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Fjäder från tjädertupp</t>
+        </is>
+      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
       <c r="AE116" t="b">
         <v>0</v>
       </c>
-      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -14674,10 +14674,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>118744805</v>
+        <v>118754238</v>
       </c>
       <c r="B120" t="n">
-        <v>57181</v>
+        <v>56502</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -14686,25 +14686,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100001</v>
+        <v>100138</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -14716,7 +14716,7 @@
       <c r="L120" t="inlineStr"/>
       <c r="M120" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N120" t="inlineStr"/>
@@ -14726,13 +14726,13 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>512471</v>
+        <v>512567</v>
       </c>
       <c r="R120" t="n">
-        <v>6728344</v>
+        <v>6728209</v>
       </c>
       <c r="S120" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -14756,17 +14756,22 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>21:32</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Tjäder slagen av duvhök, förmodligen i vintras. (Fyndet säkerställts av Göran Rönning, expert på tjäder).</t>
+          <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>21:32</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14785,7 +14790,7 @@
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>Gammal barrnaturskog</t>
+          <t>Gammal barrnaturskog.</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -14803,10 +14808,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>118754238</v>
+        <v>118744805</v>
       </c>
       <c r="B121" t="n">
-        <v>56502</v>
+        <v>57181</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -14815,25 +14820,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100138</v>
+        <v>100001</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Accipiter gentilis</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -14845,7 +14850,7 @@
       <c r="L121" t="inlineStr"/>
       <c r="M121" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N121" t="inlineStr"/>
@@ -14855,13 +14860,13 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>512567</v>
+        <v>512471</v>
       </c>
       <c r="R121" t="n">
-        <v>6728209</v>
+        <v>6728344</v>
       </c>
       <c r="S121" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -14885,22 +14890,17 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
-        </is>
-      </c>
-      <c r="Z121" t="inlineStr">
-        <is>
-          <t>21:32</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
-        </is>
-      </c>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t>21:32</t>
+          <t>2024-04-13</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Tjäder slagen av duvhök, förmodligen i vintras. (Fyndet säkerställts av Göran Rönning, expert på tjäder).</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14919,7 +14919,7 @@
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>Gammal barrnaturskog.</t>
+          <t>Gammal barrnaturskog</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>

--- a/artfynd/A 49115-2023 artfynd.xlsx
+++ b/artfynd/A 49115-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY121"/>
+  <dimension ref="A1:AY120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13427,10 +13427,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>118325960</v>
+        <v>118329502</v>
       </c>
       <c r="B110" t="n">
-        <v>97763</v>
+        <v>5166</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -13443,31 +13443,32 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>219790</v>
+        <v>100526</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
@@ -13475,10 +13476,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>512362</v>
+        <v>512542</v>
       </c>
       <c r="R110" t="n">
-        <v>6728316</v>
+        <v>6728174</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13505,12 +13506,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2024-07-07</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2024-07-07</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13530,7 +13531,7 @@
       </c>
       <c r="AI110" t="inlineStr">
         <is>
-          <t>Blött område i gammal barrnaturskog</t>
+          <t>Gammal barrnaturskog</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr"/>
@@ -13548,10 +13549,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>118329647</v>
+        <v>118325960</v>
       </c>
       <c r="B111" t="n">
-        <v>97846</v>
+        <v>97763</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -13560,38 +13561,34 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+      <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr"/>
       <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
@@ -13600,10 +13597,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>512463</v>
+        <v>512362</v>
       </c>
       <c r="R111" t="n">
-        <v>6728208</v>
+        <v>6728316</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13630,17 +13627,12 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>Återfunnen. Nu med  några blomstänglar i gruppen plantor.</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13652,6 +13644,16 @@
       <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
+      </c>
+      <c r="AH111" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI111" t="inlineStr">
+        <is>
+          <t>Blött område i gammal barrnaturskog</t>
+        </is>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
@@ -13668,10 +13670,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>118329441</v>
+        <v>118329647</v>
       </c>
       <c r="B112" t="n">
-        <v>90504</v>
+        <v>97846</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -13680,30 +13682,39 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
       <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr"/>
       <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
@@ -13711,10 +13722,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>512536</v>
+        <v>512463</v>
       </c>
       <c r="R112" t="n">
-        <v>6728176</v>
+        <v>6728208</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13749,6 +13760,11 @@
           <t>2024-07-07</t>
         </is>
       </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Återfunnen. Nu med  några blomstänglar i gruppen plantor.</t>
+        </is>
+      </c>
       <c r="AD112" t="b">
         <v>0</v>
       </c>
@@ -13758,16 +13774,6 @@
       <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
-      </c>
-      <c r="AH112" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI112" t="inlineStr">
-        <is>
-          <t>Gammal barrnaturskog</t>
-        </is>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
@@ -13784,10 +13790,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>118329502</v>
+        <v>118329471</v>
       </c>
       <c r="B113" t="n">
-        <v>5166</v>
+        <v>5186</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13800,21 +13806,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -13833,10 +13839,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>512542</v>
+        <v>512541</v>
       </c>
       <c r="R113" t="n">
-        <v>6728174</v>
+        <v>6728175</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13906,10 +13912,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>118329471</v>
+        <v>118329441</v>
       </c>
       <c r="B114" t="n">
-        <v>5186</v>
+        <v>90504</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -13918,36 +13924,30 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
@@ -13955,10 +13955,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>512541</v>
+        <v>512536</v>
       </c>
       <c r="R114" t="n">
-        <v>6728175</v>
+        <v>6728176</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -14028,10 +14028,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>118436002</v>
+        <v>118436167</v>
       </c>
       <c r="B115" t="n">
-        <v>97846</v>
+        <v>56502</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -14040,39 +14040,35 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
@@ -14080,10 +14076,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>512427</v>
+        <v>512432</v>
       </c>
       <c r="R115" t="n">
-        <v>6728245</v>
+        <v>6728362</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -14118,13 +14114,17 @@
           <t>2024-07-13</t>
         </is>
       </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Fjäder från tjädertupp</t>
+        </is>
+      </c>
       <c r="AD115" t="b">
         <v>0</v>
       </c>
       <c r="AE115" t="b">
         <v>0</v>
       </c>
-      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -14153,10 +14153,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>118436167</v>
+        <v>118436002</v>
       </c>
       <c r="B116" t="n">
-        <v>56502</v>
+        <v>97846</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -14165,35 +14165,39 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
@@ -14201,10 +14205,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>512432</v>
+        <v>512427</v>
       </c>
       <c r="R116" t="n">
-        <v>6728362</v>
+        <v>6728245</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -14239,17 +14243,13 @@
           <t>2024-07-13</t>
         </is>
       </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Fjäder från tjädertupp</t>
-        </is>
-      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -14278,10 +14278,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>118596386</v>
+        <v>118683132</v>
       </c>
       <c r="B117" t="n">
-        <v>97846</v>
+        <v>56502</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -14290,39 +14290,47 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L117" t="inlineStr"/>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
@@ -14330,10 +14338,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>512426</v>
+        <v>512534</v>
       </c>
       <c r="R117" t="n">
-        <v>6728264</v>
+        <v>6728243</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -14360,12 +14368,27 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-25</t>
+        </is>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>19:26</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-25</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>19:26</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Uppflygande tjäderhöna.</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -14374,19 +14397,8 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
-      </c>
-      <c r="AH117" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI117" t="inlineStr">
-        <is>
-          <t>Gammal barrnaturskog</t>
-        </is>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
@@ -14396,14 +14408,14 @@
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Paula Testad</t>
+          <t>Paula Testad, Lars Johan Klockars</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>118683132</v>
+        <v>118687807</v>
       </c>
       <c r="B118" t="n">
         <v>56502</v>
@@ -14441,16 +14453,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L118" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
       <c r="M118" t="inlineStr">
         <is>
           <t>förbiflygande</t>
@@ -14463,10 +14467,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>512534</v>
+        <v>512471</v>
       </c>
       <c r="R118" t="n">
-        <v>6728243</v>
+        <v>6728272</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -14498,7 +14502,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>19:26</t>
+          <t>21:47</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -14508,12 +14512,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>19:26</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Uppflygande tjäderhöna.</t>
+          <t>21:47</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -14524,6 +14523,16 @@
       </c>
       <c r="AG118" t="b">
         <v>0</v>
+      </c>
+      <c r="AH118" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI118" t="inlineStr">
+        <is>
+          <t>Gammal barrnaturskog</t>
+        </is>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
@@ -14533,14 +14542,14 @@
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Paula Testad, Lars Johan Klockars</t>
+          <t>Lars Johan Klockars, Paula Testad</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>118687807</v>
+        <v>118754238</v>
       </c>
       <c r="B119" t="n">
         <v>56502</v>
@@ -14592,10 +14601,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>512471</v>
+        <v>512567</v>
       </c>
       <c r="R119" t="n">
-        <v>6728272</v>
+        <v>6728209</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -14622,22 +14631,22 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>21:47</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>21:47</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14656,7 +14665,7 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>Gammal barrnaturskog</t>
+          <t>Gammal barrnaturskog.</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -14674,10 +14683,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>118754238</v>
+        <v>118744805</v>
       </c>
       <c r="B120" t="n">
-        <v>56502</v>
+        <v>57181</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -14686,25 +14695,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100138</v>
+        <v>100001</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Accipiter gentilis</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -14716,7 +14725,7 @@
       <c r="L120" t="inlineStr"/>
       <c r="M120" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N120" t="inlineStr"/>
@@ -14726,13 +14735,13 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>512567</v>
+        <v>512471</v>
       </c>
       <c r="R120" t="n">
-        <v>6728209</v>
+        <v>6728344</v>
       </c>
       <c r="S120" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -14756,22 +14765,17 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
-        </is>
-      </c>
-      <c r="Z120" t="inlineStr">
-        <is>
-          <t>21:32</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
-        </is>
-      </c>
-      <c r="AB120" t="inlineStr">
-        <is>
-          <t>21:32</t>
+          <t>2024-04-13</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Tjäder slagen av duvhök, förmodligen i vintras. (Fyndet säkerställts av Göran Rönning, expert på tjäder).</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14790,7 +14794,7 @@
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>Gammal barrnaturskog.</t>
+          <t>Gammal barrnaturskog</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -14805,135 +14809,6 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" t="n">
-        <v>118744805</v>
-      </c>
-      <c r="B121" t="n">
-        <v>57181</v>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E121" t="n">
-        <v>100001</v>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>Duvhök</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>Accipiter gentilis</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N121" t="inlineStr"/>
-      <c r="P121" t="inlineStr">
-        <is>
-          <t>Solberga, Dlr</t>
-        </is>
-      </c>
-      <c r="Q121" t="n">
-        <v>512471</v>
-      </c>
-      <c r="R121" t="n">
-        <v>6728344</v>
-      </c>
-      <c r="S121" t="n">
-        <v>5</v>
-      </c>
-      <c r="T121" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U121" t="inlineStr">
-        <is>
-          <t>Leksand</t>
-        </is>
-      </c>
-      <c r="V121" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W121" t="inlineStr">
-        <is>
-          <t>Ål</t>
-        </is>
-      </c>
-      <c r="Y121" t="inlineStr">
-        <is>
-          <t>2024-04-13</t>
-        </is>
-      </c>
-      <c r="AA121" t="inlineStr">
-        <is>
-          <t>2024-04-13</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Tjäder slagen av duvhök, förmodligen i vintras. (Fyndet säkerställts av Göran Rönning, expert på tjäder).</t>
-        </is>
-      </c>
-      <c r="AD121" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE121" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG121" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH121" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI121" t="inlineStr">
-        <is>
-          <t>Gammal barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AT121" t="inlineStr"/>
-      <c r="AW121" t="inlineStr">
-        <is>
-          <t>Paula Testad</t>
-        </is>
-      </c>
-      <c r="AX121" t="inlineStr">
-        <is>
-          <t>Paula Testad, Lars Johan Klockars</t>
-        </is>
-      </c>
-      <c r="AY121" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49115-2023 artfynd.xlsx
+++ b/artfynd/A 49115-2023 artfynd.xlsx
@@ -13549,10 +13549,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>118325960</v>
+        <v>118329441</v>
       </c>
       <c r="B111" t="n">
-        <v>97763</v>
+        <v>90511</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -13561,35 +13561,30 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>219790</v>
+        <v>1202</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
       <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
@@ -13597,10 +13592,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>512362</v>
+        <v>512536</v>
       </c>
       <c r="R111" t="n">
-        <v>6728316</v>
+        <v>6728176</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13627,12 +13622,12 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2024-07-07</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2024-07-07</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13652,7 +13647,7 @@
       </c>
       <c r="AI111" t="inlineStr">
         <is>
-          <t>Blött område i gammal barrnaturskog</t>
+          <t>Gammal barrnaturskog</t>
         </is>
       </c>
       <c r="AT111" t="inlineStr"/>
@@ -13670,10 +13665,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>118329647</v>
+        <v>118329471</v>
       </c>
       <c r="B112" t="n">
-        <v>97846</v>
+        <v>5186</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -13682,39 +13677,36 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+      <c r="K112" t="inlineStr"/>
       <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
@@ -13722,10 +13714,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>512463</v>
+        <v>512541</v>
       </c>
       <c r="R112" t="n">
-        <v>6728208</v>
+        <v>6728175</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13760,11 +13752,6 @@
           <t>2024-07-07</t>
         </is>
       </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>Återfunnen. Nu med  några blomstänglar i gruppen plantor.</t>
-        </is>
-      </c>
       <c r="AD112" t="b">
         <v>0</v>
       </c>
@@ -13774,6 +13761,16 @@
       <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
+      </c>
+      <c r="AH112" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI112" t="inlineStr">
+        <is>
+          <t>Gammal barrnaturskog</t>
+        </is>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
@@ -13790,10 +13787,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>118329471</v>
+        <v>118325960</v>
       </c>
       <c r="B113" t="n">
-        <v>5186</v>
+        <v>97770</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13806,32 +13803,31 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>105930</v>
+        <v>219790</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
@@ -13839,10 +13835,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>512541</v>
+        <v>512362</v>
       </c>
       <c r="R113" t="n">
-        <v>6728175</v>
+        <v>6728316</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13869,12 +13865,12 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13894,7 +13890,7 @@
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>Gammal barrnaturskog</t>
+          <t>Blött område i gammal barrnaturskog</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -13912,10 +13908,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>118329441</v>
+        <v>118329647</v>
       </c>
       <c r="B114" t="n">
-        <v>90504</v>
+        <v>97853</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -13924,30 +13920,39 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
       <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr"/>
       <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
@@ -13955,10 +13960,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>512536</v>
+        <v>512463</v>
       </c>
       <c r="R114" t="n">
-        <v>6728176</v>
+        <v>6728208</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13993,6 +13998,11 @@
           <t>2024-07-07</t>
         </is>
       </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Återfunnen. Nu med  några blomstänglar i gruppen plantor.</t>
+        </is>
+      </c>
       <c r="AD114" t="b">
         <v>0</v>
       </c>
@@ -14002,16 +14012,6 @@
       <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
-      </c>
-      <c r="AH114" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI114" t="inlineStr">
-        <is>
-          <t>Gammal barrnaturskog</t>
-        </is>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
@@ -14156,7 +14156,7 @@
         <v>118436002</v>
       </c>
       <c r="B116" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -14278,7 +14278,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>118683132</v>
+        <v>118687807</v>
       </c>
       <c r="B117" t="n">
         <v>56502</v>
@@ -14316,16 +14316,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L117" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr">
         <is>
           <t>förbiflygande</t>
@@ -14338,10 +14330,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>512534</v>
+        <v>512471</v>
       </c>
       <c r="R117" t="n">
-        <v>6728243</v>
+        <v>6728272</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -14373,7 +14365,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>19:26</t>
+          <t>21:47</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -14383,12 +14375,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>19:26</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Uppflygande tjäderhöna.</t>
+          <t>21:47</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -14399,6 +14386,16 @@
       </c>
       <c r="AG117" t="b">
         <v>0</v>
+      </c>
+      <c r="AH117" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI117" t="inlineStr">
+        <is>
+          <t>Gammal barrnaturskog</t>
+        </is>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
@@ -14415,7 +14412,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>118687807</v>
+        <v>118683132</v>
       </c>
       <c r="B118" t="n">
         <v>56502</v>
@@ -14453,8 +14450,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M118" t="inlineStr">
         <is>
           <t>förbiflygande</t>
@@ -14467,10 +14472,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>512471</v>
+        <v>512534</v>
       </c>
       <c r="R118" t="n">
-        <v>6728272</v>
+        <v>6728243</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -14502,7 +14507,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>21:47</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -14512,7 +14517,12 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>21:47</t>
+          <t>19:26</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Uppflygande tjäderhöna.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -14523,16 +14533,6 @@
       </c>
       <c r="AG118" t="b">
         <v>0</v>
-      </c>
-      <c r="AH118" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI118" t="inlineStr">
-        <is>
-          <t>Gammal barrnaturskog</t>
-        </is>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
@@ -14542,17 +14542,17 @@
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Lars Johan Klockars, Paula Testad</t>
+          <t>Paula Testad, Lars Johan Klockars</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>118754238</v>
+        <v>118744805</v>
       </c>
       <c r="B119" t="n">
-        <v>56502</v>
+        <v>57181</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -14561,25 +14561,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100138</v>
+        <v>100001</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Accipiter gentilis</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -14591,7 +14591,7 @@
       <c r="L119" t="inlineStr"/>
       <c r="M119" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N119" t="inlineStr"/>
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>512567</v>
+        <v>512471</v>
       </c>
       <c r="R119" t="n">
-        <v>6728209</v>
+        <v>6728344</v>
       </c>
       <c r="S119" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -14631,22 +14631,17 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
-        </is>
-      </c>
-      <c r="Z119" t="inlineStr">
-        <is>
-          <t>21:32</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
-        </is>
-      </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>21:32</t>
+          <t>2024-04-13</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Tjäder slagen av duvhök, förmodligen i vintras. (Fyndet säkerställts av Göran Rönning, expert på tjäder).</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14665,7 +14660,7 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>Gammal barrnaturskog.</t>
+          <t>Gammal barrnaturskog</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -14683,10 +14678,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>118744805</v>
+        <v>118754238</v>
       </c>
       <c r="B120" t="n">
-        <v>57181</v>
+        <v>56502</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -14695,25 +14690,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100001</v>
+        <v>100138</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -14725,7 +14720,7 @@
       <c r="L120" t="inlineStr"/>
       <c r="M120" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N120" t="inlineStr"/>
@@ -14735,13 +14730,13 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>512471</v>
+        <v>512567</v>
       </c>
       <c r="R120" t="n">
-        <v>6728344</v>
+        <v>6728209</v>
       </c>
       <c r="S120" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -14765,17 +14760,22 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>21:32</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Tjäder slagen av duvhök, förmodligen i vintras. (Fyndet säkerställts av Göran Rönning, expert på tjäder).</t>
+          <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>21:32</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14794,7 +14794,7 @@
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>Gammal barrnaturskog</t>
+          <t>Gammal barrnaturskog.</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>

--- a/artfynd/A 49115-2023 artfynd.xlsx
+++ b/artfynd/A 49115-2023 artfynd.xlsx
@@ -14671,7 +14671,7 @@
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Paula Testad, Lars Johan Klockars</t>
+          <t>Lars Johan Klockars, Paula Testad</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>

--- a/artfynd/A 49115-2023 artfynd.xlsx
+++ b/artfynd/A 49115-2023 artfynd.xlsx
@@ -15182,10 +15182,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>119514271</v>
+        <v>119515780</v>
       </c>
       <c r="B124" t="n">
-        <v>97907</v>
+        <v>57679</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -15194,39 +15194,39 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
@@ -15234,10 +15234,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>512424</v>
+        <v>512427</v>
       </c>
       <c r="R124" t="n">
-        <v>6728191</v>
+        <v>6728245</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -15264,12 +15264,22 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -15278,7 +15288,6 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -15307,10 +15316,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>119515721</v>
+        <v>119515148</v>
       </c>
       <c r="B125" t="n">
-        <v>91884</v>
+        <v>97907</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -15319,38 +15328,39 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K125" t="inlineStr"/>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr"/>
       <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
@@ -15358,10 +15368,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>512529</v>
+        <v>512430</v>
       </c>
       <c r="R125" t="n">
-        <v>6728275</v>
+        <v>6728267</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -15388,12 +15398,12 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -15431,7 +15441,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>119513401</v>
+        <v>119514271</v>
       </c>
       <c r="B126" t="n">
         <v>97907</v>
@@ -15464,7 +15474,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I126" t="inlineStr"/>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr">
         <is>
@@ -15479,10 +15493,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>512417</v>
+        <v>512424</v>
       </c>
       <c r="R126" t="n">
-        <v>6728312</v>
+        <v>6728191</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -15509,17 +15523,12 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>Rikligt med plantor.</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -15557,10 +15566,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>119515148</v>
+        <v>119515876</v>
       </c>
       <c r="B127" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -15569,39 +15578,30 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
       <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
@@ -15609,10 +15609,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>512430</v>
+        <v>512446</v>
       </c>
       <c r="R127" t="n">
-        <v>6728267</v>
+        <v>6728153</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -15639,12 +15639,12 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -15665,6 +15665,21 @@
       <c r="AI127" t="inlineStr">
         <is>
           <t>Gammal barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AJ127" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK127" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO127" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT127" t="inlineStr"/>
@@ -15682,7 +15697,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>119513652</v>
+        <v>119513955</v>
       </c>
       <c r="B128" t="n">
         <v>97907</v>
@@ -15715,9 +15730,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr"/>
       <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
@@ -15726,10 +15753,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>512407</v>
+        <v>512557</v>
       </c>
       <c r="R128" t="n">
-        <v>6728290</v>
+        <v>6728300</v>
       </c>
       <c r="S128" t="n">
         <v>5</v>
@@ -15756,17 +15783,12 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>Rikligt med plantor, en del blommande.</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15786,7 +15808,7 @@
       </c>
       <c r="AI128" t="inlineStr">
         <is>
-          <t>Gammal barrnaturskog.</t>
+          <t>Gammal barrnaturskog</t>
         </is>
       </c>
       <c r="AT128" t="inlineStr"/>
@@ -15804,10 +15826,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>119512756</v>
+        <v>119515762</v>
       </c>
       <c r="B129" t="n">
-        <v>97907</v>
+        <v>57463</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -15816,25 +15838,25 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -15842,13 +15864,13 @@
           <t>2</t>
         </is>
       </c>
-      <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
@@ -15856,10 +15878,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>512431</v>
+        <v>512427</v>
       </c>
       <c r="R129" t="n">
-        <v>6728318</v>
+        <v>6728245</v>
       </c>
       <c r="S129" t="n">
         <v>5</v>
@@ -15886,12 +15908,27 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>Talltitor har hörts i denna skog många gånger under flera månader, så har därför säkerligen revir i skogen.</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -15900,7 +15937,6 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
-      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
@@ -15922,17 +15958,17 @@
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Paula Testad</t>
+          <t>Paula Testad, Lars Johan Klockars</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>119515086</v>
+        <v>119515844</v>
       </c>
       <c r="B130" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -15941,39 +15977,30 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr"/>
-      <c r="L130" t="inlineStr"/>
       <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
@@ -15981,10 +16008,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>512428</v>
+        <v>512440</v>
       </c>
       <c r="R130" t="n">
-        <v>6728248</v>
+        <v>6728221</v>
       </c>
       <c r="S130" t="n">
         <v>5</v>
@@ -16011,12 +16038,12 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -16054,10 +16081,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>119515876</v>
+        <v>119512756</v>
       </c>
       <c r="B131" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -16066,30 +16093,39 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr"/>
       <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
@@ -16097,10 +16133,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>512446</v>
+        <v>512431</v>
       </c>
       <c r="R131" t="n">
-        <v>6728153</v>
+        <v>6728318</v>
       </c>
       <c r="S131" t="n">
         <v>5</v>
@@ -16127,12 +16163,12 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -16155,21 +16191,6 @@
           <t>Gammal barrnaturskog</t>
         </is>
       </c>
-      <c r="AJ131" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK131" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO131" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
@@ -16178,17 +16199,17 @@
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Paula Testad, Lars Johan Klockars</t>
+          <t>Paula Testad</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>119514745</v>
+        <v>119515857</v>
       </c>
       <c r="B132" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -16197,39 +16218,30 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
       <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
@@ -16237,10 +16249,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>512427</v>
+        <v>512447</v>
       </c>
       <c r="R132" t="n">
-        <v>6728256</v>
+        <v>6728164</v>
       </c>
       <c r="S132" t="n">
         <v>5</v>
@@ -16267,12 +16279,12 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -16293,6 +16305,21 @@
       <c r="AI132" t="inlineStr">
         <is>
           <t>Gammal barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AJ132" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK132" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO132" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT132" t="inlineStr"/>
@@ -16310,10 +16337,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>119515857</v>
+        <v>119515086</v>
       </c>
       <c r="B133" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -16322,30 +16349,39 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
       <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
@@ -16353,10 +16389,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>512447</v>
+        <v>512428</v>
       </c>
       <c r="R133" t="n">
-        <v>6728164</v>
+        <v>6728248</v>
       </c>
       <c r="S133" t="n">
         <v>5</v>
@@ -16383,12 +16419,12 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -16409,21 +16445,6 @@
       <c r="AI133" t="inlineStr">
         <is>
           <t>Gammal barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AJ133" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK133" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO133" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT133" t="inlineStr"/>
@@ -16441,7 +16462,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>119513955</v>
+        <v>119512515</v>
       </c>
       <c r="B134" t="n">
         <v>97907</v>
@@ -16476,19 +16497,11 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
       <c r="L134" t="inlineStr"/>
       <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
@@ -16497,10 +16510,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>512557</v>
+        <v>512429</v>
       </c>
       <c r="R134" t="n">
-        <v>6728300</v>
+        <v>6728264</v>
       </c>
       <c r="S134" t="n">
         <v>5</v>
@@ -16527,12 +16540,12 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -16563,17 +16576,17 @@
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Paula Testad, Lars Johan Klockars</t>
+          <t>Paula Testad</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>119515844</v>
+        <v>119514745</v>
       </c>
       <c r="B135" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -16582,30 +16595,39 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
       <c r="J135" t="inlineStr"/>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr"/>
       <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
@@ -16613,10 +16635,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>512440</v>
+        <v>512427</v>
       </c>
       <c r="R135" t="n">
-        <v>6728221</v>
+        <v>6728256</v>
       </c>
       <c r="S135" t="n">
         <v>5</v>
@@ -16643,12 +16665,12 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -16686,10 +16708,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>119515780</v>
+        <v>119513652</v>
       </c>
       <c r="B136" t="n">
-        <v>57679</v>
+        <v>97907</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -16698,39 +16720,31 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr"/>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
@@ -16738,10 +16752,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>512427</v>
+        <v>512407</v>
       </c>
       <c r="R136" t="n">
-        <v>6728245</v>
+        <v>6728290</v>
       </c>
       <c r="S136" t="n">
         <v>5</v>
@@ -16768,22 +16782,17 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
-        </is>
-      </c>
-      <c r="Z136" t="inlineStr">
-        <is>
-          <t>18:00</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
-        </is>
-      </c>
-      <c r="AB136" t="inlineStr">
-        <is>
-          <t>18:00</t>
+          <t>2024-07-25</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>Rikligt med plantor, en del blommande.</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -16792,6 +16801,7 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
+      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
@@ -16802,7 +16812,7 @@
       </c>
       <c r="AI136" t="inlineStr">
         <is>
-          <t>Gammal barrnaturskog</t>
+          <t>Gammal barrnaturskog.</t>
         </is>
       </c>
       <c r="AT136" t="inlineStr"/>
@@ -16820,10 +16830,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>119512515</v>
+        <v>119515721</v>
       </c>
       <c r="B137" t="n">
-        <v>97907</v>
+        <v>91884</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -16832,35 +16842,38 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="J137" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K137" t="inlineStr"/>
-      <c r="L137" t="inlineStr"/>
       <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
@@ -16868,10 +16881,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>512429</v>
+        <v>512529</v>
       </c>
       <c r="R137" t="n">
-        <v>6728264</v>
+        <v>6728275</v>
       </c>
       <c r="S137" t="n">
         <v>5</v>
@@ -16898,12 +16911,12 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -16934,7 +16947,7 @@
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Paula Testad</t>
+          <t>Paula Testad, Lars Johan Klockars</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
@@ -17072,7 +17085,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>119512149</v>
+        <v>119513401</v>
       </c>
       <c r="B139" t="n">
         <v>97907</v>
@@ -17105,17 +17118,13 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr"/>
       <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
@@ -17124,10 +17133,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>512444</v>
+        <v>512417</v>
       </c>
       <c r="R139" t="n">
-        <v>6728246</v>
+        <v>6728312</v>
       </c>
       <c r="S139" t="n">
         <v>5</v>
@@ -17154,12 +17163,17 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2024-07-13</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2024-07-13</t>
+          <t>2024-07-25</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>Rikligt med plantor.</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -17190,17 +17204,17 @@
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Paula Testad</t>
+          <t>Paula Testad, Lars Johan Klockars</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>119515762</v>
+        <v>119512149</v>
       </c>
       <c r="B140" t="n">
-        <v>57463</v>
+        <v>97907</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -17209,39 +17223,39 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr"/>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
@@ -17249,10 +17263,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>512427</v>
+        <v>512444</v>
       </c>
       <c r="R140" t="n">
-        <v>6728245</v>
+        <v>6728246</v>
       </c>
       <c r="S140" t="n">
         <v>5</v>
@@ -17279,27 +17293,12 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
-        </is>
-      </c>
-      <c r="Z140" t="inlineStr">
-        <is>
-          <t>18:00</t>
+          <t>2024-07-13</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
-        </is>
-      </c>
-      <c r="AB140" t="inlineStr">
-        <is>
-          <t>18:10</t>
-        </is>
-      </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>Talltitor har hörts i denna skog många gånger under flera månader, så har därför säkerligen revir i skogen.</t>
+          <t>2024-07-13</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -17308,6 +17307,7 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
+      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
@@ -17329,17 +17329,17 @@
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Paula Testad, Lars Johan Klockars</t>
+          <t>Paula Testad</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>119870076</v>
+        <v>119863311</v>
       </c>
       <c r="B141" t="n">
-        <v>91840</v>
+        <v>57326</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -17348,50 +17348,50 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Solberga, Solberga, Dlr</t>
+          <t>Solberga , Solberga , Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>512397</v>
+        <v>512452</v>
       </c>
       <c r="R141" t="n">
-        <v>6728345</v>
+        <v>6728231</v>
       </c>
       <c r="S141" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -17420,7 +17420,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -17430,7 +17430,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -17462,10 +17462,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>119869590</v>
+        <v>119863337</v>
       </c>
       <c r="B142" t="n">
-        <v>91840</v>
+        <v>57463</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -17474,35 +17474,35 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J142" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
@@ -17511,10 +17511,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>512413</v>
+        <v>512515</v>
       </c>
       <c r="R142" t="n">
-        <v>6728315</v>
+        <v>6728351</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -17544,9 +17544,19 @@
           <t>2024-09-20</t>
         </is>
       </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
       <c r="AA142" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -17578,10 +17588,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>119863337</v>
+        <v>119870076</v>
       </c>
       <c r="B143" t="n">
-        <v>57463</v>
+        <v>91840</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -17590,35 +17600,35 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P143" t="inlineStr">
@@ -17627,13 +17637,13 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>512515</v>
+        <v>512397</v>
       </c>
       <c r="R143" t="n">
-        <v>6728351</v>
+        <v>6728345</v>
       </c>
       <c r="S143" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -17662,7 +17672,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -17672,7 +17682,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -17704,10 +17714,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>119864877</v>
+        <v>119864797</v>
       </c>
       <c r="B144" t="n">
-        <v>91494</v>
+        <v>90527</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -17720,33 +17730,24 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>4769</v>
+        <v>5447</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Solberga, Solberga, Dlr</t>
@@ -17803,6 +17804,21 @@
       <c r="AH144" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ144" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK144" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO144" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT144" t="inlineStr"/>
@@ -17820,10 +17836,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>119863311</v>
+        <v>119869590</v>
       </c>
       <c r="B145" t="n">
-        <v>57326</v>
+        <v>91840</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -17832,47 +17848,47 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Solberga , Solberga , Dlr</t>
+          <t>Solberga, Solberga, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>512452</v>
+        <v>512413</v>
       </c>
       <c r="R145" t="n">
-        <v>6728231</v>
+        <v>6728315</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -17902,19 +17918,9 @@
           <t>2024-09-20</t>
         </is>
       </c>
-      <c r="Z145" t="inlineStr">
-        <is>
-          <t>10:29</t>
-        </is>
-      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AB145" t="inlineStr">
-        <is>
-          <t>10:29</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -17946,10 +17952,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>119864797</v>
+        <v>119869333</v>
       </c>
       <c r="B146" t="n">
-        <v>90527</v>
+        <v>91494</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -17962,34 +17968,43 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>5447</v>
+        <v>4769</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr"/>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P146" t="inlineStr">
         <is>
           <t>Solberga, Solberga, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>512410</v>
+        <v>512422</v>
       </c>
       <c r="R146" t="n">
-        <v>6728168</v>
+        <v>6728244</v>
       </c>
       <c r="S146" t="n">
         <v>5</v>
@@ -18036,21 +18051,6 @@
       <c r="AH146" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ146" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK146" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO146" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT146" t="inlineStr"/>
@@ -18068,7 +18068,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>119869333</v>
+        <v>119864877</v>
       </c>
       <c r="B147" t="n">
         <v>91494</v>
@@ -18117,10 +18117,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>512422</v>
+        <v>512410</v>
       </c>
       <c r="R147" t="n">
-        <v>6728244</v>
+        <v>6728168</v>
       </c>
       <c r="S147" t="n">
         <v>5</v>

--- a/artfynd/A 49115-2023 artfynd.xlsx
+++ b/artfynd/A 49115-2023 artfynd.xlsx
@@ -17336,10 +17336,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>119863311</v>
+        <v>119870076</v>
       </c>
       <c r="B141" t="n">
-        <v>57326</v>
+        <v>91840</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -17348,50 +17348,50 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Solberga , Solberga , Dlr</t>
+          <t>Solberga, Solberga, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>512452</v>
+        <v>512397</v>
       </c>
       <c r="R141" t="n">
-        <v>6728231</v>
+        <v>6728345</v>
       </c>
       <c r="S141" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -17420,7 +17420,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -17430,7 +17430,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -17462,10 +17462,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>119863337</v>
+        <v>119864877</v>
       </c>
       <c r="B142" t="n">
-        <v>57463</v>
+        <v>91494</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -17474,25 +17474,25 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>103021</v>
+        <v>4769</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -17500,9 +17500,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
@@ -17511,13 +17511,13 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>512515</v>
+        <v>512410</v>
       </c>
       <c r="R142" t="n">
-        <v>6728351</v>
+        <v>6728168</v>
       </c>
       <c r="S142" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -17544,19 +17544,9 @@
           <t>2024-09-20</t>
         </is>
       </c>
-      <c r="Z142" t="inlineStr">
-        <is>
-          <t>10:32</t>
-        </is>
-      </c>
       <c r="AA142" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AB142" t="inlineStr">
-        <is>
-          <t>10:32</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -17588,7 +17578,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>119870076</v>
+        <v>119869590</v>
       </c>
       <c r="B143" t="n">
         <v>91840</v>
@@ -17623,7 +17613,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -17637,13 +17627,13 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>512397</v>
+        <v>512413</v>
       </c>
       <c r="R143" t="n">
-        <v>6728345</v>
+        <v>6728315</v>
       </c>
       <c r="S143" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -17670,19 +17660,9 @@
           <t>2024-09-20</t>
         </is>
       </c>
-      <c r="Z143" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AB143" t="inlineStr">
-        <is>
-          <t>13:21</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -17836,10 +17816,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>119869590</v>
+        <v>119863311</v>
       </c>
       <c r="B145" t="n">
-        <v>91840</v>
+        <v>57326</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -17848,47 +17828,47 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Solberga, Solberga, Dlr</t>
+          <t>Solberga , Solberga , Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>512413</v>
+        <v>512452</v>
       </c>
       <c r="R145" t="n">
-        <v>6728315</v>
+        <v>6728231</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -17918,9 +17898,19 @@
           <t>2024-09-20</t>
         </is>
       </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AB145" t="inlineStr">
+        <is>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -18068,10 +18058,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>119864877</v>
+        <v>119863337</v>
       </c>
       <c r="B147" t="n">
-        <v>91494</v>
+        <v>57463</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -18080,25 +18070,25 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>4769</v>
+        <v>103021</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -18106,9 +18096,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J147" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P147" t="inlineStr">
@@ -18117,13 +18107,13 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>512410</v>
+        <v>512515</v>
       </c>
       <c r="R147" t="n">
-        <v>6728168</v>
+        <v>6728351</v>
       </c>
       <c r="S147" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -18150,9 +18140,19 @@
           <t>2024-09-20</t>
         </is>
       </c>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
       <c r="AA147" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AB147" t="inlineStr">
+        <is>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD147" t="b">

--- a/artfynd/A 49115-2023 artfynd.xlsx
+++ b/artfynd/A 49115-2023 artfynd.xlsx
@@ -17336,10 +17336,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>119870076</v>
+        <v>119863337</v>
       </c>
       <c r="B141" t="n">
-        <v>91840</v>
+        <v>57463</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -17348,35 +17348,35 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
@@ -17385,13 +17385,13 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>512397</v>
+        <v>512515</v>
       </c>
       <c r="R141" t="n">
-        <v>6728345</v>
+        <v>6728351</v>
       </c>
       <c r="S141" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -17420,7 +17420,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -17430,7 +17430,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -17462,10 +17462,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>119864877</v>
+        <v>119870076</v>
       </c>
       <c r="B142" t="n">
-        <v>91494</v>
+        <v>91840</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -17478,26 +17478,26 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>4769</v>
+        <v>4364</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -17511,10 +17511,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>512410</v>
+        <v>512397</v>
       </c>
       <c r="R142" t="n">
-        <v>6728168</v>
+        <v>6728345</v>
       </c>
       <c r="S142" t="n">
         <v>5</v>
@@ -17544,9 +17544,19 @@
           <t>2024-09-20</t>
         </is>
       </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
       <c r="AA142" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -17578,10 +17588,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>119869590</v>
+        <v>119863311</v>
       </c>
       <c r="B143" t="n">
-        <v>91840</v>
+        <v>57326</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -17590,47 +17600,47 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Solberga, Solberga, Dlr</t>
+          <t>Solberga , Solberga , Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>512413</v>
+        <v>512452</v>
       </c>
       <c r="R143" t="n">
-        <v>6728315</v>
+        <v>6728231</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -17660,9 +17670,19 @@
           <t>2024-09-20</t>
         </is>
       </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -17816,10 +17836,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>119863311</v>
+        <v>119864877</v>
       </c>
       <c r="B145" t="n">
-        <v>57326</v>
+        <v>91494</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -17828,25 +17848,25 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>100049</v>
+        <v>4769</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -17854,24 +17874,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Solberga , Solberga , Dlr</t>
+          <t>Solberga, Solberga, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>512452</v>
+        <v>512410</v>
       </c>
       <c r="R145" t="n">
-        <v>6728231</v>
+        <v>6728168</v>
       </c>
       <c r="S145" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -17898,19 +17918,9 @@
           <t>2024-09-20</t>
         </is>
       </c>
-      <c r="Z145" t="inlineStr">
-        <is>
-          <t>10:29</t>
-        </is>
-      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AB145" t="inlineStr">
-        <is>
-          <t>10:29</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -18058,10 +18068,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>119863337</v>
+        <v>119869590</v>
       </c>
       <c r="B147" t="n">
-        <v>57463</v>
+        <v>91840</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -18070,35 +18080,35 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P147" t="inlineStr">
@@ -18107,10 +18117,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>512515</v>
+        <v>512413</v>
       </c>
       <c r="R147" t="n">
-        <v>6728351</v>
+        <v>6728315</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -18140,19 +18150,9 @@
           <t>2024-09-20</t>
         </is>
       </c>
-      <c r="Z147" t="inlineStr">
-        <is>
-          <t>10:32</t>
-        </is>
-      </c>
       <c r="AA147" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AB147" t="inlineStr">
-        <is>
-          <t>10:32</t>
         </is>
       </c>
       <c r="AD147" t="b">

--- a/artfynd/A 49115-2023 artfynd.xlsx
+++ b/artfynd/A 49115-2023 artfynd.xlsx
@@ -17952,10 +17952,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>119869333</v>
+        <v>119869590</v>
       </c>
       <c r="B146" t="n">
-        <v>91494</v>
+        <v>91840</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -17968,26 +17968,26 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>4769</v>
+        <v>4364</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -18001,13 +18001,13 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>512422</v>
+        <v>512413</v>
       </c>
       <c r="R146" t="n">
-        <v>6728244</v>
+        <v>6728315</v>
       </c>
       <c r="S146" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -18068,10 +18068,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>119869590</v>
+        <v>119869333</v>
       </c>
       <c r="B147" t="n">
-        <v>91840</v>
+        <v>91494</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -18084,26 +18084,26 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>4364</v>
+        <v>4769</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -18117,13 +18117,13 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>512413</v>
+        <v>512422</v>
       </c>
       <c r="R147" t="n">
-        <v>6728315</v>
+        <v>6728244</v>
       </c>
       <c r="S147" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>

--- a/artfynd/A 49115-2023 artfynd.xlsx
+++ b/artfynd/A 49115-2023 artfynd.xlsx
@@ -17952,10 +17952,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>119869590</v>
+        <v>119869333</v>
       </c>
       <c r="B146" t="n">
-        <v>91840</v>
+        <v>91494</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -17968,26 +17968,26 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>4364</v>
+        <v>4769</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -18001,13 +18001,13 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>512413</v>
+        <v>512422</v>
       </c>
       <c r="R146" t="n">
-        <v>6728315</v>
+        <v>6728244</v>
       </c>
       <c r="S146" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -18068,10 +18068,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>119869333</v>
+        <v>119869590</v>
       </c>
       <c r="B147" t="n">
-        <v>91494</v>
+        <v>91840</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -18084,26 +18084,26 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>4769</v>
+        <v>4364</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -18117,13 +18117,13 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>512422</v>
+        <v>512413</v>
       </c>
       <c r="R147" t="n">
-        <v>6728244</v>
+        <v>6728315</v>
       </c>
       <c r="S147" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>

--- a/artfynd/A 49115-2023 artfynd.xlsx
+++ b/artfynd/A 49115-2023 artfynd.xlsx
@@ -17336,10 +17336,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>119863337</v>
+        <v>119864877</v>
       </c>
       <c r="B141" t="n">
-        <v>57463</v>
+        <v>91512</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -17348,25 +17348,25 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>103021</v>
+        <v>4769</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -17374,9 +17374,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
@@ -17385,13 +17385,13 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>512515</v>
+        <v>512410</v>
       </c>
       <c r="R141" t="n">
-        <v>6728351</v>
+        <v>6728168</v>
       </c>
       <c r="S141" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -17418,19 +17418,9 @@
           <t>2024-09-20</t>
         </is>
       </c>
-      <c r="Z141" t="inlineStr">
-        <is>
-          <t>10:32</t>
-        </is>
-      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AB141" t="inlineStr">
-        <is>
-          <t>10:32</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -17465,7 +17455,7 @@
         <v>119870076</v>
       </c>
       <c r="B142" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -17591,7 +17581,7 @@
         <v>119863311</v>
       </c>
       <c r="B143" t="n">
-        <v>57326</v>
+        <v>57336</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -17714,10 +17704,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>119864797</v>
+        <v>119869590</v>
       </c>
       <c r="B144" t="n">
-        <v>90527</v>
+        <v>91858</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -17730,37 +17720,46 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P144" t="inlineStr">
         <is>
           <t>Solberga, Solberga, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>512410</v>
+        <v>512413</v>
       </c>
       <c r="R144" t="n">
-        <v>6728168</v>
+        <v>6728315</v>
       </c>
       <c r="S144" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -17804,21 +17803,6 @@
       <c r="AH144" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ144" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK144" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO144" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT144" t="inlineStr"/>
@@ -17836,10 +17820,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>119864877</v>
+        <v>119864797</v>
       </c>
       <c r="B145" t="n">
-        <v>91494</v>
+        <v>90545</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -17852,33 +17836,24 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>4769</v>
+        <v>5447</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
           <t>Solberga, Solberga, Dlr</t>
@@ -17935,6 +17910,21 @@
       <c r="AH145" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ145" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK145" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO145" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT145" t="inlineStr"/>
@@ -17952,10 +17942,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>119869333</v>
+        <v>119863337</v>
       </c>
       <c r="B146" t="n">
-        <v>91494</v>
+        <v>57473</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -17964,25 +17954,25 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>4769</v>
+        <v>103021</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -17990,9 +17980,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J146" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P146" t="inlineStr">
@@ -18001,13 +17991,13 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>512422</v>
+        <v>512515</v>
       </c>
       <c r="R146" t="n">
-        <v>6728244</v>
+        <v>6728351</v>
       </c>
       <c r="S146" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -18034,9 +18024,19 @@
           <t>2024-09-20</t>
         </is>
       </c>
+      <c r="Z146" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
       <c r="AA146" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AB146" t="inlineStr">
+        <is>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -18068,10 +18068,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>119869590</v>
+        <v>119869333</v>
       </c>
       <c r="B147" t="n">
-        <v>91840</v>
+        <v>91512</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -18084,26 +18084,26 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>4364</v>
+        <v>4769</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -18117,13 +18117,13 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>512413</v>
+        <v>512422</v>
       </c>
       <c r="R147" t="n">
-        <v>6728315</v>
+        <v>6728244</v>
       </c>
       <c r="S147" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>

--- a/artfynd/A 49115-2023 artfynd.xlsx
+++ b/artfynd/A 49115-2023 artfynd.xlsx
@@ -17336,10 +17336,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>119864877</v>
+        <v>119869590</v>
       </c>
       <c r="B141" t="n">
-        <v>91512</v>
+        <v>91858</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -17352,26 +17352,26 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>4769</v>
+        <v>4364</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -17385,13 +17385,13 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>512410</v>
+        <v>512413</v>
       </c>
       <c r="R141" t="n">
-        <v>6728168</v>
+        <v>6728315</v>
       </c>
       <c r="S141" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -17578,10 +17578,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>119863311</v>
+        <v>119869333</v>
       </c>
       <c r="B143" t="n">
-        <v>57336</v>
+        <v>91512</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -17590,25 +17590,25 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>100049</v>
+        <v>4769</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -17616,24 +17616,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Solberga , Solberga , Dlr</t>
+          <t>Solberga, Solberga, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>512452</v>
+        <v>512422</v>
       </c>
       <c r="R143" t="n">
-        <v>6728231</v>
+        <v>6728244</v>
       </c>
       <c r="S143" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -17660,19 +17660,9 @@
           <t>2024-09-20</t>
         </is>
       </c>
-      <c r="Z143" t="inlineStr">
-        <is>
-          <t>10:29</t>
-        </is>
-      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AB143" t="inlineStr">
-        <is>
-          <t>10:29</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -17704,10 +17694,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>119869590</v>
+        <v>119864797</v>
       </c>
       <c r="B144" t="n">
-        <v>91858</v>
+        <v>90545</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -17720,46 +17710,37 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Solberga, Solberga, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>512413</v>
+        <v>512410</v>
       </c>
       <c r="R144" t="n">
-        <v>6728315</v>
+        <v>6728168</v>
       </c>
       <c r="S144" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -17803,6 +17784,21 @@
       <c r="AH144" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ144" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK144" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO144" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT144" t="inlineStr"/>
@@ -17820,10 +17816,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>119864797</v>
+        <v>119864877</v>
       </c>
       <c r="B145" t="n">
-        <v>90545</v>
+        <v>91512</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -17836,24 +17832,33 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>5447</v>
+        <v>4769</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr"/>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P145" t="inlineStr">
         <is>
           <t>Solberga, Solberga, Dlr</t>
@@ -17910,21 +17915,6 @@
       <c r="AH145" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ145" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK145" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO145" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT145" t="inlineStr"/>
@@ -18068,10 +18058,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>119869333</v>
+        <v>119863311</v>
       </c>
       <c r="B147" t="n">
-        <v>91512</v>
+        <v>57336</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -18080,25 +18070,25 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>4769</v>
+        <v>100049</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -18106,24 +18096,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J147" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Solberga, Solberga, Dlr</t>
+          <t>Solberga , Solberga , Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>512422</v>
+        <v>512452</v>
       </c>
       <c r="R147" t="n">
-        <v>6728244</v>
+        <v>6728231</v>
       </c>
       <c r="S147" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -18150,9 +18140,19 @@
           <t>2024-09-20</t>
         </is>
       </c>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
       <c r="AA147" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AB147" t="inlineStr">
+        <is>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD147" t="b">

--- a/artfynd/A 49115-2023 artfynd.xlsx
+++ b/artfynd/A 49115-2023 artfynd.xlsx
@@ -17336,10 +17336,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>119869590</v>
+        <v>119863311</v>
       </c>
       <c r="B141" t="n">
-        <v>91858</v>
+        <v>57336</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -17348,47 +17348,47 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Solberga, Solberga, Dlr</t>
+          <t>Solberga , Solberga , Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>512413</v>
+        <v>512452</v>
       </c>
       <c r="R141" t="n">
-        <v>6728315</v>
+        <v>6728231</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -17418,9 +17418,19 @@
           <t>2024-09-20</t>
         </is>
       </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -17452,10 +17462,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>119870076</v>
+        <v>119864877</v>
       </c>
       <c r="B142" t="n">
-        <v>91858</v>
+        <v>91512</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -17468,26 +17478,26 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>4364</v>
+        <v>4769</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -17501,10 +17511,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>512397</v>
+        <v>512410</v>
       </c>
       <c r="R142" t="n">
-        <v>6728345</v>
+        <v>6728168</v>
       </c>
       <c r="S142" t="n">
         <v>5</v>
@@ -17534,19 +17544,9 @@
           <t>2024-09-20</t>
         </is>
       </c>
-      <c r="Z142" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
       <c r="AA142" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AB142" t="inlineStr">
-        <is>
-          <t>13:21</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -17694,10 +17694,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>119864797</v>
+        <v>119870076</v>
       </c>
       <c r="B144" t="n">
-        <v>90545</v>
+        <v>91858</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -17710,34 +17710,43 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P144" t="inlineStr">
         <is>
           <t>Solberga, Solberga, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>512410</v>
+        <v>512397</v>
       </c>
       <c r="R144" t="n">
-        <v>6728168</v>
+        <v>6728345</v>
       </c>
       <c r="S144" t="n">
         <v>5</v>
@@ -17767,11 +17776,21 @@
           <t>2024-09-20</t>
         </is>
       </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>2024-09-20</t>
         </is>
       </c>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
       <c r="AD144" t="b">
         <v>0</v>
       </c>
@@ -17784,21 +17803,6 @@
       <c r="AH144" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ144" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK144" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO144" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT144" t="inlineStr"/>
@@ -17816,10 +17820,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>119864877</v>
+        <v>119863337</v>
       </c>
       <c r="B145" t="n">
-        <v>91512</v>
+        <v>57473</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -17828,25 +17832,25 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>4769</v>
+        <v>103021</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -17854,9 +17858,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
@@ -17865,13 +17869,13 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>512410</v>
+        <v>512515</v>
       </c>
       <c r="R145" t="n">
-        <v>6728168</v>
+        <v>6728351</v>
       </c>
       <c r="S145" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -17898,9 +17902,19 @@
           <t>2024-09-20</t>
         </is>
       </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AB145" t="inlineStr">
+        <is>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -17932,10 +17946,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>119863337</v>
+        <v>119869590</v>
       </c>
       <c r="B146" t="n">
-        <v>57473</v>
+        <v>91858</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -17944,35 +17958,35 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M146" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P146" t="inlineStr">
@@ -17981,10 +17995,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>512515</v>
+        <v>512413</v>
       </c>
       <c r="R146" t="n">
-        <v>6728351</v>
+        <v>6728315</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -18014,19 +18028,9 @@
           <t>2024-09-20</t>
         </is>
       </c>
-      <c r="Z146" t="inlineStr">
-        <is>
-          <t>10:32</t>
-        </is>
-      </c>
       <c r="AA146" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AB146" t="inlineStr">
-        <is>
-          <t>10:32</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -18058,10 +18062,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>119863311</v>
+        <v>119864797</v>
       </c>
       <c r="B147" t="n">
-        <v>57336</v>
+        <v>90545</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -18070,50 +18074,41 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Solberga , Solberga , Dlr</t>
+          <t>Solberga, Solberga, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>512452</v>
+        <v>512410</v>
       </c>
       <c r="R147" t="n">
-        <v>6728231</v>
+        <v>6728168</v>
       </c>
       <c r="S147" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -18140,21 +18135,11 @@
           <t>2024-09-20</t>
         </is>
       </c>
-      <c r="Z147" t="inlineStr">
-        <is>
-          <t>10:29</t>
-        </is>
-      </c>
       <c r="AA147" t="inlineStr">
         <is>
           <t>2024-09-20</t>
         </is>
       </c>
-      <c r="AB147" t="inlineStr">
-        <is>
-          <t>10:29</t>
-        </is>
-      </c>
       <c r="AD147" t="b">
         <v>0</v>
       </c>
@@ -18167,6 +18152,21 @@
       <c r="AH147" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ147" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK147" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO147" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT147" t="inlineStr"/>

--- a/artfynd/A 49115-2023 artfynd.xlsx
+++ b/artfynd/A 49115-2023 artfynd.xlsx
@@ -17336,10 +17336,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>119863311</v>
+        <v>119864877</v>
       </c>
       <c r="B141" t="n">
-        <v>57336</v>
+        <v>91512</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -17348,25 +17348,25 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100049</v>
+        <v>4769</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -17374,24 +17374,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Solberga , Solberga , Dlr</t>
+          <t>Solberga, Solberga, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>512452</v>
+        <v>512410</v>
       </c>
       <c r="R141" t="n">
-        <v>6728231</v>
+        <v>6728168</v>
       </c>
       <c r="S141" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -17418,19 +17418,9 @@
           <t>2024-09-20</t>
         </is>
       </c>
-      <c r="Z141" t="inlineStr">
-        <is>
-          <t>10:29</t>
-        </is>
-      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AB141" t="inlineStr">
-        <is>
-          <t>10:29</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -17462,10 +17452,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>119864877</v>
+        <v>119863337</v>
       </c>
       <c r="B142" t="n">
-        <v>91512</v>
+        <v>57473</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -17474,25 +17464,25 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>4769</v>
+        <v>103021</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -17500,9 +17490,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J142" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
@@ -17511,13 +17501,13 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>512410</v>
+        <v>512515</v>
       </c>
       <c r="R142" t="n">
-        <v>6728168</v>
+        <v>6728351</v>
       </c>
       <c r="S142" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -17544,9 +17534,19 @@
           <t>2024-09-20</t>
         </is>
       </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
       <c r="AA142" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -17578,10 +17578,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>119869333</v>
+        <v>119870076</v>
       </c>
       <c r="B143" t="n">
-        <v>91512</v>
+        <v>91858</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -17594,26 +17594,26 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>4769</v>
+        <v>4364</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -17627,10 +17627,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>512422</v>
+        <v>512397</v>
       </c>
       <c r="R143" t="n">
-        <v>6728244</v>
+        <v>6728345</v>
       </c>
       <c r="S143" t="n">
         <v>5</v>
@@ -17660,9 +17660,19 @@
           <t>2024-09-20</t>
         </is>
       </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -17694,10 +17704,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>119870076</v>
+        <v>119863311</v>
       </c>
       <c r="B144" t="n">
-        <v>91858</v>
+        <v>57336</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -17706,50 +17716,50 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Solberga, Solberga, Dlr</t>
+          <t>Solberga , Solberga , Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>512397</v>
+        <v>512452</v>
       </c>
       <c r="R144" t="n">
-        <v>6728345</v>
+        <v>6728231</v>
       </c>
       <c r="S144" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -17778,7 +17788,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -17788,7 +17798,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -17820,10 +17830,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>119863337</v>
+        <v>119864797</v>
       </c>
       <c r="B145" t="n">
-        <v>57473</v>
+        <v>90545</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -17832,50 +17842,41 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
           <t>Solberga, Solberga, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>512515</v>
+        <v>512410</v>
       </c>
       <c r="R145" t="n">
-        <v>6728351</v>
+        <v>6728168</v>
       </c>
       <c r="S145" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -17902,21 +17903,11 @@
           <t>2024-09-20</t>
         </is>
       </c>
-      <c r="Z145" t="inlineStr">
-        <is>
-          <t>10:32</t>
-        </is>
-      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>2024-09-20</t>
         </is>
       </c>
-      <c r="AB145" t="inlineStr">
-        <is>
-          <t>10:32</t>
-        </is>
-      </c>
       <c r="AD145" t="b">
         <v>0</v>
       </c>
@@ -17929,6 +17920,21 @@
       <c r="AH145" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ145" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK145" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO145" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT145" t="inlineStr"/>
@@ -17946,10 +17952,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>119869590</v>
+        <v>119869333</v>
       </c>
       <c r="B146" t="n">
-        <v>91858</v>
+        <v>91512</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -17962,26 +17968,26 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>4364</v>
+        <v>4769</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -17995,13 +18001,13 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>512413</v>
+        <v>512422</v>
       </c>
       <c r="R146" t="n">
-        <v>6728315</v>
+        <v>6728244</v>
       </c>
       <c r="S146" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -18062,10 +18068,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>119864797</v>
+        <v>119869590</v>
       </c>
       <c r="B147" t="n">
-        <v>90545</v>
+        <v>91858</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -18078,37 +18084,46 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P147" t="inlineStr">
         <is>
           <t>Solberga, Solberga, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>512410</v>
+        <v>512413</v>
       </c>
       <c r="R147" t="n">
-        <v>6728168</v>
+        <v>6728315</v>
       </c>
       <c r="S147" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -18152,21 +18167,6 @@
       <c r="AH147" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ147" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK147" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO147" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT147" t="inlineStr"/>

--- a/artfynd/A 49115-2023 artfynd.xlsx
+++ b/artfynd/A 49115-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY147"/>
+  <dimension ref="A1:AY155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17336,10 +17336,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>119864877</v>
+        <v>119870076</v>
       </c>
       <c r="B141" t="n">
-        <v>91512</v>
+        <v>91858</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -17352,26 +17352,26 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>4769</v>
+        <v>4364</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -17385,10 +17385,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>512410</v>
+        <v>512397</v>
       </c>
       <c r="R141" t="n">
-        <v>6728168</v>
+        <v>6728345</v>
       </c>
       <c r="S141" t="n">
         <v>5</v>
@@ -17418,9 +17418,19 @@
           <t>2024-09-20</t>
         </is>
       </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -17452,10 +17462,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>119863337</v>
+        <v>119869333</v>
       </c>
       <c r="B142" t="n">
-        <v>57473</v>
+        <v>91512</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -17464,25 +17474,25 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>103021</v>
+        <v>4769</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -17490,9 +17500,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
@@ -17501,13 +17511,13 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>512515</v>
+        <v>512422</v>
       </c>
       <c r="R142" t="n">
-        <v>6728351</v>
+        <v>6728244</v>
       </c>
       <c r="S142" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -17534,19 +17544,9 @@
           <t>2024-09-20</t>
         </is>
       </c>
-      <c r="Z142" t="inlineStr">
-        <is>
-          <t>10:32</t>
-        </is>
-      </c>
       <c r="AA142" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AB142" t="inlineStr">
-        <is>
-          <t>10:32</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -17578,10 +17578,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>119870076</v>
+        <v>119863337</v>
       </c>
       <c r="B143" t="n">
-        <v>91858</v>
+        <v>57473</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -17590,35 +17590,35 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P143" t="inlineStr">
@@ -17627,13 +17627,13 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>512397</v>
+        <v>512515</v>
       </c>
       <c r="R143" t="n">
-        <v>6728345</v>
+        <v>6728351</v>
       </c>
       <c r="S143" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -17662,7 +17662,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -17672,7 +17672,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -17704,10 +17704,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>119863311</v>
+        <v>119864797</v>
       </c>
       <c r="B144" t="n">
-        <v>57336</v>
+        <v>90545</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -17716,50 +17716,41 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Solberga , Solberga , Dlr</t>
+          <t>Solberga, Solberga, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>512452</v>
+        <v>512410</v>
       </c>
       <c r="R144" t="n">
-        <v>6728231</v>
+        <v>6728168</v>
       </c>
       <c r="S144" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -17786,21 +17777,11 @@
           <t>2024-09-20</t>
         </is>
       </c>
-      <c r="Z144" t="inlineStr">
-        <is>
-          <t>10:29</t>
-        </is>
-      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>2024-09-20</t>
         </is>
       </c>
-      <c r="AB144" t="inlineStr">
-        <is>
-          <t>10:29</t>
-        </is>
-      </c>
       <c r="AD144" t="b">
         <v>0</v>
       </c>
@@ -17813,6 +17794,21 @@
       <c r="AH144" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ144" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK144" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO144" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT144" t="inlineStr"/>
@@ -17830,10 +17826,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>119864797</v>
+        <v>119864877</v>
       </c>
       <c r="B145" t="n">
-        <v>90545</v>
+        <v>91512</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -17846,24 +17842,33 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>5447</v>
+        <v>4769</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr"/>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P145" t="inlineStr">
         <is>
           <t>Solberga, Solberga, Dlr</t>
@@ -17920,21 +17925,6 @@
       <c r="AH145" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ145" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK145" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO145" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT145" t="inlineStr"/>
@@ -17952,10 +17942,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>119869333</v>
+        <v>119869590</v>
       </c>
       <c r="B146" t="n">
-        <v>91512</v>
+        <v>91858</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -17968,26 +17958,26 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>4769</v>
+        <v>4364</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -18001,13 +17991,13 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>512422</v>
+        <v>512413</v>
       </c>
       <c r="R146" t="n">
-        <v>6728244</v>
+        <v>6728315</v>
       </c>
       <c r="S146" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -18068,10 +18058,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>119869590</v>
+        <v>119863311</v>
       </c>
       <c r="B147" t="n">
-        <v>91858</v>
+        <v>57336</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -18080,47 +18070,47 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J147" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Solberga, Solberga, Dlr</t>
+          <t>Solberga , Solberga , Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>512413</v>
+        <v>512452</v>
       </c>
       <c r="R147" t="n">
-        <v>6728315</v>
+        <v>6728231</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -18150,9 +18140,19 @@
           <t>2024-09-20</t>
         </is>
       </c>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
       <c r="AA147" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AB147" t="inlineStr">
+        <is>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -18181,6 +18181,954 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>120497339</v>
+      </c>
+      <c r="B148" t="n">
+        <v>91023</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
+      <c r="N148" t="inlineStr"/>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>Solberga, Dlr</t>
+        </is>
+      </c>
+      <c r="Q148" t="n">
+        <v>512477</v>
+      </c>
+      <c r="R148" t="n">
+        <v>6728133</v>
+      </c>
+      <c r="S148" t="n">
+        <v>10</v>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>Ål</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AD148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF148" t="inlineStr"/>
+      <c r="AG148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH148" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI148" t="inlineStr">
+        <is>
+          <t>Gammal barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AT148" t="inlineStr"/>
+      <c r="AW148" t="inlineStr">
+        <is>
+          <t>Paula Testad</t>
+        </is>
+      </c>
+      <c r="AX148" t="inlineStr">
+        <is>
+          <t>Paula Testad, Lars Johan Klockars</t>
+        </is>
+      </c>
+      <c r="AY148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>120497405</v>
+      </c>
+      <c r="B149" t="n">
+        <v>90527</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>112</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Stjärntagging</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Asterodon ferruginosus</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
+      <c r="N149" t="inlineStr"/>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>Solberga, Dlr</t>
+        </is>
+      </c>
+      <c r="Q149" t="n">
+        <v>512480</v>
+      </c>
+      <c r="R149" t="n">
+        <v>6728138</v>
+      </c>
+      <c r="S149" t="n">
+        <v>10</v>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>Ål</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AD149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF149" t="inlineStr"/>
+      <c r="AG149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH149" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI149" t="inlineStr">
+        <is>
+          <t>Gammal barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AT149" t="inlineStr"/>
+      <c r="AW149" t="inlineStr">
+        <is>
+          <t>Paula Testad</t>
+        </is>
+      </c>
+      <c r="AX149" t="inlineStr">
+        <is>
+          <t>Paula Testad, Lars Johan Klockars</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>120497089</v>
+      </c>
+      <c r="B150" t="n">
+        <v>91862</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>Solberga, Dlr</t>
+        </is>
+      </c>
+      <c r="Q150" t="n">
+        <v>512488</v>
+      </c>
+      <c r="R150" t="n">
+        <v>6728299</v>
+      </c>
+      <c r="S150" t="n">
+        <v>10</v>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>Ål</t>
+        </is>
+      </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AD150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF150" t="inlineStr"/>
+      <c r="AG150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH150" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI150" t="inlineStr">
+        <is>
+          <t>Gammal naturskog</t>
+        </is>
+      </c>
+      <c r="AT150" t="inlineStr"/>
+      <c r="AW150" t="inlineStr">
+        <is>
+          <t>Paula Testad</t>
+        </is>
+      </c>
+      <c r="AX150" t="inlineStr">
+        <is>
+          <t>Paula Testad, Lars Johan Klockars</t>
+        </is>
+      </c>
+      <c r="AY150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>120497240</v>
+      </c>
+      <c r="B151" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="N151" t="inlineStr"/>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>Solberga, Dlr</t>
+        </is>
+      </c>
+      <c r="Q151" t="n">
+        <v>512490</v>
+      </c>
+      <c r="R151" t="n">
+        <v>6728219</v>
+      </c>
+      <c r="S151" t="n">
+        <v>10</v>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>Ål</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AD151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF151" t="inlineStr"/>
+      <c r="AG151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH151" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI151" t="inlineStr">
+        <is>
+          <t>Gammal barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AT151" t="inlineStr"/>
+      <c r="AW151" t="inlineStr">
+        <is>
+          <t>Paula Testad</t>
+        </is>
+      </c>
+      <c r="AX151" t="inlineStr">
+        <is>
+          <t>Paula Testad, Lars Johan Klockars</t>
+        </is>
+      </c>
+      <c r="AY151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>120508123</v>
+      </c>
+      <c r="B152" t="n">
+        <v>91858</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr"/>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>Solberga, Dlr</t>
+        </is>
+      </c>
+      <c r="Q152" t="n">
+        <v>512407</v>
+      </c>
+      <c r="R152" t="n">
+        <v>6728297</v>
+      </c>
+      <c r="S152" t="n">
+        <v>10</v>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W152" t="inlineStr">
+        <is>
+          <t>Ål</t>
+        </is>
+      </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF152" t="inlineStr"/>
+      <c r="AG152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH152" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI152" t="inlineStr">
+        <is>
+          <t>Gammal barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AT152" t="inlineStr"/>
+      <c r="AW152" t="inlineStr">
+        <is>
+          <t>Paula Testad</t>
+        </is>
+      </c>
+      <c r="AX152" t="inlineStr">
+        <is>
+          <t>Paula Testad</t>
+        </is>
+      </c>
+      <c r="AY152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>120497421</v>
+      </c>
+      <c r="B153" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr"/>
+      <c r="N153" t="inlineStr"/>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>Solberga, Dlr</t>
+        </is>
+      </c>
+      <c r="Q153" t="n">
+        <v>512531</v>
+      </c>
+      <c r="R153" t="n">
+        <v>6728299</v>
+      </c>
+      <c r="S153" t="n">
+        <v>10</v>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>Ål</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AD153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF153" t="inlineStr"/>
+      <c r="AG153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH153" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI153" t="inlineStr">
+        <is>
+          <t>Gammal barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AT153" t="inlineStr"/>
+      <c r="AW153" t="inlineStr">
+        <is>
+          <t>Paula Testad</t>
+        </is>
+      </c>
+      <c r="AX153" t="inlineStr">
+        <is>
+          <t>Paula Testad, Lars Johan Klockars</t>
+        </is>
+      </c>
+      <c r="AY153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>120497372</v>
+      </c>
+      <c r="B154" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr"/>
+      <c r="N154" t="inlineStr"/>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>Solberga, Dlr</t>
+        </is>
+      </c>
+      <c r="Q154" t="n">
+        <v>512479</v>
+      </c>
+      <c r="R154" t="n">
+        <v>6728136</v>
+      </c>
+      <c r="S154" t="n">
+        <v>10</v>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W154" t="inlineStr">
+        <is>
+          <t>Ål</t>
+        </is>
+      </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AD154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF154" t="inlineStr"/>
+      <c r="AG154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH154" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI154" t="inlineStr">
+        <is>
+          <t>Gammal barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AT154" t="inlineStr"/>
+      <c r="AW154" t="inlineStr">
+        <is>
+          <t>Paula Testad</t>
+        </is>
+      </c>
+      <c r="AX154" t="inlineStr">
+        <is>
+          <t>Paula Testad, Lars Johan Klockars</t>
+        </is>
+      </c>
+      <c r="AY154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>120497083</v>
+      </c>
+      <c r="B155" t="n">
+        <v>90545</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
+      <c r="N155" t="inlineStr"/>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>Solberga, Dlr</t>
+        </is>
+      </c>
+      <c r="Q155" t="n">
+        <v>512483</v>
+      </c>
+      <c r="R155" t="n">
+        <v>6728300</v>
+      </c>
+      <c r="S155" t="n">
+        <v>10</v>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>Ål</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AD155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF155" t="inlineStr"/>
+      <c r="AG155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH155" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI155" t="inlineStr">
+        <is>
+          <t>Gammal naturskog</t>
+        </is>
+      </c>
+      <c r="AT155" t="inlineStr"/>
+      <c r="AW155" t="inlineStr">
+        <is>
+          <t>Paula Testad</t>
+        </is>
+      </c>
+      <c r="AX155" t="inlineStr">
+        <is>
+          <t>Paula Testad, Lars Johan Klockars</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49115-2023 artfynd.xlsx
+++ b/artfynd/A 49115-2023 artfynd.xlsx
@@ -18184,10 +18184,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>120497339</v>
+        <v>120497240</v>
       </c>
       <c r="B148" t="n">
-        <v>91023</v>
+        <v>78542</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -18196,25 +18196,25 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -18227,10 +18227,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>512477</v>
+        <v>512490</v>
       </c>
       <c r="R148" t="n">
-        <v>6728133</v>
+        <v>6728219</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -18300,10 +18300,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>120497405</v>
+        <v>120497421</v>
       </c>
       <c r="B149" t="n">
-        <v>90527</v>
+        <v>90580</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -18316,21 +18316,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>112</v>
+        <v>1202</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -18343,10 +18343,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>512480</v>
+        <v>512531</v>
       </c>
       <c r="R149" t="n">
-        <v>6728138</v>
+        <v>6728299</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -18416,10 +18416,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>120497089</v>
+        <v>120497083</v>
       </c>
       <c r="B150" t="n">
-        <v>91862</v>
+        <v>90545</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -18428,37 +18428,29 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>4365</v>
+        <v>5447</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr"/>
       <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
@@ -18467,10 +18459,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>512488</v>
+        <v>512483</v>
       </c>
       <c r="R150" t="n">
-        <v>6728299</v>
+        <v>6728300</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -18540,10 +18532,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>120497240</v>
+        <v>120497089</v>
       </c>
       <c r="B151" t="n">
-        <v>78542</v>
+        <v>91862</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -18552,29 +18544,37 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>4365</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr"/>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K151" t="inlineStr"/>
       <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
@@ -18583,10 +18583,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>512490</v>
+        <v>512488</v>
       </c>
       <c r="R151" t="n">
-        <v>6728219</v>
+        <v>6728299</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -18638,7 +18638,7 @@
       </c>
       <c r="AI151" t="inlineStr">
         <is>
-          <t>Gammal barrnaturskog</t>
+          <t>Gammal naturskog</t>
         </is>
       </c>
       <c r="AT151" t="inlineStr"/>
@@ -18656,10 +18656,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>120508123</v>
+        <v>120497339</v>
       </c>
       <c r="B152" t="n">
-        <v>91858</v>
+        <v>91023</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -18668,42 +18668,30 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>4364</v>
+        <v>1209</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J152" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr"/>
       <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
@@ -18711,10 +18699,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>512407</v>
+        <v>512477</v>
       </c>
       <c r="R152" t="n">
-        <v>6728297</v>
+        <v>6728133</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -18741,12 +18729,12 @@
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-10-12</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-10-12</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -18777,14 +18765,14 @@
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Paula Testad</t>
+          <t>Paula Testad, Lars Johan Klockars</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>120497421</v>
+        <v>120497372</v>
       </c>
       <c r="B153" t="n">
         <v>90580</v>
@@ -18827,10 +18815,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>512531</v>
+        <v>512479</v>
       </c>
       <c r="R153" t="n">
-        <v>6728299</v>
+        <v>6728136</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -18900,10 +18888,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>120497372</v>
+        <v>120508123</v>
       </c>
       <c r="B154" t="n">
-        <v>90580</v>
+        <v>91858</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -18912,30 +18900,42 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr"/>
-      <c r="J154" t="inlineStr"/>
-      <c r="K154" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
@@ -18943,10 +18943,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>512479</v>
+        <v>512407</v>
       </c>
       <c r="R154" t="n">
-        <v>6728136</v>
+        <v>6728297</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -18973,12 +18973,12 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>2024-10-12</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2024-10-12</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -19009,17 +19009,17 @@
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Paula Testad, Lars Johan Klockars</t>
+          <t>Paula Testad</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>120497083</v>
+        <v>120497405</v>
       </c>
       <c r="B155" t="n">
-        <v>90545</v>
+        <v>90527</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -19028,25 +19028,25 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>5447</v>
+        <v>112</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -19059,10 +19059,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>512483</v>
+        <v>512480</v>
       </c>
       <c r="R155" t="n">
-        <v>6728300</v>
+        <v>6728138</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -19114,7 +19114,7 @@
       </c>
       <c r="AI155" t="inlineStr">
         <is>
-          <t>Gammal naturskog</t>
+          <t>Gammal barrnaturskog</t>
         </is>
       </c>
       <c r="AT155" t="inlineStr"/>

--- a/artfynd/A 49115-2023 artfynd.xlsx
+++ b/artfynd/A 49115-2023 artfynd.xlsx
@@ -18184,10 +18184,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>120497240</v>
+        <v>120497089</v>
       </c>
       <c r="B148" t="n">
-        <v>78542</v>
+        <v>91862</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -18196,29 +18196,37 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6425</v>
+        <v>4365</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr"/>
-      <c r="J148" t="inlineStr"/>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K148" t="inlineStr"/>
       <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
@@ -18227,10 +18235,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>512490</v>
+        <v>512488</v>
       </c>
       <c r="R148" t="n">
-        <v>6728219</v>
+        <v>6728299</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -18282,7 +18290,7 @@
       </c>
       <c r="AI148" t="inlineStr">
         <is>
-          <t>Gammal barrnaturskog</t>
+          <t>Gammal naturskog</t>
         </is>
       </c>
       <c r="AT148" t="inlineStr"/>
@@ -18300,10 +18308,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>120497421</v>
+        <v>120497339</v>
       </c>
       <c r="B149" t="n">
-        <v>90580</v>
+        <v>91023</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -18312,25 +18320,25 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -18343,10 +18351,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>512531</v>
+        <v>512477</v>
       </c>
       <c r="R149" t="n">
-        <v>6728299</v>
+        <v>6728133</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -18532,10 +18540,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>120497089</v>
+        <v>120497372</v>
       </c>
       <c r="B151" t="n">
-        <v>91862</v>
+        <v>90580</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -18544,37 +18552,29 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>4365</v>
+        <v>1202</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr"/>
       <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
@@ -18583,10 +18583,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>512488</v>
+        <v>512479</v>
       </c>
       <c r="R151" t="n">
-        <v>6728299</v>
+        <v>6728136</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -18638,7 +18638,7 @@
       </c>
       <c r="AI151" t="inlineStr">
         <is>
-          <t>Gammal naturskog</t>
+          <t>Gammal barrnaturskog</t>
         </is>
       </c>
       <c r="AT151" t="inlineStr"/>
@@ -18656,10 +18656,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>120497339</v>
+        <v>120497405</v>
       </c>
       <c r="B152" t="n">
-        <v>91023</v>
+        <v>90527</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -18668,25 +18668,25 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1209</v>
+        <v>112</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -18699,10 +18699,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>512477</v>
+        <v>512480</v>
       </c>
       <c r="R152" t="n">
-        <v>6728133</v>
+        <v>6728138</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -18772,10 +18772,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>120497372</v>
+        <v>120497240</v>
       </c>
       <c r="B153" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -18788,21 +18788,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -18815,10 +18815,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>512479</v>
+        <v>512490</v>
       </c>
       <c r="R153" t="n">
-        <v>6728136</v>
+        <v>6728219</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -19016,10 +19016,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>120497405</v>
+        <v>120497421</v>
       </c>
       <c r="B155" t="n">
-        <v>90527</v>
+        <v>90580</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -19032,21 +19032,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>112</v>
+        <v>1202</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -19059,10 +19059,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>512480</v>
+        <v>512531</v>
       </c>
       <c r="R155" t="n">
-        <v>6728138</v>
+        <v>6728299</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>

--- a/artfynd/A 49115-2023 artfynd.xlsx
+++ b/artfynd/A 49115-2023 artfynd.xlsx
@@ -5420,7 +5420,7 @@
         <v>116227102</v>
       </c>
       <c r="B43" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         <v>116299476</v>
       </c>
       <c r="B47" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6036,7 +6036,7 @@
         <v>116299026</v>
       </c>
       <c r="B48" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6407,7 +6407,7 @@
         <v>116298843</v>
       </c>
       <c r="B51" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         <v>116299273</v>
       </c>
       <c r="B56" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7881,7 +7881,7 @@
         <v>116451411</v>
       </c>
       <c r="B63" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -14100,7 +14100,7 @@
         <v>118436002</v>
       </c>
       <c r="B115" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -14759,7 +14759,7 @@
         <v>118596386</v>
       </c>
       <c r="B120" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -15926,7 +15926,7 @@
         <v>119513652</v>
       </c>
       <c r="B129" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -18362,10 +18362,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>121112147</v>
+        <v>121112191</v>
       </c>
       <c r="B149" t="n">
-        <v>57501</v>
+        <v>90697</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -18378,35 +18378,26 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr"/>
-      <c r="L149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
@@ -18414,10 +18405,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>512452</v>
+        <v>512504</v>
       </c>
       <c r="R149" t="n">
-        <v>6728158</v>
+        <v>6728184</v>
       </c>
       <c r="S149" t="n">
         <v>5</v>
@@ -18458,6 +18449,7 @@
       <c r="AE149" t="b">
         <v>0</v>
       </c>
+      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
       </c>
@@ -18486,10 +18478,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>121112094</v>
+        <v>121112147</v>
       </c>
       <c r="B150" t="n">
-        <v>78598</v>
+        <v>57504</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -18502,26 +18494,35 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
@@ -18529,10 +18530,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>512340</v>
+        <v>512452</v>
       </c>
       <c r="R150" t="n">
-        <v>6728331</v>
+        <v>6728158</v>
       </c>
       <c r="S150" t="n">
         <v>5</v>
@@ -18573,7 +18574,6 @@
       <c r="AE150" t="b">
         <v>0</v>
       </c>
-      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
@@ -18602,10 +18602,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>121112119</v>
+        <v>121112195</v>
       </c>
       <c r="B151" t="n">
-        <v>90074</v>
+        <v>90697</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -18614,25 +18614,25 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>5685</v>
+        <v>1202</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -18645,10 +18645,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>512337</v>
+        <v>512504</v>
       </c>
       <c r="R151" t="n">
-        <v>6728307</v>
+        <v>6728332</v>
       </c>
       <c r="S151" t="n">
         <v>5</v>
@@ -18718,10 +18718,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>121112136</v>
+        <v>121112094</v>
       </c>
       <c r="B152" t="n">
-        <v>90652</v>
+        <v>78601</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -18730,25 +18730,25 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -18761,10 +18761,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>512407</v>
+        <v>512340</v>
       </c>
       <c r="R152" t="n">
-        <v>6728203</v>
+        <v>6728331</v>
       </c>
       <c r="S152" t="n">
         <v>5</v>
@@ -18834,10 +18834,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>121112195</v>
+        <v>121112136</v>
       </c>
       <c r="B153" t="n">
-        <v>90687</v>
+        <v>90662</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -18846,25 +18846,25 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -18877,10 +18877,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>512504</v>
+        <v>512407</v>
       </c>
       <c r="R153" t="n">
-        <v>6728332</v>
+        <v>6728203</v>
       </c>
       <c r="S153" t="n">
         <v>5</v>
@@ -18950,10 +18950,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>121112191</v>
+        <v>121112119</v>
       </c>
       <c r="B154" t="n">
-        <v>90687</v>
+        <v>90084</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -18962,25 +18962,25 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>1202</v>
+        <v>5685</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -18993,10 +18993,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>512504</v>
+        <v>512337</v>
       </c>
       <c r="R154" t="n">
-        <v>6728184</v>
+        <v>6728307</v>
       </c>
       <c r="S154" t="n">
         <v>5</v>
@@ -19069,7 +19069,7 @@
         <v>121112033</v>
       </c>
       <c r="B155" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>

--- a/artfynd/A 49115-2023 artfynd.xlsx
+++ b/artfynd/A 49115-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY155"/>
+  <dimension ref="A1:AY158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19180,6 +19180,352 @@
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>121439106</v>
+      </c>
+      <c r="B156" t="n">
+        <v>90983</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>658</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr"/>
+      <c r="N156" t="inlineStr"/>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>Solberga, Dlr</t>
+        </is>
+      </c>
+      <c r="Q156" t="n">
+        <v>512435</v>
+      </c>
+      <c r="R156" t="n">
+        <v>6728146</v>
+      </c>
+      <c r="S156" t="n">
+        <v>10</v>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W156" t="inlineStr">
+        <is>
+          <t>Ål</t>
+        </is>
+      </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="AD156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF156" t="inlineStr"/>
+      <c r="AG156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT156" t="inlineStr"/>
+      <c r="AW156" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX156" t="inlineStr">
+        <is>
+          <t>Göran Ehn, Lisa Olson, Cecilia Rastad, Paula Testad, Lars Johan Klockars</t>
+        </is>
+      </c>
+      <c r="AY156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>121442191</v>
+      </c>
+      <c r="B157" t="n">
+        <v>98081</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr"/>
+      <c r="N157" t="inlineStr"/>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>Solberga, Dlr</t>
+        </is>
+      </c>
+      <c r="Q157" t="n">
+        <v>512406</v>
+      </c>
+      <c r="R157" t="n">
+        <v>6728220</v>
+      </c>
+      <c r="S157" t="n">
+        <v>5</v>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>Ål</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="AD157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF157" t="inlineStr"/>
+      <c r="AG157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH157" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI157" t="inlineStr">
+        <is>
+          <t>Gammal barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AT157" t="inlineStr"/>
+      <c r="AW157" t="inlineStr">
+        <is>
+          <t>Paula Testad</t>
+        </is>
+      </c>
+      <c r="AX157" t="inlineStr">
+        <is>
+          <t>Paula Testad, Göran Ehn, Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>121441224</v>
+      </c>
+      <c r="B158" t="n">
+        <v>98081</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr"/>
+      <c r="N158" t="inlineStr"/>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>solberga, Dlr</t>
+        </is>
+      </c>
+      <c r="Q158" t="n">
+        <v>512424</v>
+      </c>
+      <c r="R158" t="n">
+        <v>6728268</v>
+      </c>
+      <c r="S158" t="n">
+        <v>10</v>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W158" t="inlineStr">
+        <is>
+          <t>Ål</t>
+        </is>
+      </c>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="AD158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF158" t="inlineStr"/>
+      <c r="AG158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT158" t="inlineStr"/>
+      <c r="AW158" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX158" t="inlineStr">
+        <is>
+          <t>Göran Ehn, Lisa Olson, Cecilia Rastad, Lars Johan Klockars, Paula Testad</t>
+        </is>
+      </c>
+      <c r="AY158" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49115-2023 artfynd.xlsx
+++ b/artfynd/A 49115-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY158"/>
+  <dimension ref="A1:AY166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Paula Testad, Lars Johan Klockars</t>
+          <t>Lars Johan Klockars, Paula Testad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -7135,7 +7135,7 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Paula Testad, Lars Johan Klockars</t>
+          <t>Lars Johan Klockars, Paula Testad</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -18362,10 +18362,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>121112191</v>
+        <v>121112136</v>
       </c>
       <c r="B149" t="n">
-        <v>90697</v>
+        <v>90662</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -18374,25 +18374,25 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -18405,10 +18405,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>512504</v>
+        <v>512407</v>
       </c>
       <c r="R149" t="n">
-        <v>6728184</v>
+        <v>6728203</v>
       </c>
       <c r="S149" t="n">
         <v>5</v>
@@ -18478,10 +18478,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>121112147</v>
+        <v>121112119</v>
       </c>
       <c r="B150" t="n">
-        <v>57504</v>
+        <v>90084</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -18490,39 +18490,30 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>103021</v>
+        <v>5685</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr"/>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
@@ -18530,10 +18521,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>512452</v>
+        <v>512337</v>
       </c>
       <c r="R150" t="n">
-        <v>6728158</v>
+        <v>6728307</v>
       </c>
       <c r="S150" t="n">
         <v>5</v>
@@ -18574,6 +18565,7 @@
       <c r="AE150" t="b">
         <v>0</v>
       </c>
+      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
@@ -18718,10 +18710,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>121112094</v>
+        <v>121112147</v>
       </c>
       <c r="B152" t="n">
-        <v>78601</v>
+        <v>57504</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -18734,26 +18726,35 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
@@ -18761,10 +18762,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>512340</v>
+        <v>512452</v>
       </c>
       <c r="R152" t="n">
-        <v>6728331</v>
+        <v>6728158</v>
       </c>
       <c r="S152" t="n">
         <v>5</v>
@@ -18805,7 +18806,6 @@
       <c r="AE152" t="b">
         <v>0</v>
       </c>
-      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
       </c>
@@ -18834,10 +18834,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>121112136</v>
+        <v>121112094</v>
       </c>
       <c r="B153" t="n">
-        <v>90662</v>
+        <v>78601</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -18846,25 +18846,25 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -18877,10 +18877,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>512407</v>
+        <v>512340</v>
       </c>
       <c r="R153" t="n">
-        <v>6728203</v>
+        <v>6728331</v>
       </c>
       <c r="S153" t="n">
         <v>5</v>
@@ -18950,10 +18950,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>121112119</v>
+        <v>121112191</v>
       </c>
       <c r="B154" t="n">
-        <v>90084</v>
+        <v>90697</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -18962,25 +18962,25 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>5685</v>
+        <v>1202</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -18993,10 +18993,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>512337</v>
+        <v>512504</v>
       </c>
       <c r="R154" t="n">
-        <v>6728307</v>
+        <v>6728184</v>
       </c>
       <c r="S154" t="n">
         <v>5</v>
@@ -19526,6 +19526,934 @@
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>121459568</v>
+      </c>
+      <c r="B159" t="n">
+        <v>91137</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
+      <c r="K159" t="inlineStr"/>
+      <c r="N159" t="inlineStr"/>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>Solberga, Insjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q159" t="n">
+        <v>512400</v>
+      </c>
+      <c r="R159" t="n">
+        <v>6728189</v>
+      </c>
+      <c r="S159" t="n">
+        <v>25</v>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>Ål</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="AB159" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AD159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF159" t="inlineStr"/>
+      <c r="AG159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT159" t="inlineStr"/>
+      <c r="AW159" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX159" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Paula Testad, Lars Johan Klockars</t>
+        </is>
+      </c>
+      <c r="AY159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>121459519</v>
+      </c>
+      <c r="B160" t="n">
+        <v>90662</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr"/>
+      <c r="N160" t="inlineStr"/>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>Solberga, Insjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q160" t="n">
+        <v>512484</v>
+      </c>
+      <c r="R160" t="n">
+        <v>6728298</v>
+      </c>
+      <c r="S160" t="n">
+        <v>25</v>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W160" t="inlineStr">
+        <is>
+          <t>Ål</t>
+        </is>
+      </c>
+      <c r="Y160" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="AB160" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AD160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF160" t="inlineStr"/>
+      <c r="AG160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT160" t="inlineStr"/>
+      <c r="AW160" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX160" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Paula Testad, Lars Johan Klockars</t>
+        </is>
+      </c>
+      <c r="AY160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>121459507</v>
+      </c>
+      <c r="B161" t="n">
+        <v>90697</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
+      <c r="N161" t="inlineStr"/>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>Solberga, Insjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q161" t="n">
+        <v>512458</v>
+      </c>
+      <c r="R161" t="n">
+        <v>6728308</v>
+      </c>
+      <c r="S161" t="n">
+        <v>25</v>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W161" t="inlineStr">
+        <is>
+          <t>Ål</t>
+        </is>
+      </c>
+      <c r="Y161" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="Z161" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="AB161" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AD161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF161" t="inlineStr"/>
+      <c r="AG161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT161" t="inlineStr"/>
+      <c r="AW161" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX161" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Paula Testad, Lars Johan Klockars</t>
+        </is>
+      </c>
+      <c r="AY161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>121459573</v>
+      </c>
+      <c r="B162" t="n">
+        <v>90662</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr"/>
+      <c r="K162" t="inlineStr"/>
+      <c r="N162" t="inlineStr"/>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>Solberga, Insjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q162" t="n">
+        <v>512405</v>
+      </c>
+      <c r="R162" t="n">
+        <v>6728193</v>
+      </c>
+      <c r="S162" t="n">
+        <v>25</v>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W162" t="inlineStr">
+        <is>
+          <t>Ål</t>
+        </is>
+      </c>
+      <c r="Y162" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AD162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF162" t="inlineStr"/>
+      <c r="AG162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT162" t="inlineStr"/>
+      <c r="AW162" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX162" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Paula Testad, Lars Johan Klockars</t>
+        </is>
+      </c>
+      <c r="AY162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>121459575</v>
+      </c>
+      <c r="B163" t="n">
+        <v>90662</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr"/>
+      <c r="N163" t="inlineStr"/>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>Solberga, Insjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q163" t="n">
+        <v>512450</v>
+      </c>
+      <c r="R163" t="n">
+        <v>6728160</v>
+      </c>
+      <c r="S163" t="n">
+        <v>25</v>
+      </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V163" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W163" t="inlineStr">
+        <is>
+          <t>Ål</t>
+        </is>
+      </c>
+      <c r="Y163" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="Z163" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="AB163" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AD163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF163" t="inlineStr"/>
+      <c r="AG163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT163" t="inlineStr"/>
+      <c r="AW163" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX163" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Paula Testad, Lars Johan Klockars</t>
+        </is>
+      </c>
+      <c r="AY163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>121459531</v>
+      </c>
+      <c r="B164" t="n">
+        <v>90662</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
+      <c r="K164" t="inlineStr"/>
+      <c r="N164" t="inlineStr"/>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>Solberga, Insjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q164" t="n">
+        <v>512403</v>
+      </c>
+      <c r="R164" t="n">
+        <v>6728176</v>
+      </c>
+      <c r="S164" t="n">
+        <v>25</v>
+      </c>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V164" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W164" t="inlineStr">
+        <is>
+          <t>Ål</t>
+        </is>
+      </c>
+      <c r="Y164" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="Z164" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="AB164" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AD164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF164" t="inlineStr"/>
+      <c r="AG164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT164" t="inlineStr"/>
+      <c r="AW164" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX164" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Paula Testad, Lars Johan Klockars</t>
+        </is>
+      </c>
+      <c r="AY164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>121459578</v>
+      </c>
+      <c r="B165" t="n">
+        <v>90697</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr"/>
+      <c r="N165" t="inlineStr"/>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>Solberga, Insjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q165" t="n">
+        <v>512438</v>
+      </c>
+      <c r="R165" t="n">
+        <v>6728147</v>
+      </c>
+      <c r="S165" t="n">
+        <v>25</v>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W165" t="inlineStr">
+        <is>
+          <t>Ål</t>
+        </is>
+      </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="AB165" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AD165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF165" t="inlineStr"/>
+      <c r="AG165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT165" t="inlineStr"/>
+      <c r="AW165" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX165" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Paula Testad, Lars Johan Klockars</t>
+        </is>
+      </c>
+      <c r="AY165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>121459581</v>
+      </c>
+      <c r="B166" t="n">
+        <v>90662</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr"/>
+      <c r="J166" t="inlineStr"/>
+      <c r="K166" t="inlineStr"/>
+      <c r="N166" t="inlineStr"/>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>Solberga, Insjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q166" t="n">
+        <v>512442</v>
+      </c>
+      <c r="R166" t="n">
+        <v>6728151</v>
+      </c>
+      <c r="S166" t="n">
+        <v>25</v>
+      </c>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V166" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W166" t="inlineStr">
+        <is>
+          <t>Ål</t>
+        </is>
+      </c>
+      <c r="Y166" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="Z166" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="AB166" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AD166" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE166" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF166" t="inlineStr"/>
+      <c r="AG166" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT166" t="inlineStr"/>
+      <c r="AW166" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX166" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Paula Testad, Lars Johan Klockars</t>
+        </is>
+      </c>
+      <c r="AY166" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49115-2023 artfynd.xlsx
+++ b/artfynd/A 49115-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY166"/>
+  <dimension ref="A1:AY167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20454,6 +20454,116 @@
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>121473644</v>
+      </c>
+      <c r="B167" t="n">
+        <v>78604</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" t="inlineStr"/>
+      <c r="N167" t="inlineStr"/>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>Solberga, Dlr</t>
+        </is>
+      </c>
+      <c r="Q167" t="n">
+        <v>512387</v>
+      </c>
+      <c r="R167" t="n">
+        <v>6728354</v>
+      </c>
+      <c r="S167" t="n">
+        <v>10</v>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W167" t="inlineStr">
+        <is>
+          <t>Ål</t>
+        </is>
+      </c>
+      <c r="Y167" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="AD167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF167" t="inlineStr"/>
+      <c r="AG167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT167" t="inlineStr"/>
+      <c r="AW167" t="inlineStr">
+        <is>
+          <t>Lars Johan Klockars</t>
+        </is>
+      </c>
+      <c r="AX167" t="inlineStr">
+        <is>
+          <t>Lars Johan Klockars</t>
+        </is>
+      </c>
+      <c r="AY167" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49115-2023 artfynd.xlsx
+++ b/artfynd/A 49115-2023 artfynd.xlsx
@@ -5420,7 +5420,7 @@
         <v>116227102</v>
       </c>
       <c r="B43" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         <v>116299476</v>
       </c>
       <c r="B47" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6036,7 +6036,7 @@
         <v>116299026</v>
       </c>
       <c r="B48" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Lars Johan Klockars, Paula Testad</t>
+          <t>Paula Testad, Lars Johan Klockars</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -6407,7 +6407,7 @@
         <v>116298843</v>
       </c>
       <c r="B51" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         <v>116299273</v>
       </c>
       <c r="B56" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Lars Johan Klockars, Paula Testad</t>
+          <t>Paula Testad, Lars Johan Klockars</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -7881,7 +7881,7 @@
         <v>116451411</v>
       </c>
       <c r="B63" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -14100,7 +14100,7 @@
         <v>118436002</v>
       </c>
       <c r="B115" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -14759,7 +14759,7 @@
         <v>118596386</v>
       </c>
       <c r="B120" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -15926,7 +15926,7 @@
         <v>119513652</v>
       </c>
       <c r="B129" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -18362,10 +18362,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>121112136</v>
+        <v>121112094</v>
       </c>
       <c r="B149" t="n">
-        <v>90662</v>
+        <v>78604</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -18374,25 +18374,25 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -18405,10 +18405,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>512407</v>
+        <v>512340</v>
       </c>
       <c r="R149" t="n">
-        <v>6728203</v>
+        <v>6728331</v>
       </c>
       <c r="S149" t="n">
         <v>5</v>
@@ -18478,10 +18478,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>121112119</v>
+        <v>121112136</v>
       </c>
       <c r="B150" t="n">
-        <v>90084</v>
+        <v>90674</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -18494,21 +18494,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>5685</v>
+        <v>5447</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -18521,10 +18521,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>512337</v>
+        <v>512407</v>
       </c>
       <c r="R150" t="n">
-        <v>6728307</v>
+        <v>6728203</v>
       </c>
       <c r="S150" t="n">
         <v>5</v>
@@ -18594,10 +18594,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>121112195</v>
+        <v>121112119</v>
       </c>
       <c r="B151" t="n">
-        <v>90697</v>
+        <v>90092</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -18606,25 +18606,25 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>1202</v>
+        <v>5685</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -18637,10 +18637,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>512504</v>
+        <v>512337</v>
       </c>
       <c r="R151" t="n">
-        <v>6728332</v>
+        <v>6728307</v>
       </c>
       <c r="S151" t="n">
         <v>5</v>
@@ -18710,10 +18710,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>121112147</v>
+        <v>121112195</v>
       </c>
       <c r="B152" t="n">
-        <v>57504</v>
+        <v>90709</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -18726,35 +18726,26 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr"/>
-      <c r="L152" t="inlineStr"/>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
@@ -18762,10 +18753,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>512452</v>
+        <v>512504</v>
       </c>
       <c r="R152" t="n">
-        <v>6728158</v>
+        <v>6728332</v>
       </c>
       <c r="S152" t="n">
         <v>5</v>
@@ -18806,6 +18797,7 @@
       <c r="AE152" t="b">
         <v>0</v>
       </c>
+      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
       </c>
@@ -18834,10 +18826,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>121112094</v>
+        <v>121112147</v>
       </c>
       <c r="B153" t="n">
-        <v>78601</v>
+        <v>57504</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -18850,26 +18842,35 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr"/>
-      <c r="J153" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
@@ -18877,10 +18878,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>512340</v>
+        <v>512452</v>
       </c>
       <c r="R153" t="n">
-        <v>6728331</v>
+        <v>6728158</v>
       </c>
       <c r="S153" t="n">
         <v>5</v>
@@ -18921,7 +18922,6 @@
       <c r="AE153" t="b">
         <v>0</v>
       </c>
-      <c r="AF153" t="inlineStr"/>
       <c r="AG153" t="b">
         <v>0</v>
       </c>
@@ -18953,7 +18953,7 @@
         <v>121112191</v>
       </c>
       <c r="B154" t="n">
-        <v>90697</v>
+        <v>90709</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -19069,7 +19069,7 @@
         <v>121112033</v>
       </c>
       <c r="B155" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -19185,7 +19185,7 @@
         <v>121439106</v>
       </c>
       <c r="B156" t="n">
-        <v>90983</v>
+        <v>90995</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -19288,10 +19288,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>121442191</v>
+        <v>121441224</v>
       </c>
       <c r="B157" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -19323,12 +19323,12 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K157" t="inlineStr"/>
@@ -19336,17 +19336,17 @@
       <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Solberga, Dlr</t>
+          <t>solberga, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>512406</v>
+        <v>512424</v>
       </c>
       <c r="R157" t="n">
-        <v>6728220</v>
+        <v>6728268</v>
       </c>
       <c r="S157" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -19388,35 +19388,25 @@
       <c r="AG157" t="b">
         <v>0</v>
       </c>
-      <c r="AH157" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI157" t="inlineStr">
-        <is>
-          <t>Gammal barrnaturskog</t>
-        </is>
-      </c>
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Paula Testad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Paula Testad, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn, Lisa Olson, Cecilia Rastad, Lars Johan Klockars, Paula Testad</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>121441224</v>
+        <v>121442191</v>
       </c>
       <c r="B158" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -19448,12 +19438,12 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>126</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K158" t="inlineStr"/>
@@ -19461,17 +19451,17 @@
       <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>solberga, Dlr</t>
+          <t>Solberga, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>512424</v>
+        <v>512406</v>
       </c>
       <c r="R158" t="n">
-        <v>6728268</v>
+        <v>6728220</v>
       </c>
       <c r="S158" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -19513,25 +19503,35 @@
       <c r="AG158" t="b">
         <v>0</v>
       </c>
+      <c r="AH158" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI158" t="inlineStr">
+        <is>
+          <t>Gammal barrnaturskog</t>
+        </is>
+      </c>
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Paula Testad</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Göran Ehn, Lisa Olson, Cecilia Rastad, Lars Johan Klockars, Paula Testad</t>
+          <t>Paula Testad, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>121459568</v>
+        <v>121459531</v>
       </c>
       <c r="B159" t="n">
-        <v>91137</v>
+        <v>90674</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -19540,25 +19540,25 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -19571,10 +19571,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>512400</v>
+        <v>512403</v>
       </c>
       <c r="R159" t="n">
-        <v>6728189</v>
+        <v>6728176</v>
       </c>
       <c r="S159" t="n">
         <v>25</v>
@@ -19606,7 +19606,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -19616,7 +19616,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -19644,10 +19644,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>121459519</v>
+        <v>121459575</v>
       </c>
       <c r="B160" t="n">
-        <v>90662</v>
+        <v>90674</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -19687,10 +19687,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>512484</v>
+        <v>512450</v>
       </c>
       <c r="R160" t="n">
-        <v>6728298</v>
+        <v>6728160</v>
       </c>
       <c r="S160" t="n">
         <v>25</v>
@@ -19722,7 +19722,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -19732,7 +19732,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -19760,10 +19760,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>121459507</v>
+        <v>121459581</v>
       </c>
       <c r="B161" t="n">
-        <v>90697</v>
+        <v>90674</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -19772,25 +19772,25 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -19803,10 +19803,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>512458</v>
+        <v>512442</v>
       </c>
       <c r="R161" t="n">
-        <v>6728308</v>
+        <v>6728151</v>
       </c>
       <c r="S161" t="n">
         <v>25</v>
@@ -19838,7 +19838,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -19848,7 +19848,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -19876,10 +19876,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>121459573</v>
+        <v>121459507</v>
       </c>
       <c r="B162" t="n">
-        <v>90662</v>
+        <v>90709</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -19888,25 +19888,25 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -19919,10 +19919,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>512405</v>
+        <v>512458</v>
       </c>
       <c r="R162" t="n">
-        <v>6728193</v>
+        <v>6728308</v>
       </c>
       <c r="S162" t="n">
         <v>25</v>
@@ -19954,7 +19954,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -19964,7 +19964,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -19992,10 +19992,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>121459575</v>
+        <v>121459573</v>
       </c>
       <c r="B163" t="n">
-        <v>90662</v>
+        <v>90674</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -20035,10 +20035,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>512450</v>
+        <v>512405</v>
       </c>
       <c r="R163" t="n">
-        <v>6728160</v>
+        <v>6728193</v>
       </c>
       <c r="S163" t="n">
         <v>25</v>
@@ -20070,7 +20070,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -20080,7 +20080,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -20108,10 +20108,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>121459531</v>
+        <v>121459519</v>
       </c>
       <c r="B164" t="n">
-        <v>90662</v>
+        <v>90674</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -20151,10 +20151,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>512403</v>
+        <v>512484</v>
       </c>
       <c r="R164" t="n">
-        <v>6728176</v>
+        <v>6728298</v>
       </c>
       <c r="S164" t="n">
         <v>25</v>
@@ -20186,7 +20186,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -20196,7 +20196,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -20224,10 +20224,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>121459578</v>
+        <v>121459568</v>
       </c>
       <c r="B165" t="n">
-        <v>90697</v>
+        <v>91149</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -20236,25 +20236,25 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -20267,10 +20267,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>512438</v>
+        <v>512400</v>
       </c>
       <c r="R165" t="n">
-        <v>6728147</v>
+        <v>6728189</v>
       </c>
       <c r="S165" t="n">
         <v>25</v>
@@ -20302,7 +20302,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -20312,7 +20312,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -20340,10 +20340,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>121459581</v>
+        <v>121459578</v>
       </c>
       <c r="B166" t="n">
-        <v>90662</v>
+        <v>90709</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -20352,25 +20352,25 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -20383,10 +20383,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>512442</v>
+        <v>512438</v>
       </c>
       <c r="R166" t="n">
-        <v>6728151</v>
+        <v>6728147</v>
       </c>
       <c r="S166" t="n">
         <v>25</v>
@@ -20418,7 +20418,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -20428,7 +20428,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD166" t="b">

--- a/artfynd/A 49115-2023 artfynd.xlsx
+++ b/artfynd/A 49115-2023 artfynd.xlsx
@@ -5420,7 +5420,7 @@
         <v>116227102</v>
       </c>
       <c r="B43" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         <v>116299476</v>
       </c>
       <c r="B47" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6036,7 +6036,7 @@
         <v>116299026</v>
       </c>
       <c r="B48" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6407,7 +6407,7 @@
         <v>116298843</v>
       </c>
       <c r="B51" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         <v>116299273</v>
       </c>
       <c r="B56" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7881,7 +7881,7 @@
         <v>116451411</v>
       </c>
       <c r="B63" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -14100,7 +14100,7 @@
         <v>118436002</v>
       </c>
       <c r="B115" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -14759,7 +14759,7 @@
         <v>118596386</v>
       </c>
       <c r="B120" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -15926,7 +15926,7 @@
         <v>119513652</v>
       </c>
       <c r="B129" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -18362,10 +18362,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>121112094</v>
+        <v>121112147</v>
       </c>
       <c r="B149" t="n">
-        <v>78604</v>
+        <v>57504</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -18378,26 +18378,35 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr"/>
-      <c r="J149" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
@@ -18405,10 +18414,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>512340</v>
+        <v>512452</v>
       </c>
       <c r="R149" t="n">
-        <v>6728331</v>
+        <v>6728158</v>
       </c>
       <c r="S149" t="n">
         <v>5</v>
@@ -18449,7 +18458,6 @@
       <c r="AE149" t="b">
         <v>0</v>
       </c>
-      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
       </c>
@@ -18478,10 +18486,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>121112136</v>
+        <v>121112191</v>
       </c>
       <c r="B150" t="n">
-        <v>90674</v>
+        <v>90710</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -18490,25 +18498,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -18521,10 +18529,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>512407</v>
+        <v>512504</v>
       </c>
       <c r="R150" t="n">
-        <v>6728203</v>
+        <v>6728184</v>
       </c>
       <c r="S150" t="n">
         <v>5</v>
@@ -18594,10 +18602,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>121112119</v>
+        <v>121112195</v>
       </c>
       <c r="B151" t="n">
-        <v>90092</v>
+        <v>90710</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -18606,25 +18614,25 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>5685</v>
+        <v>1202</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -18637,10 +18645,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>512337</v>
+        <v>512504</v>
       </c>
       <c r="R151" t="n">
-        <v>6728307</v>
+        <v>6728332</v>
       </c>
       <c r="S151" t="n">
         <v>5</v>
@@ -18710,10 +18718,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>121112195</v>
+        <v>121112136</v>
       </c>
       <c r="B152" t="n">
-        <v>90709</v>
+        <v>90675</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -18722,25 +18730,25 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -18753,10 +18761,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>512504</v>
+        <v>512407</v>
       </c>
       <c r="R152" t="n">
-        <v>6728332</v>
+        <v>6728203</v>
       </c>
       <c r="S152" t="n">
         <v>5</v>
@@ -18826,10 +18834,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>121112147</v>
+        <v>121112094</v>
       </c>
       <c r="B153" t="n">
-        <v>57504</v>
+        <v>78604</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -18842,35 +18850,26 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr"/>
-      <c r="L153" t="inlineStr"/>
-      <c r="M153" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
@@ -18878,10 +18877,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>512452</v>
+        <v>512340</v>
       </c>
       <c r="R153" t="n">
-        <v>6728158</v>
+        <v>6728331</v>
       </c>
       <c r="S153" t="n">
         <v>5</v>
@@ -18922,6 +18921,7 @@
       <c r="AE153" t="b">
         <v>0</v>
       </c>
+      <c r="AF153" t="inlineStr"/>
       <c r="AG153" t="b">
         <v>0</v>
       </c>
@@ -18950,10 +18950,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>121112191</v>
+        <v>121112119</v>
       </c>
       <c r="B154" t="n">
-        <v>90709</v>
+        <v>90093</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -18962,25 +18962,25 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>1202</v>
+        <v>5685</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -18993,10 +18993,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>512504</v>
+        <v>512337</v>
       </c>
       <c r="R154" t="n">
-        <v>6728184</v>
+        <v>6728307</v>
       </c>
       <c r="S154" t="n">
         <v>5</v>
@@ -19182,10 +19182,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>121439106</v>
+        <v>121442191</v>
       </c>
       <c r="B156" t="n">
-        <v>90995</v>
+        <v>98095</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -19194,30 +19194,39 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr"/>
-      <c r="J156" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr"/>
       <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
@@ -19225,13 +19234,13 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>512435</v>
+        <v>512406</v>
       </c>
       <c r="R156" t="n">
-        <v>6728146</v>
+        <v>6728220</v>
       </c>
       <c r="S156" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -19273,25 +19282,35 @@
       <c r="AG156" t="b">
         <v>0</v>
       </c>
+      <c r="AH156" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI156" t="inlineStr">
+        <is>
+          <t>Gammal barrnaturskog</t>
+        </is>
+      </c>
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Paula Testad</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Göran Ehn, Lisa Olson, Cecilia Rastad, Paula Testad, Lars Johan Klockars</t>
+          <t>Paula Testad, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>121441224</v>
+        <v>121439106</v>
       </c>
       <c r="B157" t="n">
-        <v>98094</v>
+        <v>90996</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -19300,50 +19319,41 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J157" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr"/>
-      <c r="L157" t="inlineStr"/>
       <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>solberga, Dlr</t>
+          <t>Solberga, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>512424</v>
+        <v>512435</v>
       </c>
       <c r="R157" t="n">
-        <v>6728268</v>
+        <v>6728146</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -19396,17 +19406,17 @@
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Göran Ehn, Lisa Olson, Cecilia Rastad, Lars Johan Klockars, Paula Testad</t>
+          <t>Göran Ehn, Lisa Olson, Cecilia Rastad, Paula Testad, Lars Johan Klockars</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>121442191</v>
+        <v>121441224</v>
       </c>
       <c r="B158" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -19438,12 +19448,12 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K158" t="inlineStr"/>
@@ -19451,17 +19461,17 @@
       <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Solberga, Dlr</t>
+          <t>solberga, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>512406</v>
+        <v>512424</v>
       </c>
       <c r="R158" t="n">
-        <v>6728220</v>
+        <v>6728268</v>
       </c>
       <c r="S158" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -19503,35 +19513,25 @@
       <c r="AG158" t="b">
         <v>0</v>
       </c>
-      <c r="AH158" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI158" t="inlineStr">
-        <is>
-          <t>Gammal barrnaturskog</t>
-        </is>
-      </c>
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Paula Testad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Paula Testad, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn, Lisa Olson, Cecilia Rastad, Lars Johan Klockars, Paula Testad</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>121459531</v>
+        <v>121459568</v>
       </c>
       <c r="B159" t="n">
-        <v>90674</v>
+        <v>91150</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -19540,25 +19540,25 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -19571,10 +19571,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>512403</v>
+        <v>512400</v>
       </c>
       <c r="R159" t="n">
-        <v>6728176</v>
+        <v>6728189</v>
       </c>
       <c r="S159" t="n">
         <v>25</v>
@@ -19606,7 +19606,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -19616,7 +19616,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -19644,10 +19644,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>121459575</v>
+        <v>121459581</v>
       </c>
       <c r="B160" t="n">
-        <v>90674</v>
+        <v>90675</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -19687,10 +19687,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>512450</v>
+        <v>512442</v>
       </c>
       <c r="R160" t="n">
-        <v>6728160</v>
+        <v>6728151</v>
       </c>
       <c r="S160" t="n">
         <v>25</v>
@@ -19722,7 +19722,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -19732,7 +19732,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -19760,10 +19760,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>121459581</v>
+        <v>121459531</v>
       </c>
       <c r="B161" t="n">
-        <v>90674</v>
+        <v>90675</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -19803,10 +19803,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>512442</v>
+        <v>512403</v>
       </c>
       <c r="R161" t="n">
-        <v>6728151</v>
+        <v>6728176</v>
       </c>
       <c r="S161" t="n">
         <v>25</v>
@@ -19838,7 +19838,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -19848,7 +19848,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -19876,10 +19876,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>121459507</v>
+        <v>121459519</v>
       </c>
       <c r="B162" t="n">
-        <v>90709</v>
+        <v>90675</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -19888,25 +19888,25 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -19919,10 +19919,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>512458</v>
+        <v>512484</v>
       </c>
       <c r="R162" t="n">
-        <v>6728308</v>
+        <v>6728298</v>
       </c>
       <c r="S162" t="n">
         <v>25</v>
@@ -19954,7 +19954,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -19964,7 +19964,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -19992,10 +19992,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>121459573</v>
+        <v>121459575</v>
       </c>
       <c r="B163" t="n">
-        <v>90674</v>
+        <v>90675</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -20035,10 +20035,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>512405</v>
+        <v>512450</v>
       </c>
       <c r="R163" t="n">
-        <v>6728193</v>
+        <v>6728160</v>
       </c>
       <c r="S163" t="n">
         <v>25</v>
@@ -20070,7 +20070,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -20080,7 +20080,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -20108,10 +20108,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>121459519</v>
+        <v>121459507</v>
       </c>
       <c r="B164" t="n">
-        <v>90674</v>
+        <v>90710</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -20120,25 +20120,25 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -20151,10 +20151,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>512484</v>
+        <v>512458</v>
       </c>
       <c r="R164" t="n">
-        <v>6728298</v>
+        <v>6728308</v>
       </c>
       <c r="S164" t="n">
         <v>25</v>
@@ -20186,7 +20186,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -20196,7 +20196,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -20224,10 +20224,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>121459568</v>
+        <v>121459578</v>
       </c>
       <c r="B165" t="n">
-        <v>91149</v>
+        <v>90710</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -20236,25 +20236,25 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -20267,10 +20267,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>512400</v>
+        <v>512438</v>
       </c>
       <c r="R165" t="n">
-        <v>6728189</v>
+        <v>6728147</v>
       </c>
       <c r="S165" t="n">
         <v>25</v>
@@ -20302,7 +20302,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -20312,7 +20312,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -20340,10 +20340,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>121459578</v>
+        <v>121459573</v>
       </c>
       <c r="B166" t="n">
-        <v>90709</v>
+        <v>90675</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -20352,25 +20352,25 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -20383,10 +20383,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>512438</v>
+        <v>512405</v>
       </c>
       <c r="R166" t="n">
-        <v>6728147</v>
+        <v>6728193</v>
       </c>
       <c r="S166" t="n">
         <v>25</v>
@@ -20418,7 +20418,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -20428,7 +20428,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD166" t="b">

--- a/artfynd/A 49115-2023 artfynd.xlsx
+++ b/artfynd/A 49115-2023 artfynd.xlsx
@@ -5420,7 +5420,7 @@
         <v>116227102</v>
       </c>
       <c r="B43" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         <v>116299476</v>
       </c>
       <c r="B47" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6036,7 +6036,7 @@
         <v>116299026</v>
       </c>
       <c r="B48" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6407,7 +6407,7 @@
         <v>116298843</v>
       </c>
       <c r="B51" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         <v>116299273</v>
       </c>
       <c r="B56" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7881,7 +7881,7 @@
         <v>116451411</v>
       </c>
       <c r="B63" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -14100,7 +14100,7 @@
         <v>118436002</v>
       </c>
       <c r="B115" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -14759,7 +14759,7 @@
         <v>118596386</v>
       </c>
       <c r="B120" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -15926,7 +15926,7 @@
         <v>119513652</v>
       </c>
       <c r="B129" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -18362,10 +18362,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>121112147</v>
+        <v>121112195</v>
       </c>
       <c r="B149" t="n">
-        <v>57504</v>
+        <v>90713</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -18378,35 +18378,26 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr"/>
-      <c r="L149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
@@ -18414,10 +18405,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>512452</v>
+        <v>512504</v>
       </c>
       <c r="R149" t="n">
-        <v>6728158</v>
+        <v>6728332</v>
       </c>
       <c r="S149" t="n">
         <v>5</v>
@@ -18458,6 +18449,7 @@
       <c r="AE149" t="b">
         <v>0</v>
       </c>
+      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
       </c>
@@ -18486,10 +18478,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>121112191</v>
+        <v>121112119</v>
       </c>
       <c r="B150" t="n">
-        <v>90710</v>
+        <v>90096</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -18498,25 +18490,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1202</v>
+        <v>5685</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -18529,10 +18521,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>512504</v>
+        <v>512337</v>
       </c>
       <c r="R150" t="n">
-        <v>6728184</v>
+        <v>6728307</v>
       </c>
       <c r="S150" t="n">
         <v>5</v>
@@ -18602,10 +18594,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>121112195</v>
+        <v>121112136</v>
       </c>
       <c r="B151" t="n">
-        <v>90710</v>
+        <v>90678</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -18614,25 +18606,25 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -18645,10 +18637,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>512504</v>
+        <v>512407</v>
       </c>
       <c r="R151" t="n">
-        <v>6728332</v>
+        <v>6728203</v>
       </c>
       <c r="S151" t="n">
         <v>5</v>
@@ -18718,10 +18710,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>121112136</v>
+        <v>121112191</v>
       </c>
       <c r="B152" t="n">
-        <v>90675</v>
+        <v>90713</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -18730,25 +18722,25 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -18761,10 +18753,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>512407</v>
+        <v>512504</v>
       </c>
       <c r="R152" t="n">
-        <v>6728203</v>
+        <v>6728184</v>
       </c>
       <c r="S152" t="n">
         <v>5</v>
@@ -18837,7 +18829,7 @@
         <v>121112094</v>
       </c>
       <c r="B153" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -18950,10 +18942,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>121112119</v>
+        <v>121112147</v>
       </c>
       <c r="B154" t="n">
-        <v>90093</v>
+        <v>57507</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -18962,30 +18954,39 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>5685</v>
+        <v>103021</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr"/>
-      <c r="J154" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
@@ -18993,10 +18994,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>512337</v>
+        <v>512452</v>
       </c>
       <c r="R154" t="n">
-        <v>6728307</v>
+        <v>6728158</v>
       </c>
       <c r="S154" t="n">
         <v>5</v>
@@ -19037,7 +19038,6 @@
       <c r="AE154" t="b">
         <v>0</v>
       </c>
-      <c r="AF154" t="inlineStr"/>
       <c r="AG154" t="b">
         <v>0</v>
       </c>
@@ -19069,7 +19069,7 @@
         <v>121112033</v>
       </c>
       <c r="B155" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -19182,10 +19182,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>121442191</v>
+        <v>121439106</v>
       </c>
       <c r="B156" t="n">
-        <v>98095</v>
+        <v>90999</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -19194,39 +19194,30 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="J156" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr"/>
-      <c r="L156" t="inlineStr"/>
       <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
@@ -19234,13 +19225,13 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>512406</v>
+        <v>512435</v>
       </c>
       <c r="R156" t="n">
-        <v>6728220</v>
+        <v>6728146</v>
       </c>
       <c r="S156" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -19282,35 +19273,25 @@
       <c r="AG156" t="b">
         <v>0</v>
       </c>
-      <c r="AH156" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI156" t="inlineStr">
-        <is>
-          <t>Gammal barrnaturskog</t>
-        </is>
-      </c>
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Paula Testad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Paula Testad, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn, Lisa Olson, Cecilia Rastad, Paula Testad, Lars Johan Klockars</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>121439106</v>
+        <v>121442191</v>
       </c>
       <c r="B157" t="n">
-        <v>90996</v>
+        <v>98098</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -19319,30 +19300,39 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr"/>
-      <c r="J157" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr"/>
       <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
@@ -19350,13 +19340,13 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>512435</v>
+        <v>512406</v>
       </c>
       <c r="R157" t="n">
-        <v>6728146</v>
+        <v>6728220</v>
       </c>
       <c r="S157" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -19398,15 +19388,25 @@
       <c r="AG157" t="b">
         <v>0</v>
       </c>
+      <c r="AH157" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI157" t="inlineStr">
+        <is>
+          <t>Gammal barrnaturskog</t>
+        </is>
+      </c>
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Paula Testad</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Göran Ehn, Lisa Olson, Cecilia Rastad, Paula Testad, Lars Johan Klockars</t>
+          <t>Paula Testad, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
@@ -19416,7 +19416,7 @@
         <v>121441224</v>
       </c>
       <c r="B158" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -19528,10 +19528,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>121459568</v>
+        <v>121459507</v>
       </c>
       <c r="B159" t="n">
-        <v>91150</v>
+        <v>90713</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -19540,25 +19540,25 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -19571,10 +19571,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>512400</v>
+        <v>512458</v>
       </c>
       <c r="R159" t="n">
-        <v>6728189</v>
+        <v>6728308</v>
       </c>
       <c r="S159" t="n">
         <v>25</v>
@@ -19606,7 +19606,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -19616,7 +19616,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -19644,10 +19644,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>121459581</v>
+        <v>121459531</v>
       </c>
       <c r="B160" t="n">
-        <v>90675</v>
+        <v>90678</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -19687,10 +19687,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>512442</v>
+        <v>512403</v>
       </c>
       <c r="R160" t="n">
-        <v>6728151</v>
+        <v>6728176</v>
       </c>
       <c r="S160" t="n">
         <v>25</v>
@@ -19722,7 +19722,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -19732,7 +19732,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -19760,10 +19760,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>121459531</v>
+        <v>121459575</v>
       </c>
       <c r="B161" t="n">
-        <v>90675</v>
+        <v>90678</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -19803,10 +19803,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>512403</v>
+        <v>512450</v>
       </c>
       <c r="R161" t="n">
-        <v>6728176</v>
+        <v>6728160</v>
       </c>
       <c r="S161" t="n">
         <v>25</v>
@@ -19838,7 +19838,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -19848,7 +19848,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -19876,10 +19876,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>121459519</v>
+        <v>121459581</v>
       </c>
       <c r="B162" t="n">
-        <v>90675</v>
+        <v>90678</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -19919,10 +19919,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>512484</v>
+        <v>512442</v>
       </c>
       <c r="R162" t="n">
-        <v>6728298</v>
+        <v>6728151</v>
       </c>
       <c r="S162" t="n">
         <v>25</v>
@@ -19954,7 +19954,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -19964,7 +19964,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -19992,10 +19992,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>121459575</v>
+        <v>121459568</v>
       </c>
       <c r="B163" t="n">
-        <v>90675</v>
+        <v>91153</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -20004,25 +20004,25 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -20035,10 +20035,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>512450</v>
+        <v>512400</v>
       </c>
       <c r="R163" t="n">
-        <v>6728160</v>
+        <v>6728189</v>
       </c>
       <c r="S163" t="n">
         <v>25</v>
@@ -20070,7 +20070,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -20080,7 +20080,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -20108,10 +20108,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>121459507</v>
+        <v>121459573</v>
       </c>
       <c r="B164" t="n">
-        <v>90710</v>
+        <v>90678</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -20120,25 +20120,25 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -20151,10 +20151,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>512458</v>
+        <v>512405</v>
       </c>
       <c r="R164" t="n">
-        <v>6728308</v>
+        <v>6728193</v>
       </c>
       <c r="S164" t="n">
         <v>25</v>
@@ -20186,7 +20186,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -20196,7 +20196,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -20227,7 +20227,7 @@
         <v>121459578</v>
       </c>
       <c r="B165" t="n">
-        <v>90710</v>
+        <v>90713</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -20340,10 +20340,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>121459573</v>
+        <v>121459519</v>
       </c>
       <c r="B166" t="n">
-        <v>90675</v>
+        <v>90678</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -20383,10 +20383,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>512405</v>
+        <v>512484</v>
       </c>
       <c r="R166" t="n">
-        <v>6728193</v>
+        <v>6728298</v>
       </c>
       <c r="S166" t="n">
         <v>25</v>
@@ -20418,7 +20418,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -20428,7 +20428,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -20459,7 +20459,7 @@
         <v>121473644</v>
       </c>
       <c r="B167" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>

--- a/artfynd/A 49115-2023 artfynd.xlsx
+++ b/artfynd/A 49115-2023 artfynd.xlsx
@@ -18362,10 +18362,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>121112195</v>
+        <v>121112119</v>
       </c>
       <c r="B149" t="n">
-        <v>90713</v>
+        <v>90096</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -18374,25 +18374,25 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>1202</v>
+        <v>5685</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -18405,10 +18405,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>512504</v>
+        <v>512337</v>
       </c>
       <c r="R149" t="n">
-        <v>6728332</v>
+        <v>6728307</v>
       </c>
       <c r="S149" t="n">
         <v>5</v>
@@ -18478,10 +18478,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>121112119</v>
+        <v>121112191</v>
       </c>
       <c r="B150" t="n">
-        <v>90096</v>
+        <v>90713</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -18490,25 +18490,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>5685</v>
+        <v>1202</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -18521,10 +18521,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>512337</v>
+        <v>512504</v>
       </c>
       <c r="R150" t="n">
-        <v>6728307</v>
+        <v>6728184</v>
       </c>
       <c r="S150" t="n">
         <v>5</v>
@@ -18710,10 +18710,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>121112191</v>
+        <v>121112094</v>
       </c>
       <c r="B152" t="n">
-        <v>90713</v>
+        <v>78607</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -18726,21 +18726,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -18753,10 +18753,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>512504</v>
+        <v>512340</v>
       </c>
       <c r="R152" t="n">
-        <v>6728184</v>
+        <v>6728331</v>
       </c>
       <c r="S152" t="n">
         <v>5</v>
@@ -18826,10 +18826,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>121112094</v>
+        <v>121112147</v>
       </c>
       <c r="B153" t="n">
-        <v>78607</v>
+        <v>57507</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -18842,26 +18842,35 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr"/>
-      <c r="J153" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
@@ -18869,10 +18878,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>512340</v>
+        <v>512452</v>
       </c>
       <c r="R153" t="n">
-        <v>6728331</v>
+        <v>6728158</v>
       </c>
       <c r="S153" t="n">
         <v>5</v>
@@ -18913,7 +18922,6 @@
       <c r="AE153" t="b">
         <v>0</v>
       </c>
-      <c r="AF153" t="inlineStr"/>
       <c r="AG153" t="b">
         <v>0</v>
       </c>
@@ -18942,10 +18950,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>121112147</v>
+        <v>121112195</v>
       </c>
       <c r="B154" t="n">
-        <v>57507</v>
+        <v>90713</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -18958,35 +18966,26 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr"/>
-      <c r="L154" t="inlineStr"/>
-      <c r="M154" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
@@ -18994,10 +18993,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>512452</v>
+        <v>512504</v>
       </c>
       <c r="R154" t="n">
-        <v>6728158</v>
+        <v>6728332</v>
       </c>
       <c r="S154" t="n">
         <v>5</v>
@@ -19038,6 +19037,7 @@
       <c r="AE154" t="b">
         <v>0</v>
       </c>
+      <c r="AF154" t="inlineStr"/>
       <c r="AG154" t="b">
         <v>0</v>
       </c>
@@ -19288,7 +19288,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>121442191</v>
+        <v>121441224</v>
       </c>
       <c r="B157" t="n">
         <v>98098</v>
@@ -19323,12 +19323,12 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K157" t="inlineStr"/>
@@ -19336,17 +19336,17 @@
       <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Solberga, Dlr</t>
+          <t>solberga, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>512406</v>
+        <v>512424</v>
       </c>
       <c r="R157" t="n">
-        <v>6728220</v>
+        <v>6728268</v>
       </c>
       <c r="S157" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -19388,32 +19388,22 @@
       <c r="AG157" t="b">
         <v>0</v>
       </c>
-      <c r="AH157" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI157" t="inlineStr">
-        <is>
-          <t>Gammal barrnaturskog</t>
-        </is>
-      </c>
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Paula Testad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Paula Testad, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn, Lisa Olson, Cecilia Rastad, Lars Johan Klockars, Paula Testad</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>121441224</v>
+        <v>121442191</v>
       </c>
       <c r="B158" t="n">
         <v>98098</v>
@@ -19448,12 +19438,12 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>126</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K158" t="inlineStr"/>
@@ -19461,17 +19451,17 @@
       <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>solberga, Dlr</t>
+          <t>Solberga, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>512424</v>
+        <v>512406</v>
       </c>
       <c r="R158" t="n">
-        <v>6728268</v>
+        <v>6728220</v>
       </c>
       <c r="S158" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -19513,15 +19503,25 @@
       <c r="AG158" t="b">
         <v>0</v>
       </c>
+      <c r="AH158" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI158" t="inlineStr">
+        <is>
+          <t>Gammal barrnaturskog</t>
+        </is>
+      </c>
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Paula Testad</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Göran Ehn, Lisa Olson, Cecilia Rastad, Lars Johan Klockars, Paula Testad</t>
+          <t>Paula Testad, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
@@ -19760,7 +19760,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>121459575</v>
+        <v>121459519</v>
       </c>
       <c r="B161" t="n">
         <v>90678</v>
@@ -19803,10 +19803,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>512450</v>
+        <v>512484</v>
       </c>
       <c r="R161" t="n">
-        <v>6728160</v>
+        <v>6728298</v>
       </c>
       <c r="S161" t="n">
         <v>25</v>
@@ -19838,7 +19838,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -19848,7 +19848,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -19876,10 +19876,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>121459581</v>
+        <v>121459568</v>
       </c>
       <c r="B162" t="n">
-        <v>90678</v>
+        <v>91153</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -19888,25 +19888,25 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -19919,10 +19919,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>512442</v>
+        <v>512400</v>
       </c>
       <c r="R162" t="n">
-        <v>6728151</v>
+        <v>6728189</v>
       </c>
       <c r="S162" t="n">
         <v>25</v>
@@ -19954,7 +19954,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -19964,7 +19964,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -19992,10 +19992,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>121459568</v>
+        <v>121459581</v>
       </c>
       <c r="B163" t="n">
-        <v>91153</v>
+        <v>90678</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -20004,25 +20004,25 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -20035,10 +20035,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>512400</v>
+        <v>512442</v>
       </c>
       <c r="R163" t="n">
-        <v>6728189</v>
+        <v>6728151</v>
       </c>
       <c r="S163" t="n">
         <v>25</v>
@@ -20070,7 +20070,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -20080,7 +20080,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -20108,7 +20108,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>121459573</v>
+        <v>121459575</v>
       </c>
       <c r="B164" t="n">
         <v>90678</v>
@@ -20151,10 +20151,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>512405</v>
+        <v>512450</v>
       </c>
       <c r="R164" t="n">
-        <v>6728193</v>
+        <v>6728160</v>
       </c>
       <c r="S164" t="n">
         <v>25</v>
@@ -20186,7 +20186,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -20196,7 +20196,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -20224,10 +20224,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>121459578</v>
+        <v>121459573</v>
       </c>
       <c r="B165" t="n">
-        <v>90713</v>
+        <v>90678</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -20236,25 +20236,25 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -20267,10 +20267,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>512438</v>
+        <v>512405</v>
       </c>
       <c r="R165" t="n">
-        <v>6728147</v>
+        <v>6728193</v>
       </c>
       <c r="S165" t="n">
         <v>25</v>
@@ -20302,7 +20302,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -20312,7 +20312,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -20340,10 +20340,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>121459519</v>
+        <v>121459578</v>
       </c>
       <c r="B166" t="n">
-        <v>90678</v>
+        <v>90713</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -20352,25 +20352,25 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -20383,10 +20383,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>512484</v>
+        <v>512438</v>
       </c>
       <c r="R166" t="n">
-        <v>6728298</v>
+        <v>6728147</v>
       </c>
       <c r="S166" t="n">
         <v>25</v>
@@ -20418,7 +20418,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -20428,7 +20428,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD166" t="b">

--- a/artfynd/A 49115-2023 artfynd.xlsx
+++ b/artfynd/A 49115-2023 artfynd.xlsx
@@ -19069,7 +19069,7 @@
         <v>121112033</v>
       </c>
       <c r="B155" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -19182,10 +19182,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>121439106</v>
+        <v>121441224</v>
       </c>
       <c r="B156" t="n">
-        <v>90999</v>
+        <v>98104</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -19194,41 +19194,50 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr"/>
-      <c r="J156" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr"/>
       <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Solberga, Dlr</t>
+          <t>solberga, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>512435</v>
+        <v>512424</v>
       </c>
       <c r="R156" t="n">
-        <v>6728146</v>
+        <v>6728268</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -19281,17 +19290,17 @@
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Göran Ehn, Lisa Olson, Cecilia Rastad, Paula Testad, Lars Johan Klockars</t>
+          <t>Göran Ehn, Lisa Olson, Cecilia Rastad, Lars Johan Klockars, Paula Testad</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>121441224</v>
+        <v>121442191</v>
       </c>
       <c r="B157" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -19323,12 +19332,12 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>126</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K157" t="inlineStr"/>
@@ -19336,17 +19345,17 @@
       <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>solberga, Dlr</t>
+          <t>Solberga, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>512424</v>
+        <v>512406</v>
       </c>
       <c r="R157" t="n">
-        <v>6728268</v>
+        <v>6728220</v>
       </c>
       <c r="S157" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -19388,25 +19397,35 @@
       <c r="AG157" t="b">
         <v>0</v>
       </c>
+      <c r="AH157" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI157" t="inlineStr">
+        <is>
+          <t>Gammal barrnaturskog</t>
+        </is>
+      </c>
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Paula Testad</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Göran Ehn, Lisa Olson, Cecilia Rastad, Lars Johan Klockars, Paula Testad</t>
+          <t>Paula Testad, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>121442191</v>
+        <v>121439106</v>
       </c>
       <c r="B158" t="n">
-        <v>98098</v>
+        <v>91005</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -19415,39 +19434,30 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="J158" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr"/>
-      <c r="L158" t="inlineStr"/>
       <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
@@ -19455,13 +19465,13 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>512406</v>
+        <v>512435</v>
       </c>
       <c r="R158" t="n">
-        <v>6728220</v>
+        <v>6728146</v>
       </c>
       <c r="S158" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -19503,35 +19513,25 @@
       <c r="AG158" t="b">
         <v>0</v>
       </c>
-      <c r="AH158" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI158" t="inlineStr">
-        <is>
-          <t>Gammal barrnaturskog</t>
-        </is>
-      </c>
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Paula Testad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Paula Testad, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn, Lisa Olson, Cecilia Rastad, Paula Testad, Lars Johan Klockars</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>121459507</v>
+        <v>121459568</v>
       </c>
       <c r="B159" t="n">
-        <v>90713</v>
+        <v>91159</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -19540,25 +19540,25 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -19571,10 +19571,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>512458</v>
+        <v>512400</v>
       </c>
       <c r="R159" t="n">
-        <v>6728308</v>
+        <v>6728189</v>
       </c>
       <c r="S159" t="n">
         <v>25</v>
@@ -19606,7 +19606,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -19616,7 +19616,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -19644,10 +19644,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>121459531</v>
+        <v>121459519</v>
       </c>
       <c r="B160" t="n">
-        <v>90678</v>
+        <v>90684</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -19687,10 +19687,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>512403</v>
+        <v>512484</v>
       </c>
       <c r="R160" t="n">
-        <v>6728176</v>
+        <v>6728298</v>
       </c>
       <c r="S160" t="n">
         <v>25</v>
@@ -19722,7 +19722,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -19732,7 +19732,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -19760,10 +19760,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>121459519</v>
+        <v>121459578</v>
       </c>
       <c r="B161" t="n">
-        <v>90678</v>
+        <v>90719</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -19772,25 +19772,25 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -19803,10 +19803,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>512484</v>
+        <v>512438</v>
       </c>
       <c r="R161" t="n">
-        <v>6728298</v>
+        <v>6728147</v>
       </c>
       <c r="S161" t="n">
         <v>25</v>
@@ -19838,7 +19838,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -19848,7 +19848,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -19876,10 +19876,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>121459568</v>
+        <v>121459507</v>
       </c>
       <c r="B162" t="n">
-        <v>91153</v>
+        <v>90719</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -19888,25 +19888,25 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -19919,10 +19919,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>512400</v>
+        <v>512458</v>
       </c>
       <c r="R162" t="n">
-        <v>6728189</v>
+        <v>6728308</v>
       </c>
       <c r="S162" t="n">
         <v>25</v>
@@ -19954,7 +19954,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -19964,7 +19964,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -19992,10 +19992,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>121459581</v>
+        <v>121459573</v>
       </c>
       <c r="B163" t="n">
-        <v>90678</v>
+        <v>90684</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -20035,10 +20035,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>512442</v>
+        <v>512405</v>
       </c>
       <c r="R163" t="n">
-        <v>6728151</v>
+        <v>6728193</v>
       </c>
       <c r="S163" t="n">
         <v>25</v>
@@ -20070,7 +20070,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -20080,7 +20080,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -20108,10 +20108,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>121459575</v>
+        <v>121459581</v>
       </c>
       <c r="B164" t="n">
-        <v>90678</v>
+        <v>90684</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -20151,10 +20151,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>512450</v>
+        <v>512442</v>
       </c>
       <c r="R164" t="n">
-        <v>6728160</v>
+        <v>6728151</v>
       </c>
       <c r="S164" t="n">
         <v>25</v>
@@ -20186,7 +20186,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -20196,7 +20196,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -20224,10 +20224,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>121459573</v>
+        <v>121459531</v>
       </c>
       <c r="B165" t="n">
-        <v>90678</v>
+        <v>90684</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -20267,10 +20267,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>512405</v>
+        <v>512403</v>
       </c>
       <c r="R165" t="n">
-        <v>6728193</v>
+        <v>6728176</v>
       </c>
       <c r="S165" t="n">
         <v>25</v>
@@ -20302,7 +20302,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -20312,7 +20312,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -20340,10 +20340,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>121459578</v>
+        <v>121459575</v>
       </c>
       <c r="B166" t="n">
-        <v>90713</v>
+        <v>90684</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -20352,25 +20352,25 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -20383,10 +20383,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>512438</v>
+        <v>512450</v>
       </c>
       <c r="R166" t="n">
-        <v>6728147</v>
+        <v>6728160</v>
       </c>
       <c r="S166" t="n">
         <v>25</v>
@@ -20418,7 +20418,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -20428,7 +20428,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -20459,7 +20459,7 @@
         <v>121473644</v>
       </c>
       <c r="B167" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>

--- a/artfynd/A 49115-2023 artfynd.xlsx
+++ b/artfynd/A 49115-2023 artfynd.xlsx
@@ -19185,7 +19185,7 @@
         <v>121441224</v>
       </c>
       <c r="B156" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -19300,7 +19300,7 @@
         <v>121442191</v>
       </c>
       <c r="B157" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -19425,7 +19425,7 @@
         <v>121439106</v>
       </c>
       <c r="B158" t="n">
-        <v>91005</v>
+        <v>91006</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -19528,10 +19528,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>121459568</v>
+        <v>121459519</v>
       </c>
       <c r="B159" t="n">
-        <v>91159</v>
+        <v>90685</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -19540,25 +19540,25 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -19571,10 +19571,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>512400</v>
+        <v>512484</v>
       </c>
       <c r="R159" t="n">
-        <v>6728189</v>
+        <v>6728298</v>
       </c>
       <c r="S159" t="n">
         <v>25</v>
@@ -19606,7 +19606,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -19616,7 +19616,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -19644,10 +19644,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>121459519</v>
+        <v>121459575</v>
       </c>
       <c r="B160" t="n">
-        <v>90684</v>
+        <v>90685</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -19687,10 +19687,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>512484</v>
+        <v>512450</v>
       </c>
       <c r="R160" t="n">
-        <v>6728298</v>
+        <v>6728160</v>
       </c>
       <c r="S160" t="n">
         <v>25</v>
@@ -19722,7 +19722,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -19732,7 +19732,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -19760,10 +19760,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>121459578</v>
+        <v>121459531</v>
       </c>
       <c r="B161" t="n">
-        <v>90719</v>
+        <v>90685</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -19772,25 +19772,25 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -19803,10 +19803,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>512438</v>
+        <v>512403</v>
       </c>
       <c r="R161" t="n">
-        <v>6728147</v>
+        <v>6728176</v>
       </c>
       <c r="S161" t="n">
         <v>25</v>
@@ -19838,7 +19838,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -19848,7 +19848,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -19876,10 +19876,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>121459507</v>
+        <v>121459581</v>
       </c>
       <c r="B162" t="n">
-        <v>90719</v>
+        <v>90685</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -19888,25 +19888,25 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -19919,10 +19919,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>512458</v>
+        <v>512442</v>
       </c>
       <c r="R162" t="n">
-        <v>6728308</v>
+        <v>6728151</v>
       </c>
       <c r="S162" t="n">
         <v>25</v>
@@ -19954,7 +19954,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -19964,7 +19964,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -19992,10 +19992,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>121459573</v>
+        <v>121459568</v>
       </c>
       <c r="B163" t="n">
-        <v>90684</v>
+        <v>91160</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -20004,25 +20004,25 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -20035,10 +20035,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>512405</v>
+        <v>512400</v>
       </c>
       <c r="R163" t="n">
-        <v>6728193</v>
+        <v>6728189</v>
       </c>
       <c r="S163" t="n">
         <v>25</v>
@@ -20070,7 +20070,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -20080,7 +20080,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -20108,10 +20108,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>121459581</v>
+        <v>121459507</v>
       </c>
       <c r="B164" t="n">
-        <v>90684</v>
+        <v>90720</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -20120,25 +20120,25 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -20151,10 +20151,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>512442</v>
+        <v>512458</v>
       </c>
       <c r="R164" t="n">
-        <v>6728151</v>
+        <v>6728308</v>
       </c>
       <c r="S164" t="n">
         <v>25</v>
@@ -20186,7 +20186,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -20196,7 +20196,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -20224,10 +20224,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>121459531</v>
+        <v>121459573</v>
       </c>
       <c r="B165" t="n">
-        <v>90684</v>
+        <v>90685</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -20267,10 +20267,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>512403</v>
+        <v>512405</v>
       </c>
       <c r="R165" t="n">
-        <v>6728176</v>
+        <v>6728193</v>
       </c>
       <c r="S165" t="n">
         <v>25</v>
@@ -20302,7 +20302,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -20312,7 +20312,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -20340,10 +20340,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>121459575</v>
+        <v>121459578</v>
       </c>
       <c r="B166" t="n">
-        <v>90684</v>
+        <v>90720</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -20352,25 +20352,25 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -20383,10 +20383,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>512450</v>
+        <v>512438</v>
       </c>
       <c r="R166" t="n">
-        <v>6728160</v>
+        <v>6728147</v>
       </c>
       <c r="S166" t="n">
         <v>25</v>
@@ -20418,7 +20418,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -20428,7 +20428,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -20459,7 +20459,7 @@
         <v>121473644</v>
       </c>
       <c r="B167" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>

--- a/artfynd/A 49115-2023 artfynd.xlsx
+++ b/artfynd/A 49115-2023 artfynd.xlsx
@@ -19182,7 +19182,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>121441224</v>
+        <v>121442191</v>
       </c>
       <c r="B156" t="n">
         <v>98105</v>
@@ -19217,12 +19217,12 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>126</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K156" t="inlineStr"/>
@@ -19230,17 +19230,17 @@
       <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>solberga, Dlr</t>
+          <t>Solberga, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>512424</v>
+        <v>512406</v>
       </c>
       <c r="R156" t="n">
-        <v>6728268</v>
+        <v>6728220</v>
       </c>
       <c r="S156" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -19282,25 +19282,35 @@
       <c r="AG156" t="b">
         <v>0</v>
       </c>
+      <c r="AH156" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI156" t="inlineStr">
+        <is>
+          <t>Gammal barrnaturskog</t>
+        </is>
+      </c>
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Paula Testad</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Göran Ehn, Lisa Olson, Cecilia Rastad, Lars Johan Klockars, Paula Testad</t>
+          <t>Paula Testad, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>121442191</v>
+        <v>121439106</v>
       </c>
       <c r="B157" t="n">
-        <v>98105</v>
+        <v>91006</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -19309,39 +19319,30 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="J157" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr"/>
-      <c r="L157" t="inlineStr"/>
       <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
@@ -19349,13 +19350,13 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>512406</v>
+        <v>512435</v>
       </c>
       <c r="R157" t="n">
-        <v>6728220</v>
+        <v>6728146</v>
       </c>
       <c r="S157" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -19397,35 +19398,25 @@
       <c r="AG157" t="b">
         <v>0</v>
       </c>
-      <c r="AH157" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI157" t="inlineStr">
-        <is>
-          <t>Gammal barrnaturskog</t>
-        </is>
-      </c>
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Paula Testad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Paula Testad, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn, Lisa Olson, Cecilia Rastad, Paula Testad, Lars Johan Klockars</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>121439106</v>
+        <v>121441224</v>
       </c>
       <c r="B158" t="n">
-        <v>91006</v>
+        <v>98105</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -19434,41 +19425,50 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr"/>
-      <c r="J158" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr"/>
       <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Solberga, Dlr</t>
+          <t>solberga, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>512435</v>
+        <v>512424</v>
       </c>
       <c r="R158" t="n">
-        <v>6728146</v>
+        <v>6728268</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -19521,17 +19521,17 @@
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Göran Ehn, Lisa Olson, Cecilia Rastad, Paula Testad, Lars Johan Klockars</t>
+          <t>Göran Ehn, Lisa Olson, Cecilia Rastad, Lars Johan Klockars, Paula Testad</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>121459519</v>
+        <v>121459568</v>
       </c>
       <c r="B159" t="n">
-        <v>90685</v>
+        <v>91160</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -19540,25 +19540,25 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -19571,10 +19571,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>512484</v>
+        <v>512400</v>
       </c>
       <c r="R159" t="n">
-        <v>6728298</v>
+        <v>6728189</v>
       </c>
       <c r="S159" t="n">
         <v>25</v>
@@ -19606,7 +19606,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -19616,7 +19616,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -19760,7 +19760,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>121459531</v>
+        <v>121459519</v>
       </c>
       <c r="B161" t="n">
         <v>90685</v>
@@ -19803,10 +19803,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>512403</v>
+        <v>512484</v>
       </c>
       <c r="R161" t="n">
-        <v>6728176</v>
+        <v>6728298</v>
       </c>
       <c r="S161" t="n">
         <v>25</v>
@@ -19838,7 +19838,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -19848,7 +19848,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -19992,10 +19992,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>121459568</v>
+        <v>121459578</v>
       </c>
       <c r="B163" t="n">
-        <v>91160</v>
+        <v>90720</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -20004,25 +20004,25 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -20035,10 +20035,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>512400</v>
+        <v>512438</v>
       </c>
       <c r="R163" t="n">
-        <v>6728189</v>
+        <v>6728147</v>
       </c>
       <c r="S163" t="n">
         <v>25</v>
@@ -20070,7 +20070,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -20080,7 +20080,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -20108,10 +20108,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>121459507</v>
+        <v>121459573</v>
       </c>
       <c r="B164" t="n">
-        <v>90720</v>
+        <v>90685</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -20120,25 +20120,25 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -20151,10 +20151,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>512458</v>
+        <v>512405</v>
       </c>
       <c r="R164" t="n">
-        <v>6728308</v>
+        <v>6728193</v>
       </c>
       <c r="S164" t="n">
         <v>25</v>
@@ -20186,7 +20186,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -20196,7 +20196,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -20224,7 +20224,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>121459573</v>
+        <v>121459531</v>
       </c>
       <c r="B165" t="n">
         <v>90685</v>
@@ -20267,10 +20267,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>512405</v>
+        <v>512403</v>
       </c>
       <c r="R165" t="n">
-        <v>6728193</v>
+        <v>6728176</v>
       </c>
       <c r="S165" t="n">
         <v>25</v>
@@ -20302,7 +20302,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -20312,7 +20312,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -20340,7 +20340,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>121459578</v>
+        <v>121459507</v>
       </c>
       <c r="B166" t="n">
         <v>90720</v>
@@ -20383,10 +20383,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>512438</v>
+        <v>512458</v>
       </c>
       <c r="R166" t="n">
-        <v>6728147</v>
+        <v>6728308</v>
       </c>
       <c r="S166" t="n">
         <v>25</v>
@@ -20418,7 +20418,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -20428,7 +20428,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD166" t="b">

--- a/artfynd/A 49115-2023 artfynd.xlsx
+++ b/artfynd/A 49115-2023 artfynd.xlsx
@@ -19182,7 +19182,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>121442191</v>
+        <v>121441224</v>
       </c>
       <c r="B156" t="n">
         <v>98105</v>
@@ -19217,12 +19217,12 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K156" t="inlineStr"/>
@@ -19230,17 +19230,17 @@
       <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Solberga, Dlr</t>
+          <t>solberga, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>512406</v>
+        <v>512424</v>
       </c>
       <c r="R156" t="n">
-        <v>6728220</v>
+        <v>6728268</v>
       </c>
       <c r="S156" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -19282,35 +19282,25 @@
       <c r="AG156" t="b">
         <v>0</v>
       </c>
-      <c r="AH156" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI156" t="inlineStr">
-        <is>
-          <t>Gammal barrnaturskog</t>
-        </is>
-      </c>
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Paula Testad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Paula Testad, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn, Lisa Olson, Cecilia Rastad, Lars Johan Klockars, Paula Testad</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>121439106</v>
+        <v>121442191</v>
       </c>
       <c r="B157" t="n">
-        <v>91006</v>
+        <v>98105</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -19319,30 +19309,39 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr"/>
-      <c r="J157" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr"/>
       <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
@@ -19350,13 +19349,13 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>512435</v>
+        <v>512406</v>
       </c>
       <c r="R157" t="n">
-        <v>6728146</v>
+        <v>6728220</v>
       </c>
       <c r="S157" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -19398,25 +19397,35 @@
       <c r="AG157" t="b">
         <v>0</v>
       </c>
+      <c r="AH157" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI157" t="inlineStr">
+        <is>
+          <t>Gammal barrnaturskog</t>
+        </is>
+      </c>
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Paula Testad</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Göran Ehn, Lisa Olson, Cecilia Rastad, Paula Testad, Lars Johan Klockars</t>
+          <t>Paula Testad, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>121441224</v>
+        <v>121439106</v>
       </c>
       <c r="B158" t="n">
-        <v>98105</v>
+        <v>91006</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -19425,50 +19434,41 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J158" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr"/>
-      <c r="L158" t="inlineStr"/>
       <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>solberga, Dlr</t>
+          <t>Solberga, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>512424</v>
+        <v>512435</v>
       </c>
       <c r="R158" t="n">
-        <v>6728268</v>
+        <v>6728146</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -19521,7 +19521,7 @@
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Göran Ehn, Lisa Olson, Cecilia Rastad, Lars Johan Klockars, Paula Testad</t>
+          <t>Göran Ehn, Lisa Olson, Cecilia Rastad, Paula Testad, Lars Johan Klockars</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
@@ -19644,7 +19644,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>121459575</v>
+        <v>121459531</v>
       </c>
       <c r="B160" t="n">
         <v>90685</v>
@@ -19687,10 +19687,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>512450</v>
+        <v>512403</v>
       </c>
       <c r="R160" t="n">
-        <v>6728160</v>
+        <v>6728176</v>
       </c>
       <c r="S160" t="n">
         <v>25</v>
@@ -19722,7 +19722,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -19732,7 +19732,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -19992,10 +19992,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>121459578</v>
+        <v>121459575</v>
       </c>
       <c r="B163" t="n">
-        <v>90720</v>
+        <v>90685</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -20004,25 +20004,25 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -20035,10 +20035,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>512438</v>
+        <v>512450</v>
       </c>
       <c r="R163" t="n">
-        <v>6728147</v>
+        <v>6728160</v>
       </c>
       <c r="S163" t="n">
         <v>25</v>
@@ -20070,7 +20070,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -20080,7 +20080,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -20108,10 +20108,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>121459573</v>
+        <v>121459507</v>
       </c>
       <c r="B164" t="n">
-        <v>90685</v>
+        <v>90720</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -20120,25 +20120,25 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -20151,10 +20151,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>512405</v>
+        <v>512458</v>
       </c>
       <c r="R164" t="n">
-        <v>6728193</v>
+        <v>6728308</v>
       </c>
       <c r="S164" t="n">
         <v>25</v>
@@ -20186,7 +20186,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -20196,7 +20196,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -20224,10 +20224,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>121459531</v>
+        <v>121459578</v>
       </c>
       <c r="B165" t="n">
-        <v>90685</v>
+        <v>90720</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -20236,25 +20236,25 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -20267,10 +20267,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>512403</v>
+        <v>512438</v>
       </c>
       <c r="R165" t="n">
-        <v>6728176</v>
+        <v>6728147</v>
       </c>
       <c r="S165" t="n">
         <v>25</v>
@@ -20302,7 +20302,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -20312,7 +20312,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -20340,10 +20340,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>121459507</v>
+        <v>121459573</v>
       </c>
       <c r="B166" t="n">
-        <v>90720</v>
+        <v>90685</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -20352,25 +20352,25 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -20383,10 +20383,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>512458</v>
+        <v>512405</v>
       </c>
       <c r="R166" t="n">
-        <v>6728308</v>
+        <v>6728193</v>
       </c>
       <c r="S166" t="n">
         <v>25</v>
@@ -20418,7 +20418,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -20428,7 +20428,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD166" t="b">

--- a/artfynd/A 49115-2023 artfynd.xlsx
+++ b/artfynd/A 49115-2023 artfynd.xlsx
@@ -19182,10 +19182,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>121441224</v>
+        <v>121439106</v>
       </c>
       <c r="B156" t="n">
-        <v>98105</v>
+        <v>91006</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -19194,50 +19194,41 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J156" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr"/>
-      <c r="L156" t="inlineStr"/>
       <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>solberga, Dlr</t>
+          <t>Solberga, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>512424</v>
+        <v>512435</v>
       </c>
       <c r="R156" t="n">
-        <v>6728268</v>
+        <v>6728146</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -19290,14 +19281,14 @@
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Göran Ehn, Lisa Olson, Cecilia Rastad, Lars Johan Klockars, Paula Testad</t>
+          <t>Göran Ehn, Lisa Olson, Cecilia Rastad, Paula Testad, Lars Johan Klockars</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>121442191</v>
+        <v>121441224</v>
       </c>
       <c r="B157" t="n">
         <v>98105</v>
@@ -19332,12 +19323,12 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K157" t="inlineStr"/>
@@ -19345,17 +19336,17 @@
       <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Solberga, Dlr</t>
+          <t>solberga, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>512406</v>
+        <v>512424</v>
       </c>
       <c r="R157" t="n">
-        <v>6728220</v>
+        <v>6728268</v>
       </c>
       <c r="S157" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -19397,35 +19388,25 @@
       <c r="AG157" t="b">
         <v>0</v>
       </c>
-      <c r="AH157" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI157" t="inlineStr">
-        <is>
-          <t>Gammal barrnaturskog</t>
-        </is>
-      </c>
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Paula Testad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Paula Testad, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn, Lisa Olson, Cecilia Rastad, Lars Johan Klockars, Paula Testad</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>121439106</v>
+        <v>121442191</v>
       </c>
       <c r="B158" t="n">
-        <v>91006</v>
+        <v>98105</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -19434,30 +19415,39 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr"/>
-      <c r="J158" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr"/>
       <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
@@ -19465,13 +19455,13 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>512435</v>
+        <v>512406</v>
       </c>
       <c r="R158" t="n">
-        <v>6728146</v>
+        <v>6728220</v>
       </c>
       <c r="S158" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -19513,15 +19503,25 @@
       <c r="AG158" t="b">
         <v>0</v>
       </c>
+      <c r="AH158" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI158" t="inlineStr">
+        <is>
+          <t>Gammal barrnaturskog</t>
+        </is>
+      </c>
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Paula Testad</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Göran Ehn, Lisa Olson, Cecilia Rastad, Paula Testad, Lars Johan Klockars</t>
+          <t>Paula Testad, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
@@ -19644,10 +19644,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>121459531</v>
+        <v>121459578</v>
       </c>
       <c r="B160" t="n">
-        <v>90685</v>
+        <v>90720</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -19656,25 +19656,25 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -19687,10 +19687,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>512403</v>
+        <v>512438</v>
       </c>
       <c r="R160" t="n">
-        <v>6728176</v>
+        <v>6728147</v>
       </c>
       <c r="S160" t="n">
         <v>25</v>
@@ -19722,7 +19722,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -19732,7 +19732,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -19876,7 +19876,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>121459581</v>
+        <v>121459575</v>
       </c>
       <c r="B162" t="n">
         <v>90685</v>
@@ -19919,10 +19919,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>512442</v>
+        <v>512450</v>
       </c>
       <c r="R162" t="n">
-        <v>6728151</v>
+        <v>6728160</v>
       </c>
       <c r="S162" t="n">
         <v>25</v>
@@ -19954,7 +19954,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -19964,7 +19964,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -19992,10 +19992,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>121459575</v>
+        <v>121459507</v>
       </c>
       <c r="B163" t="n">
-        <v>90685</v>
+        <v>90720</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -20004,25 +20004,25 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -20035,10 +20035,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>512450</v>
+        <v>512458</v>
       </c>
       <c r="R163" t="n">
-        <v>6728160</v>
+        <v>6728308</v>
       </c>
       <c r="S163" t="n">
         <v>25</v>
@@ -20070,7 +20070,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -20080,7 +20080,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -20108,10 +20108,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>121459507</v>
+        <v>121459573</v>
       </c>
       <c r="B164" t="n">
-        <v>90720</v>
+        <v>90685</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -20120,25 +20120,25 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -20151,10 +20151,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>512458</v>
+        <v>512405</v>
       </c>
       <c r="R164" t="n">
-        <v>6728308</v>
+        <v>6728193</v>
       </c>
       <c r="S164" t="n">
         <v>25</v>
@@ -20186,7 +20186,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -20196,7 +20196,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -20224,10 +20224,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>121459578</v>
+        <v>121459581</v>
       </c>
       <c r="B165" t="n">
-        <v>90720</v>
+        <v>90685</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -20236,25 +20236,25 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -20267,10 +20267,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>512438</v>
+        <v>512442</v>
       </c>
       <c r="R165" t="n">
-        <v>6728147</v>
+        <v>6728151</v>
       </c>
       <c r="S165" t="n">
         <v>25</v>
@@ -20302,7 +20302,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -20312,7 +20312,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -20340,7 +20340,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>121459573</v>
+        <v>121459531</v>
       </c>
       <c r="B166" t="n">
         <v>90685</v>
@@ -20383,10 +20383,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>512405</v>
+        <v>512403</v>
       </c>
       <c r="R166" t="n">
-        <v>6728193</v>
+        <v>6728176</v>
       </c>
       <c r="S166" t="n">
         <v>25</v>
@@ -20418,7 +20418,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -20428,7 +20428,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD166" t="b">

--- a/artfynd/A 49115-2023 artfynd.xlsx
+++ b/artfynd/A 49115-2023 artfynd.xlsx
@@ -20108,7 +20108,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>121459573</v>
+        <v>121459581</v>
       </c>
       <c r="B164" t="n">
         <v>90685</v>
@@ -20151,10 +20151,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>512405</v>
+        <v>512442</v>
       </c>
       <c r="R164" t="n">
-        <v>6728193</v>
+        <v>6728151</v>
       </c>
       <c r="S164" t="n">
         <v>25</v>
@@ -20186,7 +20186,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -20196,7 +20196,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -20224,7 +20224,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>121459581</v>
+        <v>121459573</v>
       </c>
       <c r="B165" t="n">
         <v>90685</v>
@@ -20267,10 +20267,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>512442</v>
+        <v>512405</v>
       </c>
       <c r="R165" t="n">
-        <v>6728151</v>
+        <v>6728193</v>
       </c>
       <c r="S165" t="n">
         <v>25</v>
@@ -20302,7 +20302,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -20312,7 +20312,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD165" t="b">

--- a/artfynd/A 49115-2023 artfynd.xlsx
+++ b/artfynd/A 49115-2023 artfynd.xlsx
@@ -19288,7 +19288,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>121441224</v>
+        <v>121442191</v>
       </c>
       <c r="B157" t="n">
         <v>98105</v>
@@ -19323,12 +19323,12 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>126</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K157" t="inlineStr"/>
@@ -19336,17 +19336,17 @@
       <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>solberga, Dlr</t>
+          <t>Solberga, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>512424</v>
+        <v>512406</v>
       </c>
       <c r="R157" t="n">
-        <v>6728268</v>
+        <v>6728220</v>
       </c>
       <c r="S157" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -19388,22 +19388,32 @@
       <c r="AG157" t="b">
         <v>0</v>
       </c>
+      <c r="AH157" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI157" t="inlineStr">
+        <is>
+          <t>Gammal barrnaturskog</t>
+        </is>
+      </c>
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Paula Testad</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Göran Ehn, Lisa Olson, Cecilia Rastad, Lars Johan Klockars, Paula Testad</t>
+          <t>Paula Testad, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>121442191</v>
+        <v>121441224</v>
       </c>
       <c r="B158" t="n">
         <v>98105</v>
@@ -19438,12 +19448,12 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K158" t="inlineStr"/>
@@ -19451,17 +19461,17 @@
       <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Solberga, Dlr</t>
+          <t>solberga, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>512406</v>
+        <v>512424</v>
       </c>
       <c r="R158" t="n">
-        <v>6728220</v>
+        <v>6728268</v>
       </c>
       <c r="S158" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -19503,25 +19513,15 @@
       <c r="AG158" t="b">
         <v>0</v>
       </c>
-      <c r="AH158" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI158" t="inlineStr">
-        <is>
-          <t>Gammal barrnaturskog</t>
-        </is>
-      </c>
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Paula Testad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Paula Testad, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn, Lisa Olson, Cecilia Rastad, Lars Johan Klockars, Paula Testad</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
@@ -20108,7 +20108,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>121459581</v>
+        <v>121459573</v>
       </c>
       <c r="B164" t="n">
         <v>90685</v>
@@ -20151,10 +20151,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>512442</v>
+        <v>512405</v>
       </c>
       <c r="R164" t="n">
-        <v>6728151</v>
+        <v>6728193</v>
       </c>
       <c r="S164" t="n">
         <v>25</v>
@@ -20186,7 +20186,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -20196,7 +20196,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -20224,7 +20224,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>121459573</v>
+        <v>121459581</v>
       </c>
       <c r="B165" t="n">
         <v>90685</v>
@@ -20267,10 +20267,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>512405</v>
+        <v>512442</v>
       </c>
       <c r="R165" t="n">
-        <v>6728193</v>
+        <v>6728151</v>
       </c>
       <c r="S165" t="n">
         <v>25</v>
@@ -20302,7 +20302,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -20312,7 +20312,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD165" t="b">

--- a/artfynd/A 49115-2023 artfynd.xlsx
+++ b/artfynd/A 49115-2023 artfynd.xlsx
@@ -19182,10 +19182,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>121439106</v>
+        <v>121442191</v>
       </c>
       <c r="B156" t="n">
-        <v>91006</v>
+        <v>98113</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -19194,30 +19194,39 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr"/>
-      <c r="J156" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr"/>
       <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
@@ -19225,13 +19234,13 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>512435</v>
+        <v>512406</v>
       </c>
       <c r="R156" t="n">
-        <v>6728146</v>
+        <v>6728220</v>
       </c>
       <c r="S156" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -19273,25 +19282,35 @@
       <c r="AG156" t="b">
         <v>0</v>
       </c>
+      <c r="AH156" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI156" t="inlineStr">
+        <is>
+          <t>Gammal barrnaturskog</t>
+        </is>
+      </c>
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Paula Testad</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Göran Ehn, Lisa Olson, Cecilia Rastad, Paula Testad, Lars Johan Klockars</t>
+          <t>Paula Testad, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>121442191</v>
+        <v>121439106</v>
       </c>
       <c r="B157" t="n">
-        <v>98105</v>
+        <v>91014</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -19300,39 +19319,30 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="J157" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr"/>
-      <c r="L157" t="inlineStr"/>
       <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
@@ -19340,13 +19350,13 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>512406</v>
+        <v>512435</v>
       </c>
       <c r="R157" t="n">
-        <v>6728220</v>
+        <v>6728146</v>
       </c>
       <c r="S157" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -19388,25 +19398,15 @@
       <c r="AG157" t="b">
         <v>0</v>
       </c>
-      <c r="AH157" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI157" t="inlineStr">
-        <is>
-          <t>Gammal barrnaturskog</t>
-        </is>
-      </c>
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Paula Testad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Paula Testad, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn, Lisa Olson, Cecilia Rastad, Paula Testad, Lars Johan Klockars</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
@@ -19416,7 +19416,7 @@
         <v>121441224</v>
       </c>
       <c r="B158" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -19528,10 +19528,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>121459568</v>
+        <v>121459573</v>
       </c>
       <c r="B159" t="n">
-        <v>91160</v>
+        <v>90693</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -19540,25 +19540,25 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -19571,10 +19571,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>512400</v>
+        <v>512405</v>
       </c>
       <c r="R159" t="n">
-        <v>6728189</v>
+        <v>6728193</v>
       </c>
       <c r="S159" t="n">
         <v>25</v>
@@ -19606,7 +19606,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -19616,7 +19616,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -19644,10 +19644,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>121459578</v>
+        <v>121459568</v>
       </c>
       <c r="B160" t="n">
-        <v>90720</v>
+        <v>91168</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -19656,25 +19656,25 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -19687,10 +19687,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>512438</v>
+        <v>512400</v>
       </c>
       <c r="R160" t="n">
-        <v>6728147</v>
+        <v>6728189</v>
       </c>
       <c r="S160" t="n">
         <v>25</v>
@@ -19722,7 +19722,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -19732,7 +19732,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -19760,10 +19760,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>121459519</v>
+        <v>121459531</v>
       </c>
       <c r="B161" t="n">
-        <v>90685</v>
+        <v>90693</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -19803,10 +19803,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>512484</v>
+        <v>512403</v>
       </c>
       <c r="R161" t="n">
-        <v>6728298</v>
+        <v>6728176</v>
       </c>
       <c r="S161" t="n">
         <v>25</v>
@@ -19838,7 +19838,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -19848,7 +19848,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -19876,10 +19876,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>121459575</v>
+        <v>121459581</v>
       </c>
       <c r="B162" t="n">
-        <v>90685</v>
+        <v>90693</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -19919,10 +19919,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>512450</v>
+        <v>512442</v>
       </c>
       <c r="R162" t="n">
-        <v>6728160</v>
+        <v>6728151</v>
       </c>
       <c r="S162" t="n">
         <v>25</v>
@@ -19954,7 +19954,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -19964,7 +19964,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -19995,7 +19995,7 @@
         <v>121459507</v>
       </c>
       <c r="B163" t="n">
-        <v>90720</v>
+        <v>90728</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -20108,10 +20108,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>121459573</v>
+        <v>121459519</v>
       </c>
       <c r="B164" t="n">
-        <v>90685</v>
+        <v>90693</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -20151,10 +20151,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>512405</v>
+        <v>512484</v>
       </c>
       <c r="R164" t="n">
-        <v>6728193</v>
+        <v>6728298</v>
       </c>
       <c r="S164" t="n">
         <v>25</v>
@@ -20186,7 +20186,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -20196,7 +20196,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -20224,10 +20224,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>121459581</v>
+        <v>121459578</v>
       </c>
       <c r="B165" t="n">
-        <v>90685</v>
+        <v>90728</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -20236,25 +20236,25 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -20267,10 +20267,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>512442</v>
+        <v>512438</v>
       </c>
       <c r="R165" t="n">
-        <v>6728151</v>
+        <v>6728147</v>
       </c>
       <c r="S165" t="n">
         <v>25</v>
@@ -20302,7 +20302,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -20312,7 +20312,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -20340,10 +20340,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>121459531</v>
+        <v>121459575</v>
       </c>
       <c r="B166" t="n">
-        <v>90685</v>
+        <v>90693</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -20383,10 +20383,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>512403</v>
+        <v>512450</v>
       </c>
       <c r="R166" t="n">
-        <v>6728176</v>
+        <v>6728160</v>
       </c>
       <c r="S166" t="n">
         <v>25</v>
@@ -20418,7 +20418,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -20428,7 +20428,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -20459,7 +20459,7 @@
         <v>121473644</v>
       </c>
       <c r="B167" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>

--- a/artfynd/A 49115-2023 artfynd.xlsx
+++ b/artfynd/A 49115-2023 artfynd.xlsx
@@ -19182,10 +19182,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>121442191</v>
+        <v>121439106</v>
       </c>
       <c r="B156" t="n">
-        <v>98113</v>
+        <v>91014</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -19194,39 +19194,30 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="J156" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr"/>
-      <c r="L156" t="inlineStr"/>
       <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
@@ -19234,13 +19225,13 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>512406</v>
+        <v>512435</v>
       </c>
       <c r="R156" t="n">
-        <v>6728220</v>
+        <v>6728146</v>
       </c>
       <c r="S156" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -19282,32 +19273,22 @@
       <c r="AG156" t="b">
         <v>0</v>
       </c>
-      <c r="AH156" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI156" t="inlineStr">
-        <is>
-          <t>Gammal barrnaturskog</t>
-        </is>
-      </c>
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Paula Testad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Paula Testad, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn, Lisa Olson, Cecilia Rastad, Paula Testad, Lars Johan Klockars</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>121441224</v>
+        <v>121442191</v>
       </c>
       <c r="B157" t="n">
         <v>98113</v>
@@ -19342,12 +19323,12 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>126</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K157" t="inlineStr"/>
@@ -19355,17 +19336,17 @@
       <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>solberga, Dlr</t>
+          <t>Solberga, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>512424</v>
+        <v>512406</v>
       </c>
       <c r="R157" t="n">
-        <v>6728268</v>
+        <v>6728220</v>
       </c>
       <c r="S157" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -19407,25 +19388,35 @@
       <c r="AG157" t="b">
         <v>0</v>
       </c>
+      <c r="AH157" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI157" t="inlineStr">
+        <is>
+          <t>Gammal barrnaturskog</t>
+        </is>
+      </c>
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Paula Testad</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Göran Ehn, Lisa Olson, Cecilia Rastad, Lars Johan Klockars, Paula Testad</t>
+          <t>Paula Testad, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>121439106</v>
+        <v>121441224</v>
       </c>
       <c r="B158" t="n">
-        <v>91014</v>
+        <v>98113</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -19434,41 +19425,50 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr"/>
-      <c r="J158" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr"/>
       <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Solberga, Dlr</t>
+          <t>solberga, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>512435</v>
+        <v>512424</v>
       </c>
       <c r="R158" t="n">
-        <v>6728146</v>
+        <v>6728268</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -19521,17 +19521,17 @@
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Göran Ehn, Lisa Olson, Cecilia Rastad, Paula Testad, Lars Johan Klockars</t>
+          <t>Göran Ehn, Lisa Olson, Cecilia Rastad, Lars Johan Klockars, Paula Testad</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>121459578</v>
+        <v>121459531</v>
       </c>
       <c r="B159" t="n">
-        <v>90728</v>
+        <v>90693</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -19540,25 +19540,25 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -19571,10 +19571,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>512438</v>
+        <v>512403</v>
       </c>
       <c r="R159" t="n">
-        <v>6728147</v>
+        <v>6728176</v>
       </c>
       <c r="S159" t="n">
         <v>25</v>
@@ -19606,7 +19606,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -19616,7 +19616,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -19644,10 +19644,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>121459581</v>
+        <v>121459507</v>
       </c>
       <c r="B160" t="n">
-        <v>90693</v>
+        <v>90728</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -19656,25 +19656,25 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -19687,10 +19687,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>512442</v>
+        <v>512458</v>
       </c>
       <c r="R160" t="n">
-        <v>6728151</v>
+        <v>6728308</v>
       </c>
       <c r="S160" t="n">
         <v>25</v>
@@ -19722,7 +19722,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -19732,7 +19732,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -19760,7 +19760,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>121459531</v>
+        <v>121459573</v>
       </c>
       <c r="B161" t="n">
         <v>90693</v>
@@ -19803,10 +19803,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>512403</v>
+        <v>512405</v>
       </c>
       <c r="R161" t="n">
-        <v>6728176</v>
+        <v>6728193</v>
       </c>
       <c r="S161" t="n">
         <v>25</v>
@@ -19838,7 +19838,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -19848,7 +19848,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -19876,10 +19876,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>121459568</v>
+        <v>121459578</v>
       </c>
       <c r="B162" t="n">
-        <v>91168</v>
+        <v>90728</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -19888,25 +19888,25 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -19919,10 +19919,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>512400</v>
+        <v>512438</v>
       </c>
       <c r="R162" t="n">
-        <v>6728189</v>
+        <v>6728147</v>
       </c>
       <c r="S162" t="n">
         <v>25</v>
@@ -19954,7 +19954,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -19964,7 +19964,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -19992,7 +19992,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>121459573</v>
+        <v>121459575</v>
       </c>
       <c r="B163" t="n">
         <v>90693</v>
@@ -20035,10 +20035,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>512405</v>
+        <v>512450</v>
       </c>
       <c r="R163" t="n">
-        <v>6728193</v>
+        <v>6728160</v>
       </c>
       <c r="S163" t="n">
         <v>25</v>
@@ -20070,7 +20070,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -20080,7 +20080,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -20108,10 +20108,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>121459519</v>
+        <v>121459568</v>
       </c>
       <c r="B164" t="n">
-        <v>90693</v>
+        <v>91168</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -20120,25 +20120,25 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -20151,10 +20151,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>512484</v>
+        <v>512400</v>
       </c>
       <c r="R164" t="n">
-        <v>6728298</v>
+        <v>6728189</v>
       </c>
       <c r="S164" t="n">
         <v>25</v>
@@ -20186,7 +20186,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -20196,7 +20196,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -20224,10 +20224,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>121459507</v>
+        <v>121459519</v>
       </c>
       <c r="B165" t="n">
-        <v>90728</v>
+        <v>90693</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -20236,25 +20236,25 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -20267,10 +20267,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>512458</v>
+        <v>512484</v>
       </c>
       <c r="R165" t="n">
-        <v>6728308</v>
+        <v>6728298</v>
       </c>
       <c r="S165" t="n">
         <v>25</v>
@@ -20302,7 +20302,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -20312,7 +20312,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -20340,7 +20340,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>121459575</v>
+        <v>121459581</v>
       </c>
       <c r="B166" t="n">
         <v>90693</v>
@@ -20383,10 +20383,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>512450</v>
+        <v>512442</v>
       </c>
       <c r="R166" t="n">
-        <v>6728160</v>
+        <v>6728151</v>
       </c>
       <c r="S166" t="n">
         <v>25</v>
@@ -20418,7 +20418,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -20428,7 +20428,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD166" t="b">

--- a/artfynd/A 49115-2023 artfynd.xlsx
+++ b/artfynd/A 49115-2023 artfynd.xlsx
@@ -9182,7 +9182,7 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Paula Testad, Lars Johan Klockars</t>
+          <t>Lars Johan Klockars, Paula Testad</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>

--- a/artfynd/A 49115-2023 artfynd.xlsx
+++ b/artfynd/A 49115-2023 artfynd.xlsx
@@ -4209,7 +4209,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Paula Testad, Lars Johan Klockars</t>
+          <t>Lars Johan Klockars, Paula Testad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -9182,7 +9182,7 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Lars Johan Klockars, Paula Testad</t>
+          <t>Paula Testad, Lars Johan Klockars</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>

--- a/artfynd/A 49115-2023 artfynd.xlsx
+++ b/artfynd/A 49115-2023 artfynd.xlsx
@@ -4209,7 +4209,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Lars Johan Klockars, Paula Testad</t>
+          <t>Paula Testad, Lars Johan Klockars</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>

--- a/artfynd/A 49115-2023 artfynd.xlsx
+++ b/artfynd/A 49115-2023 artfynd.xlsx
@@ -9182,7 +9182,7 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Lars Johan Klockars, Paula Testad</t>
+          <t>Paula Testad, Lars Johan Klockars</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>

--- a/artfynd/A 49115-2023 artfynd.xlsx
+++ b/artfynd/A 49115-2023 artfynd.xlsx
@@ -1593,7 +1593,7 @@
         <v>115142434</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>115143099</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>115142552</v>
       </c>
       <c r="B14" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -3753,7 +3753,7 @@
         <v>116204119</v>
       </c>
       <c r="B29" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         <v>116203980</v>
       </c>
       <c r="B30" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4099,7 +4099,7 @@
         <v>116204226</v>
       </c>
       <c r="B32" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>116226914</v>
       </c>
       <c r="B36" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         <v>116226859</v>
       </c>
       <c r="B37" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5180,7 +5180,7 @@
         <v>116226784</v>
       </c>
       <c r="B41" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5300,7 +5300,7 @@
         <v>116226828</v>
       </c>
       <c r="B42" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
         <v>116299804</v>
       </c>
       <c r="B49" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -7400,7 +7400,7 @@
         <v>116253318</v>
       </c>
       <c r="B59" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -9072,7 +9072,7 @@
         <v>116451965</v>
       </c>
       <c r="B73" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -10157,7 +10157,7 @@
         <v>117694331</v>
       </c>
       <c r="B82" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10513,7 +10513,7 @@
         <v>117694297</v>
       </c>
       <c r="B85" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10633,7 +10633,7 @@
         <v>117694195</v>
       </c>
       <c r="B86" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10753,7 +10753,7 @@
         <v>117694462</v>
       </c>
       <c r="B87" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -11105,7 +11105,7 @@
         <v>117694775</v>
       </c>
       <c r="B90" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11225,7 +11225,7 @@
         <v>117694161</v>
       </c>
       <c r="B91" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11461,7 +11461,7 @@
         <v>117694131</v>
       </c>
       <c r="B93" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11581,7 +11581,7 @@
         <v>117694724</v>
       </c>
       <c r="B94" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -12054,7 +12054,7 @@
         <v>117694278</v>
       </c>
       <c r="B98" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
